--- a/AAAGameData/Translations/Localization.xlsx
+++ b/AAAGameData/Translations/Localization.xlsx
@@ -553,573 +553,579 @@
     <t>Cash out</t>
   </si>
   <si>
-    <t>Canjear</t>
-  </si>
-  <si>
-    <t>Échanger</t>
-  </si>
-  <si>
-    <t>Обменять</t>
-  </si>
-  <si>
-    <t>交換</t>
-  </si>
-  <si>
-    <t>रिडीम करें</t>
+    <t>Sacar</t>
+  </si>
+  <si>
+    <t>Levantar</t>
+  </si>
+  <si>
+    <t>Retirar</t>
+  </si>
+  <si>
+    <t>Retirer</t>
+  </si>
+  <si>
+    <t>Вывести</t>
+  </si>
+  <si>
+    <t>出金</t>
+  </si>
+  <si>
+    <t>निकासी करें</t>
+  </si>
+  <si>
+    <t>ArrowWithdrawalInfoItem.infoTxt</t>
+  </si>
+  <si>
+    <t>Congratulations to player {0} for passing ({1}) and claiming {2}.</t>
+  </si>
+  <si>
+    <t>Parabéns ao jogador {0} por concluir ({1}) e resgatar {2}.</t>
+  </si>
+  <si>
+    <t>Parabéns ao jogador {0} por concluir ({1}) e receber {2}.</t>
+  </si>
+  <si>
+    <t>Felicidades al jugador {0} por superar ({1}) y reclamar {2}.</t>
+  </si>
+  <si>
+    <t>Félicitations au joueur {0} pour avoir terminé ({1}) et récupéré {2}.</t>
+  </si>
+  <si>
+    <t>Поздравляем игрока {0} с прохождением ({1}) и получением {2}.</t>
+  </si>
+  <si>
+    <t>プレイヤー{0}さん、({1})のクリアと{2}の獲得、おめでとうございます！</t>
+  </si>
+  <si>
+    <t>खिलाड़ी {0} को ({1}) पार करने और {2} प्राप्त करने पर बधाई।</t>
+  </si>
+  <si>
+    <t>claim</t>
+  </si>
+  <si>
+    <t>CoinRewardUIForm.titletxt</t>
+  </si>
+  <si>
+    <t>Enteraccountnumber</t>
+  </si>
+  <si>
+    <t>Enter your account</t>
+  </si>
+  <si>
+    <t>Digite sua conta</t>
+  </si>
+  <si>
+    <t>Introduza a sua conta</t>
+  </si>
+  <si>
+    <t>Introduce tu cuenta</t>
+  </si>
+  <si>
+    <t>Saisissez votre compte</t>
+  </si>
+  <si>
+    <t>Введите свой счёт</t>
+  </si>
+  <si>
+    <t>口座を入力</t>
+  </si>
+  <si>
+    <t>अपना खाता दर्ज करें</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>EnterCPF</t>
+  </si>
+  <si>
+    <t>Enter CPF</t>
+  </si>
+  <si>
+    <t>Digite o CPF</t>
+  </si>
+  <si>
+    <t>Introduza o CPF</t>
+  </si>
+  <si>
+    <t>Introduce el CPF</t>
+  </si>
+  <si>
+    <t>Saisissez le CPF</t>
+  </si>
+  <si>
+    <t>Введите CPF</t>
+  </si>
+  <si>
+    <t>CPFを入力</t>
+  </si>
+  <si>
+    <t>CPF दर्ज करें</t>
+  </si>
+  <si>
+    <t>Enteremail</t>
+  </si>
+  <si>
+    <t>Confirm email</t>
+  </si>
+  <si>
+    <t>Confirme o e-mail</t>
+  </si>
+  <si>
+    <t>Confirma el correo electrónico</t>
+  </si>
+  <si>
+    <t>Confirmez l’adresse e-mail</t>
+  </si>
+  <si>
+    <t>Подтвердите электронную почту</t>
+  </si>
+  <si>
+    <t>メールアドレスを確認</t>
+  </si>
+  <si>
+    <t>ईमेल की पुष्टि करें</t>
+  </si>
+  <si>
+    <t>EnterFullName</t>
+  </si>
+  <si>
+    <t>Enter Full Name</t>
+  </si>
+  <si>
+    <t>Digite o nome completo</t>
+  </si>
+  <si>
+    <t>Introduza o nome completo</t>
+  </si>
+  <si>
+    <t>Introduce tu nombre completo</t>
+  </si>
+  <si>
+    <t>Saisissez votre nom complet</t>
+  </si>
+  <si>
+    <t>Введите полное имя</t>
+  </si>
+  <si>
+    <t>氏名を入力</t>
+  </si>
+  <si>
+    <t>पूरा नाम दर्ज करें</t>
+  </si>
+  <si>
+    <t>EnterPayPalaccount</t>
+  </si>
+  <si>
+    <t>Enter PayPal account</t>
+  </si>
+  <si>
+    <t>Digite a conta do PayPal</t>
+  </si>
+  <si>
+    <t>Introduza a conta PayPal</t>
+  </si>
+  <si>
+    <t>Introduce tu cuenta de PayPal</t>
+  </si>
+  <si>
+    <t>Saisissez votre compte PayPal</t>
+  </si>
+  <si>
+    <t>Введите аккаунт PayPal</t>
+  </si>
+  <si>
+    <t>PayPalアカウントを入力</t>
+  </si>
+  <si>
+    <t>PayPal खाता दर्ज करें</t>
+  </si>
+  <si>
+    <t>GuidTxt1</t>
+  </si>
+  <si>
+    <t>Tap to Move</t>
+  </si>
+  <si>
+    <t>Toque para mover</t>
+  </si>
+  <si>
+    <t>Toca para mover</t>
+  </si>
+  <si>
+    <t>Touchez pour déplacer</t>
+  </si>
+  <si>
+    <t>Нажмите, чтобы переместить</t>
+  </si>
+  <si>
+    <t>タップして移動</t>
+  </si>
+  <si>
+    <t>हिलाने के लिए टैप करें</t>
+  </si>
+  <si>
+    <t>GuidTxt3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Click here to cash out </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toque aqui para sacar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toque aqui para levantar </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Toca aquí para retirar dinero </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Touchez ici pour retirer de l’argent </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Нажмите здесь, чтобы вывести деньги </t>
+  </si>
+  <si>
+    <t xml:space="preserve">ここをタップして出金 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">पैसे निकालने के लिए यहाँ टैप करें </t>
+  </si>
+  <si>
+    <t>GuidTxt4</t>
+  </si>
+  <si>
+    <t>Spread Fingers to Zoom</t>
+  </si>
+  <si>
+    <t>Afaste os dedos para ampliar</t>
+  </si>
+  <si>
+    <t>Separa los dedos para ampliar</t>
+  </si>
+  <si>
+    <t>Écartez les doigts pour zoomer</t>
+  </si>
+  <si>
+    <t>Разведите пальцы, чтобы увеличить</t>
+  </si>
+  <si>
+    <t>指を広げて拡大</t>
+  </si>
+  <si>
+    <t>ज़ूम करने के लिए उँगलियाँ फैलाएँ</t>
+  </si>
+  <si>
+    <t>GuidTxt5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Please find your current balance here. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confira seu saldo atual aqui. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consulte aqui o seu saldo atual. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consulta aquí tu saldo actual. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Consultez votre solde actuel ici. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Здесь указан ваш текущий баланс. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">現在の残高はこちらで確認できます。 </t>
+  </si>
+  <si>
+    <t xml:space="preserve">अपना वर्तमान बैलेंस यहाँ देखें। </t>
+  </si>
+  <si>
+    <t>GuidTxt6</t>
+  </si>
+  <si>
+    <t>Complete requirements to cash out.</t>
+  </si>
+  <si>
+    <t>Cumpra os requisitos para sacar.</t>
+  </si>
+  <si>
+    <t>Cumpra os requisitos para levantar dinheiro.</t>
+  </si>
+  <si>
+    <t>Cumple los requisitos para retirar dinero.</t>
+  </si>
+  <si>
+    <t>Remplissez les conditions pour retirer de l’argent.</t>
+  </si>
+  <si>
+    <t>Выполните условия для вывода денег.</t>
+  </si>
+  <si>
+    <t>条件を達成すると出金できます。</t>
+  </si>
+  <si>
+    <t>पैसे निकालने के लिए शर्तें पूरी करें।</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.home</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.setting</t>
+  </si>
+  <si>
+    <t>Setting</t>
+  </si>
+  <si>
+    <t>HallTabUIForm.task</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Tarefa</t>
+  </si>
+  <si>
+    <t>Tarea</t>
+  </si>
+  <si>
+    <t>Tâche</t>
+  </si>
+  <si>
+    <t>Задание</t>
+  </si>
+  <si>
+    <t>タスク</t>
+  </si>
+  <si>
+    <t>कार्य</t>
+  </si>
+  <si>
+    <t>InfoErrTips1</t>
+  </si>
+  <si>
+    <t>Please enter a valid email address</t>
+  </si>
+  <si>
+    <t>Digite um endereço de e-mail válido</t>
+  </si>
+  <si>
+    <t>Introduza um endereço de e-mail válido</t>
+  </si>
+  <si>
+    <t>Introduce una dirección de correo electrónico válida</t>
+  </si>
+  <si>
+    <t>Veuillez saisir une adresse e-mail valide</t>
+  </si>
+  <si>
+    <t>Введите действительный адрес электронной почты</t>
+  </si>
+  <si>
+    <t>有効なメールアドレスを入力してください</t>
+  </si>
+  <si>
+    <t>कृपया एक मान्य ईमेल पता दर्ज करें</t>
+  </si>
+  <si>
+    <t>InfoErrTips2</t>
+  </si>
+  <si>
+    <t>Please enter a valid CPF</t>
+  </si>
+  <si>
+    <t>Digite um CPF válido</t>
+  </si>
+  <si>
+    <t>Introduza um CPF válido</t>
+  </si>
+  <si>
+    <t>Introduce un CPF válido</t>
+  </si>
+  <si>
+    <t>Veuillez saisir un CPF valide</t>
+  </si>
+  <si>
+    <t>Введите действительный CPF</t>
+  </si>
+  <si>
+    <t>有効なCPFを入力してください</t>
+  </si>
+  <si>
+    <t>कृपया एक मान्य CPF दर्ज करें</t>
+  </si>
+  <si>
+    <t>InfoErrTips3</t>
+  </si>
+  <si>
+    <t>PayPal account must be a valid email</t>
+  </si>
+  <si>
+    <t>A conta do PayPal deve ser um e-mail válido</t>
+  </si>
+  <si>
+    <t>A conta PayPal deve ser um e-mail válido</t>
+  </si>
+  <si>
+    <t>La cuenta de PayPal debe ser una dirección de correo electrónico válida</t>
+  </si>
+  <si>
+    <t>Le compte PayPal doit être une adresse e-mail valide</t>
+  </si>
+  <si>
+    <t>Аккаунт PayPal должен быть действительным адресом электронной почты</t>
+  </si>
+  <si>
+    <t>PayPalアカウントには有効なメールアドレスが必要です</t>
+  </si>
+  <si>
+    <t>PayPal खाते के लिए एक मान्य ईमेल पता आवश्यक है</t>
+  </si>
+  <si>
+    <t>InfoErrTips4</t>
+  </si>
+  <si>
+    <t>Please enter your full name</t>
+  </si>
+  <si>
+    <t>Digite seu nome completo</t>
+  </si>
+  <si>
+    <t>Introduza o seu nome completo</t>
+  </si>
+  <si>
+    <t>Veuillez saisir votre nom complet</t>
+  </si>
+  <si>
+    <t>Введите своё полное имя</t>
+  </si>
+  <si>
+    <t>氏名を入力してください</t>
+  </si>
+  <si>
+    <t>कृपया अपना पूरा नाम दर्ज करें</t>
+  </si>
+  <si>
+    <t>InfoErrTips5</t>
+  </si>
+  <si>
+    <t>Please enter your account number</t>
+  </si>
+  <si>
+    <t>Digite o número da sua conta</t>
+  </si>
+  <si>
+    <t>Introduza o número da sua conta</t>
+  </si>
+  <si>
+    <t>Introduce tu número de cuenta</t>
+  </si>
+  <si>
+    <t>Veuillez saisir votre numéro de compte</t>
+  </si>
+  <si>
+    <t>Введите номер своего счёта</t>
+  </si>
+  <si>
+    <t>口座番号を入力してください</t>
+  </si>
+  <si>
+    <t>कृपया अपना खाता नंबर दर्ज करें</t>
+  </si>
+  <si>
+    <t>InfoErrTips6</t>
+  </si>
+  <si>
+    <t>Please select a payment method</t>
+  </si>
+  <si>
+    <t>Selecione uma forma de pagamento</t>
+  </si>
+  <si>
+    <t>Selecione um método de pagamento</t>
+  </si>
+  <si>
+    <t>Selecciona un método de pago</t>
+  </si>
+  <si>
+    <t>Veuillez sélectionner un mode de paiement</t>
+  </si>
+  <si>
+    <t>Выберите способ оплаты</t>
+  </si>
+  <si>
+    <t>お支払い方法を選択してください</t>
+  </si>
+  <si>
+    <t>कृपया भुगतान का तरीका चुनें</t>
+  </si>
+  <si>
+    <t>InfoErrTips7</t>
+  </si>
+  <si>
+    <t>Payment information saved successfully</t>
+  </si>
+  <si>
+    <t>Dados de pagamento salvos com sucesso</t>
+  </si>
+  <si>
+    <t>Dados de pagamento guardados com sucesso</t>
+  </si>
+  <si>
+    <t>Información de pago guardada correctamente</t>
+  </si>
+  <si>
+    <t>Informations de paiement enregistrées</t>
+  </si>
+  <si>
+    <t>Платёжные данные успешно сохранены</t>
+  </si>
+  <si>
+    <t>お支払い情報を保存しました</t>
+  </si>
+  <si>
+    <t>भुगतान की जानकारी सफलतापूर्वक सहेजी गई</t>
+  </si>
+  <si>
+    <t>level</t>
+  </si>
+  <si>
+    <t>Level {0}</t>
+  </si>
+  <si>
+    <t>Fase {0}</t>
+  </si>
+  <si>
+    <t>Nível {0}</t>
+  </si>
+  <si>
+    <t>Nivel {0}</t>
+  </si>
+  <si>
+    <t>Niveau {0}</t>
+  </si>
+  <si>
+    <t>Уровень {0}</t>
+  </si>
+  <si>
+    <t>ステージ{0}</t>
+  </si>
+  <si>
+    <t>स्तर {0}</t>
+  </si>
+  <si>
+    <t>LevelCompleteUIForm.complete</t>
+  </si>
+  <si>
+    <t>Completed</t>
   </si>
   <si>
     <t>待复核</t>
   </si>
   <si>
-    <t>Redeem</t>
-  </si>
-  <si>
-    <t>ArrowWithdrawalInfoItem.infoTxt</t>
-  </si>
-  <si>
-    <t>Congratulations to player {0} for passing ({1}) and claiming {2}.</t>
-  </si>
-  <si>
-    <t>Parabéns ao jogador {0} por concluir ({1}) e resgatar {2}.</t>
-  </si>
-  <si>
-    <t>Parabéns ao jogador {0} por concluir ({1}) e receber {2}.</t>
-  </si>
-  <si>
-    <t>Felicidades al jugador {0} por superar ({1}) y reclamar {2}.</t>
-  </si>
-  <si>
-    <t>Félicitations au joueur {0} pour avoir terminé ({1}) et récupéré {2}.</t>
-  </si>
-  <si>
-    <t>Поздравляем игрока {0} с прохождением ({1}) и получением {2}.</t>
-  </si>
-  <si>
-    <t>プレイヤー{0}さん、({1})のクリアと{2}の獲得、おめでとうございます！</t>
-  </si>
-  <si>
-    <t>खिलाड़ी {0} को ({1}) पार करने और {2} प्राप्त करने पर बधाई।</t>
-  </si>
-  <si>
-    <t>claim</t>
-  </si>
-  <si>
-    <t>CoinRewardUIForm.titletxt</t>
-  </si>
-  <si>
-    <t>Enteraccountnumber</t>
-  </si>
-  <si>
-    <t>Enter your account</t>
-  </si>
-  <si>
-    <t>Digite sua conta</t>
-  </si>
-  <si>
-    <t>Introduza a sua conta</t>
-  </si>
-  <si>
-    <t>Introduce tu cuenta</t>
-  </si>
-  <si>
-    <t>Saisissez votre compte</t>
-  </si>
-  <si>
-    <t>Введите свой счёт</t>
-  </si>
-  <si>
-    <t>口座を入力</t>
-  </si>
-  <si>
-    <t>अपना खाता दर्ज करें</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>EnterCPF</t>
-  </si>
-  <si>
-    <t>Enter CPF</t>
-  </si>
-  <si>
-    <t>Digite o CPF</t>
-  </si>
-  <si>
-    <t>Introduza o CPF</t>
-  </si>
-  <si>
-    <t>Introduce el CPF</t>
-  </si>
-  <si>
-    <t>Saisissez le CPF</t>
-  </si>
-  <si>
-    <t>Введите CPF</t>
-  </si>
-  <si>
-    <t>CPFを入力</t>
-  </si>
-  <si>
-    <t>CPF दर्ज करें</t>
-  </si>
-  <si>
-    <t>Enteremail</t>
-  </si>
-  <si>
-    <t>Confirm email</t>
-  </si>
-  <si>
-    <t>Confirme o e-mail</t>
-  </si>
-  <si>
-    <t>Confirma el correo electrónico</t>
-  </si>
-  <si>
-    <t>Confirmez l’adresse e-mail</t>
-  </si>
-  <si>
-    <t>Подтвердите электронную почту</t>
-  </si>
-  <si>
-    <t>メールアドレスを確認</t>
-  </si>
-  <si>
-    <t>ईमेल की पुष्टि करें</t>
-  </si>
-  <si>
-    <t>EnterFullName</t>
-  </si>
-  <si>
-    <t>Enter Full Name</t>
-  </si>
-  <si>
-    <t>Digite o nome completo</t>
-  </si>
-  <si>
-    <t>Introduza o nome completo</t>
-  </si>
-  <si>
-    <t>Introduce tu nombre completo</t>
-  </si>
-  <si>
-    <t>Saisissez votre nom complet</t>
-  </si>
-  <si>
-    <t>Введите полное имя</t>
-  </si>
-  <si>
-    <t>氏名を入力</t>
-  </si>
-  <si>
-    <t>पूरा नाम दर्ज करें</t>
-  </si>
-  <si>
-    <t>EnterPayPalaccount</t>
-  </si>
-  <si>
-    <t>Enter PayPal account</t>
-  </si>
-  <si>
-    <t>Digite a conta do PayPal</t>
-  </si>
-  <si>
-    <t>Introduza a conta PayPal</t>
-  </si>
-  <si>
-    <t>Introduce tu cuenta de PayPal</t>
-  </si>
-  <si>
-    <t>Saisissez votre compte PayPal</t>
-  </si>
-  <si>
-    <t>Введите аккаунт PayPal</t>
-  </si>
-  <si>
-    <t>PayPalアカウントを入力</t>
-  </si>
-  <si>
-    <t>PayPal खाता दर्ज करें</t>
-  </si>
-  <si>
-    <t>GuidTxt1</t>
-  </si>
-  <si>
-    <t>Tap to Move</t>
-  </si>
-  <si>
-    <t>Toque para mover</t>
-  </si>
-  <si>
-    <t>Toca para mover</t>
-  </si>
-  <si>
-    <t>Touchez pour déplacer</t>
-  </si>
-  <si>
-    <t>Нажмите, чтобы переместить</t>
-  </si>
-  <si>
-    <t>タップして移動</t>
-  </si>
-  <si>
-    <t>हिलाने के लिए टैप करें</t>
-  </si>
-  <si>
-    <t>GuidTxt3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Click here to cash out </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toque aqui para sacar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toque aqui para levantar </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Toca aquí para retirar dinero </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Touchez ici pour retirer de l’argent </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Нажмите здесь, чтобы вывести деньги </t>
-  </si>
-  <si>
-    <t xml:space="preserve">ここをタップして出金 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">पैसे निकालने के लिए यहाँ टैप करें </t>
-  </si>
-  <si>
-    <t>GuidTxt4</t>
-  </si>
-  <si>
-    <t>Spread Fingers to Zoom</t>
-  </si>
-  <si>
-    <t>Afaste os dedos para ampliar</t>
-  </si>
-  <si>
-    <t>Separa los dedos para ampliar</t>
-  </si>
-  <si>
-    <t>Écartez les doigts pour zoomer</t>
-  </si>
-  <si>
-    <t>Разведите пальцы, чтобы увеличить</t>
-  </si>
-  <si>
-    <t>指を広げて拡大</t>
-  </si>
-  <si>
-    <t>ज़ूम करने के लिए उँगलियाँ फैलाएँ</t>
-  </si>
-  <si>
-    <t>GuidTxt5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Please find your current balance here. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confira seu saldo atual aqui. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulte aqui o seu saldo atual. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consulta aquí tu saldo actual. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Consultez votre solde actuel ici. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Здесь указан ваш текущий баланс. </t>
-  </si>
-  <si>
-    <t xml:space="preserve">現在の残高はこちらで確認できます。 </t>
-  </si>
-  <si>
-    <t xml:space="preserve">अपना वर्तमान बैलेंस यहाँ देखें। </t>
-  </si>
-  <si>
-    <t>GuidTxt6</t>
-  </si>
-  <si>
-    <t>Complete requirements to cash out.</t>
-  </si>
-  <si>
-    <t>Cumpra os requisitos para sacar.</t>
-  </si>
-  <si>
-    <t>Cumpra os requisitos para levantar dinheiro.</t>
-  </si>
-  <si>
-    <t>Cumple los requisitos para retirar dinero.</t>
-  </si>
-  <si>
-    <t>Remplissez les conditions pour retirer de l’argent.</t>
-  </si>
-  <si>
-    <t>Выполните условия для вывода денег.</t>
-  </si>
-  <si>
-    <t>条件を達成すると出金できます。</t>
-  </si>
-  <si>
-    <t>पैसे निकालने के लिए शर्तें पूरी करें।</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.home</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.setting</t>
-  </si>
-  <si>
-    <t>Setting</t>
-  </si>
-  <si>
-    <t>HallTabUIForm.task</t>
-  </si>
-  <si>
-    <t>Task</t>
-  </si>
-  <si>
-    <t>Tarefa</t>
-  </si>
-  <si>
-    <t>Tarea</t>
-  </si>
-  <si>
-    <t>Tâche</t>
-  </si>
-  <si>
-    <t>Задание</t>
-  </si>
-  <si>
-    <t>タスク</t>
-  </si>
-  <si>
-    <t>कार्य</t>
-  </si>
-  <si>
-    <t>InfoErrTips1</t>
-  </si>
-  <si>
-    <t>Please enter a valid email address</t>
-  </si>
-  <si>
-    <t>Digite um endereço de e-mail válido</t>
-  </si>
-  <si>
-    <t>Introduza um endereço de e-mail válido</t>
-  </si>
-  <si>
-    <t>Introduce una dirección de correo electrónico válida</t>
-  </si>
-  <si>
-    <t>Veuillez saisir une adresse e-mail valide</t>
-  </si>
-  <si>
-    <t>Введите действительный адрес электронной почты</t>
-  </si>
-  <si>
-    <t>有効なメールアドレスを入力してください</t>
-  </si>
-  <si>
-    <t>कृपया एक मान्य ईमेल पता दर्ज करें</t>
-  </si>
-  <si>
-    <t>InfoErrTips2</t>
-  </si>
-  <si>
-    <t>Please enter a valid CPF</t>
-  </si>
-  <si>
-    <t>Digite um CPF válido</t>
-  </si>
-  <si>
-    <t>Introduza um CPF válido</t>
-  </si>
-  <si>
-    <t>Introduce un CPF válido</t>
-  </si>
-  <si>
-    <t>Veuillez saisir un CPF valide</t>
-  </si>
-  <si>
-    <t>Введите действительный CPF</t>
-  </si>
-  <si>
-    <t>有効なCPFを入力してください</t>
-  </si>
-  <si>
-    <t>कृपया एक मान्य CPF दर्ज करें</t>
-  </si>
-  <si>
-    <t>InfoErrTips3</t>
-  </si>
-  <si>
-    <t>PayPal account must be a valid email</t>
-  </si>
-  <si>
-    <t>A conta do PayPal deve ser um e-mail válido</t>
-  </si>
-  <si>
-    <t>A conta PayPal deve ser um e-mail válido</t>
-  </si>
-  <si>
-    <t>La cuenta de PayPal debe ser una dirección de correo electrónico válida</t>
-  </si>
-  <si>
-    <t>Le compte PayPal doit être une adresse e-mail valide</t>
-  </si>
-  <si>
-    <t>Аккаунт PayPal должен быть действительным адресом электронной почты</t>
-  </si>
-  <si>
-    <t>PayPalアカウントには有効なメールアドレスが必要です</t>
-  </si>
-  <si>
-    <t>PayPal खाते के लिए एक मान्य ईमेल पता आवश्यक है</t>
-  </si>
-  <si>
-    <t>InfoErrTips4</t>
-  </si>
-  <si>
-    <t>Please enter your full name</t>
-  </si>
-  <si>
-    <t>Digite seu nome completo</t>
-  </si>
-  <si>
-    <t>Introduza o seu nome completo</t>
-  </si>
-  <si>
-    <t>Veuillez saisir votre nom complet</t>
-  </si>
-  <si>
-    <t>Введите своё полное имя</t>
-  </si>
-  <si>
-    <t>氏名を入力してください</t>
-  </si>
-  <si>
-    <t>कृपया अपना पूरा नाम दर्ज करें</t>
-  </si>
-  <si>
-    <t>InfoErrTips5</t>
-  </si>
-  <si>
-    <t>Please enter your account number</t>
-  </si>
-  <si>
-    <t>Digite o número da sua conta</t>
-  </si>
-  <si>
-    <t>Introduza o número da sua conta</t>
-  </si>
-  <si>
-    <t>Introduce tu número de cuenta</t>
-  </si>
-  <si>
-    <t>Veuillez saisir votre numéro de compte</t>
-  </si>
-  <si>
-    <t>Введите номер своего счёта</t>
-  </si>
-  <si>
-    <t>口座番号を入力してください</t>
-  </si>
-  <si>
-    <t>कृपया अपना खाता नंबर दर्ज करें</t>
-  </si>
-  <si>
-    <t>InfoErrTips6</t>
-  </si>
-  <si>
-    <t>Please select a payment method</t>
-  </si>
-  <si>
-    <t>Selecione uma forma de pagamento</t>
-  </si>
-  <si>
-    <t>Selecione um método de pagamento</t>
-  </si>
-  <si>
-    <t>Selecciona un método de pago</t>
-  </si>
-  <si>
-    <t>Veuillez sélectionner un mode de paiement</t>
-  </si>
-  <si>
-    <t>Выберите способ оплаты</t>
-  </si>
-  <si>
-    <t>お支払い方法を選択してください</t>
-  </si>
-  <si>
-    <t>कृपया भुगतान का तरीका चुनें</t>
-  </si>
-  <si>
-    <t>InfoErrTips7</t>
-  </si>
-  <si>
-    <t>Payment information saved successfully</t>
-  </si>
-  <si>
-    <t>Dados de pagamento salvos com sucesso</t>
-  </si>
-  <si>
-    <t>Dados de pagamento guardados com sucesso</t>
-  </si>
-  <si>
-    <t>Información de pago guardada correctamente</t>
-  </si>
-  <si>
-    <t>Informations de paiement enregistrées</t>
-  </si>
-  <si>
-    <t>Платёжные данные успешно сохранены</t>
-  </si>
-  <si>
-    <t>お支払い情報を保存しました</t>
-  </si>
-  <si>
-    <t>भुगतान की जानकारी सफलतापूर्वक सहेजी गई</t>
-  </si>
-  <si>
-    <t>level</t>
-  </si>
-  <si>
-    <t>Level {0}</t>
-  </si>
-  <si>
-    <t>Fase {0}</t>
-  </si>
-  <si>
-    <t>Nível {0}</t>
-  </si>
-  <si>
-    <t>Nivel {0}</t>
-  </si>
-  <si>
-    <t>Niveau {0}</t>
-  </si>
-  <si>
-    <t>Уровень {0}</t>
-  </si>
-  <si>
-    <t>ステージ{0}</t>
-  </si>
-  <si>
-    <t>स्तर {0}</t>
-  </si>
-  <si>
-    <t>LevelCompleteUIForm.complete</t>
-  </si>
-  <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
@@ -1393,9 +1399,6 @@
     <t>Cash Out</t>
   </si>
   <si>
-    <t>Sacar</t>
-  </si>
-  <si>
     <t>Levantar dinheiro</t>
   </si>
   <si>
@@ -1408,9 +1411,6 @@
     <t>Вывести деньги</t>
   </si>
   <si>
-    <t>出金</t>
-  </si>
-  <si>
     <t>पैसे निकालें</t>
   </si>
   <si>
@@ -1582,7 +1582,7 @@
     <t>Keys (do not edit)</t>
   </si>
   <si>
-    <t>cffce284a3ce44fbb78edede929b2f64</t>
+    <t>788988eed19b498ca46d59332918ad27</t>
   </si>
   <si>
     <t>请在 Translations 工作表填写译文；可以整行排序，不要单独排序某一列。</t>
@@ -2599,41 +2599,41 @@
       <c r="A23" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="B23" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="G23" s="2" t="s">
+      <c r="E23" s="1" t="s">
         <v>180</v>
       </c>
-      <c r="H23" s="2" t="s">
+      <c r="F23" s="1" t="s">
         <v>181</v>
       </c>
-      <c r="I23" s="2" t="s">
+      <c r="G23" s="1" t="s">
         <v>182</v>
       </c>
-      <c r="J23" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="2" t="s">
+      <c r="H23" s="1" t="s">
         <v>183</v>
       </c>
-      <c r="L23" s="2" t="s">
+      <c r="I23" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="J23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="1" t="s">
         <v>22</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
     </row>
     <row r="24">
@@ -3624,37 +3624,37 @@
       <c r="A48" s="1" t="s">
         <v>366</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>358</v>
-      </c>
-      <c r="C48" s="1" t="s">
+      <c r="B48" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L48" s="1" t="s">
+      <c r="J48" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="L48" s="2" t="s">
         <v>22</v>
       </c>
       <c r="M48" s="1" t="s">
@@ -3663,31 +3663,31 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="I49" s="1" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J49" s="1" t="s">
         <v>20</v>
@@ -3699,36 +3699,36 @@
         <v>22</v>
       </c>
       <c r="M49" s="1" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E50" s="1" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I50" s="1" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J50" s="1" t="s">
         <v>20</v>
@@ -3740,36 +3740,36 @@
         <v>205</v>
       </c>
       <c r="M50" s="1" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D51" s="1" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E51" s="1" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="I51" s="1" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="J51" s="1" t="s">
         <v>20</v>
@@ -3781,36 +3781,36 @@
         <v>205</v>
       </c>
       <c r="M51" s="1" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D52" s="1" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="J52" s="1" t="s">
         <v>20</v>
@@ -3822,36 +3822,36 @@
         <v>205</v>
       </c>
       <c r="M52" s="1" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="J53" s="1" t="s">
         <v>20</v>
@@ -3863,36 +3863,36 @@
         <v>22</v>
       </c>
       <c r="M53" s="1" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D54" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="I54" s="1" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J54" s="1" t="s">
         <v>20</v>
@@ -3904,36 +3904,36 @@
         <v>22</v>
       </c>
       <c r="M54" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="D55" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="I55" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J55" s="1" t="s">
         <v>20</v>
@@ -3945,36 +3945,36 @@
         <v>205</v>
       </c>
       <c r="M55" s="1" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="D56" s="1" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="I56" s="1" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="J56" s="1" t="s">
         <v>20</v>
@@ -3986,36 +3986,36 @@
         <v>205</v>
       </c>
       <c r="M56" s="1" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="D57" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E57" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="I57" s="1" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="J57" s="1" t="s">
         <v>20</v>
@@ -4027,36 +4027,36 @@
         <v>22</v>
       </c>
       <c r="M57" s="1" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="I58" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="J58" s="1" t="s">
         <v>20</v>
@@ -4068,33 +4068,33 @@
         <v>22</v>
       </c>
       <c r="M58" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>458</v>
+        <v>178</v>
       </c>
       <c r="D59" s="1" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H59" s="1" t="s">
-        <v>463</v>
+        <v>183</v>
       </c>
       <c r="I59" s="1" t="s">
         <v>464</v>
@@ -4109,7 +4109,7 @@
         <v>22</v>
       </c>
       <c r="M59" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
     </row>
     <row r="60">
@@ -4445,28 +4445,28 @@
         <v>516</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>20</v>
+        <v>452</v>
       </c>
       <c r="D68" s="1" t="s">
-        <v>20</v>
+        <v>452</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>20</v>
+        <v>453</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>20</v>
+        <v>454</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>20</v>
+        <v>455</v>
       </c>
       <c r="H68" s="1" t="s">
-        <v>20</v>
+        <v>456</v>
       </c>
       <c r="I68" s="1" t="s">
-        <v>20</v>
+        <v>457</v>
       </c>
       <c r="J68" s="1" t="s">
         <v>20</v>
@@ -4478,13 +4478,13 @@
         <v>22</v>
       </c>
       <c r="M68" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:L68"/>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K68" xr:uid="{DD473D72-5AF9-4B52-8B11-69264EA79921}">
+    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K68" xr:uid="{DE5B0CF3-6F57-4396-A63C-05C210810983}">
       <formula1>"正常,待复核,已复核,待清理"</formula1>
     </dataValidation>
   </dataValidations>
@@ -4761,57 +4761,57 @@
     </row>
     <row r="51">
       <c r="A51" s="0" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="0" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="0" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="0" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="0" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="0" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="0" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="0" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="0" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="0" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="0" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
     </row>
     <row r="62">

--- a/AAAGameData/Translations/Localization.xlsx
+++ b/AAAGameData/Translations/Localization.xlsx
@@ -17,7 +17,7 @@
     <sheet name="填写说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$79</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$81</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1120" uniqueCount="618">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="627">
   <si>
     <t>Key</t>
   </si>
@@ -1164,9 +1164,6 @@
     <t>पूरा हुआ</t>
   </si>
   <si>
-    <t>已复核</t>
-  </si>
-  <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
@@ -1854,6 +1851,36 @@
     <t>जाएँ</t>
   </si>
   <si>
+    <t>cashoutHint</t>
+  </si>
+  <si>
+    <t>You need to pass {0} levels and collect {1} Reaching Balance before you can claim it.</t>
+  </si>
+  <si>
+    <t>Você precisa concluir {0} fases e acumular um saldo de {1} para poder resgatar.</t>
+  </si>
+  <si>
+    <t>Tem de concluir {0} níveis e acumular um saldo de {1} para poder receber.</t>
+  </si>
+  <si>
+    <t>Debes superar {0} niveles y acumular un saldo de {1} para poder reclamarlo.</t>
+  </si>
+  <si>
+    <t>Vous devez terminer {0} niveaux et accumuler un solde de {1} pour pouvoir récupérer la récompense.</t>
+  </si>
+  <si>
+    <t>Чтобы получить награду, нужно пройти {0} уровней и накопить на балансе {1}.</t>
+  </si>
+  <si>
+    <t>{0}ステージをクリアし、残高が{1}に達すると受け取れます。</t>
+  </si>
+  <si>
+    <t>इसे प्राप्त करने के लिए आपको {0} स्तर पार करने होंगे और अपना बैलेंस {1} तक पहुँचाना होगा।</t>
+  </si>
+  <si>
+    <t>MakeupItem.cashout</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -1866,7 +1893,7 @@
     <t>Keys (do not edit)</t>
   </si>
   <si>
-    <t>85fd67377d944cc780e2b07d621f7f75</t>
+    <t>a6ea3b24b4734874afb97d430869d7a9</t>
   </si>
   <si>
     <t>请在 Translations 工作表填写译文；可以整行排序，不要单独排序某一列。</t>
@@ -3059,7 +3086,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M79"/>
+  <dimension ref="A1:M81"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" style="3" hidden="1" customWidth="1"/>
@@ -5029,42 +5056,42 @@
         <v>20</v>
       </c>
       <c r="K48" s="3" t="s">
-        <v>375</v>
+        <v>21</v>
       </c>
       <c r="L48" s="3" t="s">
         <v>22</v>
       </c>
       <c r="M48" s="3" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
     </row>
     <row r="49" ht="16.5" spans="1:13">
       <c r="A49" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B49" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="B49" s="3" t="s">
+      <c r="C49" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="D49" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="E49" s="3" t="s">
+      <c r="F49" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="F49" s="3" t="s">
+      <c r="G49" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="G49" s="3" t="s">
+      <c r="H49" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="H49" s="3" t="s">
+      <c r="I49" s="3" t="s">
         <v>383</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>384</v>
       </c>
       <c r="J49" s="3" t="s">
         <v>20</v>
@@ -5076,36 +5103,36 @@
         <v>22</v>
       </c>
       <c r="M49" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="50" ht="30" spans="1:13">
       <c r="A50" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B50" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B50" s="3" t="s">
+      <c r="C50" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="D50" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D50" s="3" t="s">
+      <c r="E50" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="E50" s="3" t="s">
+      <c r="F50" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="F50" s="3" t="s">
+      <c r="G50" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="G50" s="3" t="s">
+      <c r="H50" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="H50" s="3" t="s">
+      <c r="I50" s="3" t="s">
         <v>392</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>393</v>
       </c>
       <c r="J50" s="3" t="s">
         <v>20</v>
@@ -5117,36 +5144,36 @@
         <v>206</v>
       </c>
       <c r="M50" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="51" ht="49.5" spans="1:13">
       <c r="A51" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="B51" s="3" t="s">
+      <c r="C51" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="D51" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="D51" s="3" t="s">
+      <c r="E51" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="E51" s="3" t="s">
+      <c r="F51" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="F51" s="3" t="s">
+      <c r="G51" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="G51" s="3" t="s">
+      <c r="H51" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="H51" s="3" t="s">
+      <c r="I51" s="3" t="s">
         <v>401</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>402</v>
       </c>
       <c r="J51" s="3" t="s">
         <v>20</v>
@@ -5158,36 +5185,36 @@
         <v>206</v>
       </c>
       <c r="M51" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="52" ht="33" spans="1:13">
       <c r="A52" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B52" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B52" s="3" t="s">
+      <c r="C52" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="D52" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D52" s="3" t="s">
+      <c r="E52" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="E52" s="3" t="s">
+      <c r="F52" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="F52" s="3" t="s">
+      <c r="G52" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="G52" s="3" t="s">
+      <c r="H52" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="H52" s="3" t="s">
+      <c r="I52" s="3" t="s">
         <v>410</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>411</v>
       </c>
       <c r="J52" s="3" t="s">
         <v>20</v>
@@ -5199,36 +5226,36 @@
         <v>206</v>
       </c>
       <c r="M52" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="53" ht="16.5" spans="1:13">
       <c r="A53" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B53" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="B53" s="3" t="s">
+      <c r="C53" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="D53" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="D53" s="3" t="s">
+      <c r="E53" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="E53" s="3" t="s">
+      <c r="F53" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="F53" s="3" t="s">
+      <c r="G53" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="G53" s="3" t="s">
+      <c r="H53" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="H53" s="3" t="s">
+      <c r="I53" s="3" t="s">
         <v>419</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>420</v>
       </c>
       <c r="J53" s="3" t="s">
         <v>20</v>
@@ -5240,36 +5267,36 @@
         <v>22</v>
       </c>
       <c r="M53" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="54" ht="30" spans="1:13">
       <c r="A54" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="B54" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="C54" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="D54" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="D54" s="3" t="s">
+      <c r="E54" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="E54" s="3" t="s">
+      <c r="F54" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="F54" s="3" t="s">
+      <c r="G54" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="G54" s="3" t="s">
+      <c r="H54" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="H54" s="3" t="s">
+      <c r="I54" s="3" t="s">
         <v>428</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>429</v>
       </c>
       <c r="J54" s="3" t="s">
         <v>20</v>
@@ -5281,36 +5308,36 @@
         <v>22</v>
       </c>
       <c r="M54" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="55" ht="33" spans="1:13">
       <c r="A55" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="B55" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="C55" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="D55" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D55" s="3" t="s">
+      <c r="E55" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="E55" s="3" t="s">
+      <c r="F55" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="F55" s="3" t="s">
+      <c r="G55" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="G55" s="3" t="s">
+      <c r="H55" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="H55" s="3" t="s">
+      <c r="I55" s="3" t="s">
         <v>437</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>438</v>
       </c>
       <c r="J55" s="3" t="s">
         <v>20</v>
@@ -5322,36 +5349,36 @@
         <v>206</v>
       </c>
       <c r="M55" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="56" ht="33" spans="1:13">
       <c r="A56" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="B56" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="B56" s="3" t="s">
+      <c r="C56" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="D56" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="D56" s="3" t="s">
+      <c r="E56" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="E56" s="3" t="s">
+      <c r="F56" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="F56" s="3" t="s">
+      <c r="G56" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="G56" s="3" t="s">
+      <c r="H56" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="H56" s="3" t="s">
+      <c r="I56" s="3" t="s">
         <v>446</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>447</v>
       </c>
       <c r="J56" s="3" t="s">
         <v>20</v>
@@ -5363,36 +5390,36 @@
         <v>206</v>
       </c>
       <c r="M56" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="57" ht="16.5" spans="1:13">
       <c r="A57" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="B57" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="C57" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="D57" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="D57" s="3" t="s">
+      <c r="E57" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="E57" s="3" t="s">
+      <c r="F57" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="F57" s="3" t="s">
+      <c r="G57" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="G57" s="3" t="s">
+      <c r="H57" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="H57" s="3" t="s">
+      <c r="I57" s="3" t="s">
         <v>455</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>456</v>
       </c>
       <c r="J57" s="3" t="s">
         <v>20</v>
@@ -5404,36 +5431,36 @@
         <v>22</v>
       </c>
       <c r="M57" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="58" ht="16.5" spans="1:13">
       <c r="A58" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="D58" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E58" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="E58" s="3" t="s">
+      <c r="F58" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="F58" s="3" t="s">
+      <c r="G58" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="G58" s="3" t="s">
+      <c r="H58" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="H58" s="3" t="s">
+      <c r="I58" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="J58" s="3" t="s">
         <v>20</v>
@@ -5445,36 +5472,36 @@
         <v>22</v>
       </c>
       <c r="M58" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="59" ht="16.5" spans="1:13">
       <c r="A59" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="B59" s="3" t="s">
         <v>465</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>466</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>179</v>
       </c>
       <c r="D59" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="E59" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="E59" s="3" t="s">
+      <c r="F59" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="F59" s="3" t="s">
+      <c r="G59" s="3" t="s">
         <v>469</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>470</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>184</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="J59" s="3" t="s">
         <v>20</v>
@@ -5486,36 +5513,36 @@
         <v>22</v>
       </c>
       <c r="M59" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="60" ht="16.5" spans="1:13">
       <c r="A60" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="B60" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="C60" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="D60" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="F60" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="F60" s="3" t="s">
+      <c r="G60" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="G60" s="3" t="s">
+      <c r="H60" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="H60" s="3" t="s">
+      <c r="I60" s="3" t="s">
         <v>477</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>478</v>
       </c>
       <c r="J60" s="3" t="s">
         <v>20</v>
@@ -5527,36 +5554,36 @@
         <v>22</v>
       </c>
       <c r="M60" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="61" ht="45" spans="1:13">
       <c r="A61" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="B61" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="C61" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="D61" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="D61" s="3" t="s">
+      <c r="E61" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="E61" s="3" t="s">
+      <c r="F61" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="F61" s="3" t="s">
+      <c r="G61" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="G61" s="3" t="s">
+      <c r="H61" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="H61" s="3" t="s">
+      <c r="I61" s="3" t="s">
         <v>486</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>487</v>
       </c>
       <c r="J61" s="3" t="s">
         <v>20</v>
@@ -5568,36 +5595,36 @@
         <v>22</v>
       </c>
       <c r="M61" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="62" ht="33" spans="1:13">
       <c r="A62" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B62" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="C62" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="D62" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="E62" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="E62" s="3" t="s">
+      <c r="F62" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="F62" s="3" t="s">
+      <c r="G62" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="G62" s="3" t="s">
+      <c r="H62" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="H62" s="3" t="s">
+      <c r="I62" s="3" t="s">
         <v>494</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>495</v>
       </c>
       <c r="J62" s="3" t="s">
         <v>20</v>
@@ -5609,36 +5636,36 @@
         <v>22</v>
       </c>
       <c r="M62" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="63" ht="16.5" spans="1:13">
       <c r="A63" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="C63" s="3" t="s">
+      <c r="D63" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="E63" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="E63" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="F63" s="3" t="s">
+      <c r="G63" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="G63" s="3" t="s">
+      <c r="H63" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="H63" s="3" t="s">
+      <c r="I63" s="3" t="s">
         <v>502</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>503</v>
       </c>
       <c r="J63" s="3" t="s">
         <v>20</v>
@@ -5650,12 +5677,12 @@
         <v>22</v>
       </c>
       <c r="M63" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="64" ht="16.5" spans="1:13">
       <c r="A64" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>74</v>
@@ -5696,7 +5723,7 @@
     </row>
     <row r="65" ht="30" spans="1:13">
       <c r="A65" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>57</v>
@@ -5737,31 +5764,31 @@
     </row>
     <row r="66" ht="16.5" spans="1:13">
       <c r="A66" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B66" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="C66" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C66" s="3" t="s">
+      <c r="D66" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="E66" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E66" s="3" t="s">
+      <c r="F66" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="F66" s="3" t="s">
+      <c r="G66" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="G66" s="3" t="s">
+      <c r="H66" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="H66" s="3" t="s">
+      <c r="I66" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>513</v>
       </c>
       <c r="J66" s="3" t="s">
         <v>20</v>
@@ -5773,36 +5800,36 @@
         <v>22</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="67" ht="28.5" spans="1:13">
       <c r="A67" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="B67" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="C67" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="C67" s="3" t="s">
+      <c r="D67" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="D67" s="3" t="s">
+      <c r="E67" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="E67" s="3" t="s">
+      <c r="F67" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="F67" s="3" t="s">
+      <c r="G67" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="G67" s="3" t="s">
+      <c r="H67" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="H67" s="3" t="s">
+      <c r="I67" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="J67" s="3" t="s">
         <v>20</v>
@@ -5814,36 +5841,36 @@
         <v>22</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="68" ht="16.5" spans="1:13">
       <c r="A68" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B68" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="C68" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="C68" s="3" t="s">
+      <c r="D68" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="E68" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="E68" s="3" t="s">
+      <c r="F68" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="F68" s="3" t="s">
+      <c r="G68" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="G68" s="3" t="s">
+      <c r="H68" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="H68" s="3" t="s">
+      <c r="I68" s="3" t="s">
         <v>463</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>464</v>
       </c>
       <c r="J68" s="3" t="s">
         <v>20</v>
@@ -5855,36 +5882,36 @@
         <v>22</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="69" ht="16.5" spans="1:13">
       <c r="A69" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="B69" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="C69" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="C69" s="3" t="s">
+      <c r="D69" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="D69" s="3" t="s">
+      <c r="E69" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="F69" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="E69" s="3" t="s">
-        <v>527</v>
-      </c>
-      <c r="F69" s="3" t="s">
+      <c r="G69" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="G69" s="3" t="s">
+      <c r="H69" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="H69" s="3" t="s">
+      <c r="I69" s="3" t="s">
         <v>530</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>531</v>
       </c>
       <c r="J69" s="3" t="s">
         <v>20</v>
@@ -5896,36 +5923,36 @@
         <v>22</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="70" ht="16.5" spans="1:13">
       <c r="A70" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="B70" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="C70" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="C70" s="3" t="s">
+      <c r="D70" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="D70" s="3" t="s">
+      <c r="E70" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="E70" s="3" t="s">
+      <c r="F70" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="F70" s="3" t="s">
+      <c r="G70" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="G70" s="3" t="s">
+      <c r="H70" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="H70" s="3" t="s">
+      <c r="I70" s="3" t="s">
         <v>539</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>540</v>
       </c>
       <c r="J70" s="3" t="s">
         <v>20</v>
@@ -5937,36 +5964,36 @@
         <v>22</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="71" ht="16.5" spans="1:13">
       <c r="A71" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="B71" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="C71" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="C71" s="3" t="s">
+      <c r="D71" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="D71" s="3" t="s">
+      <c r="E71" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="E71" s="3" t="s">
+      <c r="F71" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="F71" s="3" t="s">
+      <c r="G71" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="G71" s="3" t="s">
+      <c r="H71" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="H71" s="3" t="s">
+      <c r="I71" s="3" t="s">
         <v>548</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>549</v>
       </c>
       <c r="J71" s="3" t="s">
         <v>20</v>
@@ -5978,36 +6005,36 @@
         <v>22</v>
       </c>
       <c r="M71" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="72" ht="16.5" spans="1:13">
       <c r="A72" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B72" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="C72" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="C72" s="3" t="s">
+      <c r="D72" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>508</v>
-      </c>
-      <c r="E72" s="3" t="s">
+      <c r="F72" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="F72" s="3" t="s">
+      <c r="G72" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="G72" s="3" t="s">
+      <c r="H72" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="H72" s="3" t="s">
+      <c r="I72" s="3" t="s">
         <v>512</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>513</v>
       </c>
       <c r="J72" s="3" t="s">
         <v>20</v>
@@ -6019,36 +6046,36 @@
         <v>22</v>
       </c>
       <c r="M72" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="73" ht="16.5" spans="1:13">
       <c r="A73" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="C73" s="3" t="s">
+      <c r="D73" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="E73" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="D73" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="E73" s="3" t="s">
+      <c r="F73" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="F73" s="3" t="s">
+      <c r="G73" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="G73" s="3" t="s">
+      <c r="H73" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="H73" s="3" t="s">
+      <c r="I73" s="3" t="s">
         <v>557</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>558</v>
       </c>
       <c r="J73" s="3" t="s">
         <v>20</v>
@@ -6060,21 +6087,21 @@
         <v>22</v>
       </c>
       <c r="M73" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="74" ht="16.5" spans="1:13">
       <c r="A74" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B74" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="C74" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="C74" s="3" t="s">
+      <c r="D74" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>562</v>
       </c>
       <c r="E74" s="3" t="s">
         <v>237</v>
@@ -6083,13 +6110,13 @@
         <v>238</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>240</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J74" s="3" t="s">
         <v>20</v>
@@ -6101,36 +6128,36 @@
         <v>22</v>
       </c>
       <c r="M74" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="75" ht="30" spans="1:13">
       <c r="A75" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="C75" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="D75" s="3" t="s">
+      <c r="E75" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="E75" s="3" t="s">
+      <c r="F75" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="F75" s="3" t="s">
+      <c r="G75" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="G75" s="3" t="s">
+      <c r="H75" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="H75" s="3" t="s">
+      <c r="I75" s="3" t="s">
         <v>572</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>573</v>
       </c>
       <c r="J75" s="3" t="s">
         <v>20</v>
@@ -6142,36 +6169,36 @@
         <v>22</v>
       </c>
       <c r="M75" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="76" ht="16.5" spans="1:13">
       <c r="A76" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="C76" s="3" t="s">
+      <c r="D76" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="E76" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="F76" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="E76" s="3" t="s">
-        <v>576</v>
-      </c>
-      <c r="F76" s="3" t="s">
+      <c r="G76" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="G76" s="3" t="s">
+      <c r="H76" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="H76" s="3" t="s">
+      <c r="I76" s="3" t="s">
         <v>579</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>580</v>
       </c>
       <c r="J76" s="3" t="s">
         <v>20</v>
@@ -6183,36 +6210,36 @@
         <v>22</v>
       </c>
       <c r="M76" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="77" ht="16.5" spans="1:13">
       <c r="A77" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="B77" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="B77" s="3" t="s">
+      <c r="C77" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="C77" s="3" t="s">
+      <c r="D77" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="D77" s="3" t="s">
+      <c r="E77" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="E77" s="3" t="s">
+      <c r="F77" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="F77" s="3" t="s">
+      <c r="G77" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="G77" s="3" t="s">
+      <c r="H77" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="H77" s="3" t="s">
+      <c r="I77" s="3" t="s">
         <v>588</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>589</v>
       </c>
       <c r="J77" s="3" t="s">
         <v>20</v>
@@ -6224,36 +6251,36 @@
         <v>22</v>
       </c>
       <c r="M77" s="3" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="78" ht="16.5" spans="1:13">
       <c r="A78" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="B78" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="B78" s="3" t="s">
+      <c r="C78" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="C78" s="3" t="s">
+      <c r="D78" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="E78" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>592</v>
-      </c>
-      <c r="E78" s="3" t="s">
+      <c r="F78" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="F78" s="3" t="s">
+      <c r="G78" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="G78" s="3" t="s">
+      <c r="H78" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="I78" s="3" t="s">
         <v>596</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>597</v>
       </c>
       <c r="J78" s="3" t="s">
         <v>20</v>
@@ -6265,36 +6292,36 @@
         <v>22</v>
       </c>
       <c r="M78" s="3" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
     </row>
     <row r="79" ht="16.5" spans="1:13">
       <c r="A79" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="B79" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="B79" s="3" t="s">
+      <c r="C79" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="C79" s="3" t="s">
+      <c r="D79" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="E79" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="F79" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>600</v>
-      </c>
-      <c r="F79" s="3" t="s">
+      <c r="G79" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="G79" s="3" t="s">
+      <c r="H79" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="I79" s="3" t="s">
         <v>603</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>604</v>
       </c>
       <c r="J79" s="3" t="s">
         <v>20</v>
@@ -6306,15 +6333,97 @@
         <v>22</v>
       </c>
       <c r="M79" s="3" t="s">
-        <v>599</v>
+        <v>598</v>
+      </c>
+    </row>
+    <row r="80" ht="60" spans="1:13">
+      <c r="A80" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="B80" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="C80" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="E80" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="H80" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="J80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L80" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M80" s="3" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="81" ht="16.5" spans="1:13">
+      <c r="A81" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C81" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H81" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="J81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L81" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M81" s="3" t="s">
+        <v>178</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L79" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L81" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K79">
+    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K81">
       <formula1>"正常,待复核,已复核,待清理"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6326,12 +6435,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C81"/>
+  <dimension ref="A1:C83"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>605</v>
+        <v>614</v>
       </c>
       <c r="B1" t="s">
         <v>206</v>
@@ -6339,21 +6448,21 @@
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>606</v>
+        <v>615</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>607</v>
+        <v>616</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>608</v>
+        <v>617</v>
       </c>
       <c r="B3" t="s">
-        <v>609</v>
+        <v>618</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -6593,157 +6702,167 @@
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="73" spans="1:1">
       <c r="A73" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="74" spans="1:1">
       <c r="A74" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="75" spans="1:1">
       <c r="A75" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="76" spans="1:1">
       <c r="A76" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
     </row>
     <row r="77" spans="1:1">
       <c r="A77" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="78" spans="1:1">
       <c r="A78" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="79" spans="1:1">
       <c r="A79" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="80" spans="1:1">
       <c r="A80" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
     </row>
     <row r="81" spans="1:1">
       <c r="A81" t="s">
-        <v>598</v>
+        <v>597</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>613</v>
       </c>
     </row>
   </sheetData>
@@ -6764,42 +6883,42 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>610</v>
+        <v>619</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>611</v>
+        <v>620</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>612</v>
+        <v>621</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>613</v>
+        <v>622</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>614</v>
+        <v>623</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>615</v>
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>616</v>
+        <v>625</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>617</v>
+        <v>626</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Translations/Localization.xlsx
+++ b/AAAGameData/Translations/Localization.xlsx
@@ -10,14 +10,14 @@
     <sheet name="填写说明" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$82</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$83</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
   <si>
     <t>Key</t>
   </si>
@@ -1873,6 +1873,12 @@
     <t>Clear every item before you run out of shots!</t>
   </si>
   <si>
+    <t>MakeupRecordItem.bouns</t>
+  </si>
+  <si>
+    <t>Today`s Bonus Pool</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -1885,7 +1891,7 @@
     <t>Keys (do not edit)</t>
   </si>
   <si>
-    <t>42153bfe15934310a6fcba4a81d150b8</t>
+    <t>b87c000551a842a2814af27e31fe80e9</t>
   </si>
   <si>
     <t>请在 Translations 工作表填写译文；可以整行排序，不要单独排序某一列。</t>
@@ -1977,7 +1983,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable=" xr">
-  <dimension ref="A1:M82"/>
+  <dimension ref="A1:M83"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" hidden="1" width="28" customWidth="1" style="1"/>
@@ -5352,16 +5358,57 @@
         <v>21</v>
       </c>
       <c r="L82" s="1" t="s">
-        <v>22</v>
+        <v>206</v>
       </c>
       <c r="M82" s="1" t="s">
         <v>617</v>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>618</v>
+      </c>
+      <c r="B83" s="1" t="s">
+        <v>619</v>
+      </c>
+      <c r="C83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J83" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L83" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M83" s="1" t="s">
+        <v>619</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L82"/>
+  <autoFilter ref="A1:L83"/>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K82" xr:uid="{66D05500-0732-48A6-B9A3-FC9A14703C64}">
+    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K83" xr:uid="{98B78E26-0FF8-4F21-B6F6-05043C0233F3}">
       <formula1>"正常,待复核,已复核,待清理"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5371,12 +5418,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C85"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="B1" s="0" t="s">
         <v>206</v>
@@ -5384,21 +5431,21 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="4">
@@ -5804,6 +5851,11 @@
     <row r="84">
       <c r="A84" s="0" t="s">
         <v>616</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="0" t="s">
+        <v>618</v>
       </c>
     </row>
   </sheetData>
@@ -5822,42 +5874,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Translations/Localization.xlsx
+++ b/AAAGameData/Translations/Localization.xlsx
@@ -10,14 +10,14 @@
     <sheet name="填写说明" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$83</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$84</definedName>
   </definedNames>
   <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="633" uniqueCount="633">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="635">
   <si>
     <t>Key</t>
   </si>
@@ -1879,6 +1879,12 @@
     <t>Today`s Bonus Pool</t>
   </si>
   <si>
+    <t>PlayUIForm.txtHint</t>
+  </si>
+  <si>
+    <t>Tap the items on the table</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -1891,7 +1897,7 @@
     <t>Keys (do not edit)</t>
   </si>
   <si>
-    <t>b87c000551a842a2814af27e31fe80e9</t>
+    <t>f247a98793ac46feb7823f09d62bf6ba</t>
   </si>
   <si>
     <t>请在 Translations 工作表填写译文；可以整行排序，不要单独排序某一列。</t>
@@ -1983,7 +1989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable=" xr">
-  <dimension ref="A1:M83"/>
+  <dimension ref="A1:M84"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" hidden="1" width="28" customWidth="1" style="1"/>
@@ -5405,10 +5411,51 @@
         <v>619</v>
       </c>
     </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>620</v>
+      </c>
+      <c r="B84" s="1" t="s">
+        <v>621</v>
+      </c>
+      <c r="C84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="J84" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="L84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>621</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L83"/>
+  <autoFilter ref="A1:L84"/>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K83" xr:uid="{98B78E26-0FF8-4F21-B6F6-05043C0233F3}">
+    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K84" xr:uid="{8DABD7B3-D640-48FF-A348-40544460443A}">
       <formula1>"正常,待复核,已复核,待清理"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5418,12 +5465,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C86"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="0" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B1" s="0" t="s">
         <v>206</v>
@@ -5431,21 +5478,21 @@
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="B2" s="0" t="s">
         <v>1</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
     </row>
     <row r="4">
@@ -5856,6 +5903,11 @@
     <row r="85">
       <c r="A85" s="0" t="s">
         <v>618</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="0" t="s">
+        <v>620</v>
       </c>
     </row>
   </sheetData>
@@ -5874,42 +5926,42 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="4" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
     </row>
   </sheetData>

--- a/AAAGameData/Translations/Localization.xlsx
+++ b/AAAGameData/Translations/Localization.xlsx
@@ -1,23 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\Translations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
-    <sheet name="_Metadata" sheetId="2" r:id="rId3" state="veryHidden"/>
-    <sheet name="填写说明" sheetId="3" r:id="rId4"/>
+    <sheet name="_Metadata" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet name="填写说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$84</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$87</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1232" uniqueCount="681">
   <si>
     <t>Key</t>
   </si>
@@ -751,25 +771,25 @@
     <t>Tap that item and let the cannon fly!</t>
   </si>
   <si>
-    <t>Toque para mover</t>
-  </si>
-  <si>
-    <t>Toca para mover</t>
-  </si>
-  <si>
-    <t>Touchez pour déplacer</t>
-  </si>
-  <si>
-    <t>Нажмите, чтобы переместить</t>
-  </si>
-  <si>
-    <t>タップして移動</t>
-  </si>
-  <si>
-    <t>हिलाने के लिए टैप करें</t>
-  </si>
-  <si>
-    <t>待复核</t>
+    <t>Toque nesse objeto e dispare o canhão!</t>
+  </si>
+  <si>
+    <t>¡Toca ese objeto y dispara el cañón!</t>
+  </si>
+  <si>
+    <t>Touchez cet objet et faites feu avec le canon !</t>
+  </si>
+  <si>
+    <t>Нажмите на этот предмет и стреляйте из пушки!</t>
+  </si>
+  <si>
+    <t>そのアイテムをタップして大砲を撃とう！</t>
+  </si>
+  <si>
+    <t>उस वस्तु पर टैप करें और तोप चलाएँ!</t>
+  </si>
+  <si>
+    <t>已复核</t>
   </si>
   <si>
     <t>Tap to Move</t>
@@ -1873,18 +1893,156 @@
     <t>Clear every item before you run out of shots!</t>
   </si>
   <si>
+    <t>Elimine todos os objetos antes que os disparos acabem!</t>
+  </si>
+  <si>
+    <t>Elimine todos os objetos antes de ficar sem disparos!</t>
+  </si>
+  <si>
+    <t>¡Elimina todos los objetos antes de quedarte sin disparos!</t>
+  </si>
+  <si>
+    <t>Éliminez tous les objets avant de manquer de tirs !</t>
+  </si>
+  <si>
+    <t>Уберите все предметы, пока не закончились выстрелы!</t>
+  </si>
+  <si>
+    <t>弾がなくなる前にすべてのアイテムを消そう！</t>
+  </si>
+  <si>
+    <t>गोले खत्म होने से पहले सभी वस्तुएँ हटाएँ!</t>
+  </si>
+  <si>
     <t>MakeupRecordItem.bouns</t>
   </si>
   <si>
     <t>Today`s Bonus Pool</t>
   </si>
   <si>
+    <t>Prêmio total de hoje</t>
+  </si>
+  <si>
+    <t>Prémio total de hoje</t>
+  </si>
+  <si>
+    <t>Premio total de hoy</t>
+  </si>
+  <si>
+    <t>Cagnotte du jour</t>
+  </si>
+  <si>
+    <t>Призовой фонд на сегодня</t>
+  </si>
+  <si>
+    <t>本日の賞金総額</t>
+  </si>
+  <si>
+    <t>आज की कुल पुरस्कार राशि</t>
+  </si>
+  <si>
     <t>PlayUIForm.txtHint</t>
   </si>
   <si>
     <t>Tap the items on the table</t>
   </si>
   <si>
+    <t>Toque nos objetos sobre a mesa</t>
+  </si>
+  <si>
+    <t>Toque nos objetos em cima da mesa</t>
+  </si>
+  <si>
+    <t>Toca los objetos de la mesa</t>
+  </si>
+  <si>
+    <t>Touchez les objets sur la table</t>
+  </si>
+  <si>
+    <t>Нажимайте на предметы на столе</t>
+  </si>
+  <si>
+    <t>テーブルの上のアイテムをタップ</t>
+  </si>
+  <si>
+    <t>मेज़ पर रखी वस्तुओं पर टैप करें</t>
+  </si>
+  <si>
+    <t>MakeupItem.reach</t>
+  </si>
+  <si>
+    <t>Reaching Balance</t>
+  </si>
+  <si>
+    <t>Saldo necessário</t>
+  </si>
+  <si>
+    <t>Saldo necesario</t>
+  </si>
+  <si>
+    <t>Solde requis</t>
+  </si>
+  <si>
+    <t>Необходимый баланс</t>
+  </si>
+  <si>
+    <t>必要残高</t>
+  </si>
+  <si>
+    <t>आवश्यक बैलेंस</t>
+  </si>
+  <si>
+    <t>PrelevelUIForm.desc</t>
+  </si>
+  <si>
+    <t>Select Booster:</t>
+  </si>
+  <si>
+    <t>Selecione um reforço:</t>
+  </si>
+  <si>
+    <t>Selecciona un potenciador:</t>
+  </si>
+  <si>
+    <t>Sélectionnez un bonus :</t>
+  </si>
+  <si>
+    <t>Выберите усилитель:</t>
+  </si>
+  <si>
+    <t>ブースターを選択：</t>
+  </si>
+  <si>
+    <t>बूस्टर चुनें:</t>
+  </si>
+  <si>
+    <t>MakeupPaymentEndUIForm.desc</t>
+  </si>
+  <si>
+    <t>Thank you for your generous donation!</t>
+  </si>
+  <si>
+    <t>Agradecemos sua generosa doação!</t>
+  </si>
+  <si>
+    <t>Agradecemos a sua generosa doação!</t>
+  </si>
+  <si>
+    <t>¡Gracias por tu generosa donación!</t>
+  </si>
+  <si>
+    <t>Merci pour votre généreux don !</t>
+  </si>
+  <si>
+    <t>Спасибо за ваше щедрое пожертвование!</t>
+  </si>
+  <si>
+    <t>温かいご寄付をありがとうございます！</t>
+  </si>
+  <si>
+    <t>आपके उदार दान के लिए धन्यवाद!</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -1897,7 +2055,7 @@
     <t>Keys (do not edit)</t>
   </si>
   <si>
-    <t>f247a98793ac46feb7823f09d62bf6ba</t>
+    <t>c699ba1653ca43adb52ee977f6207ca1</t>
   </si>
   <si>
     <t>请在 Translations 工作表填写译文；可以整行排序，不要单独排序某一列。</t>
@@ -1927,20 +2085,178 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1949,11 +2265,192 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFE0" tint="0"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1961,4010 +2458,4909 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" xfId="0" applyAlignment="1">
+  <cellXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" fillId="2" applyFill="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable=" xr">
-  <dimension ref="A1:M84"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M87"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" hidden="1" width="28" customWidth="1" style="1"/>
-    <col min="2" max="2" width="28" customWidth="1" style="1"/>
-    <col min="3" max="3" width="28" customWidth="1" style="1"/>
-    <col min="4" max="4" width="28" customWidth="1" style="1"/>
-    <col min="5" max="5" width="28" customWidth="1" style="1"/>
-    <col min="6" max="6" width="28" customWidth="1" style="1"/>
-    <col min="7" max="7" width="28" customWidth="1" style="1"/>
-    <col min="8" max="8" width="28" customWidth="1" style="1"/>
-    <col min="9" max="9" width="28" customWidth="1" style="1"/>
-    <col min="10" max="10" width="28" customWidth="1" style="1"/>
-    <col min="11" max="11" width="12" customWidth="1" style="1"/>
-    <col min="12" max="12" width="8" customWidth="1" style="1"/>
-    <col min="13" max="13" hidden="1" width="28" customWidth="1" style="1"/>
-    <col min="14" max="16384" width="9.140625" customWidth="1" style="1"/>
+    <col min="1" max="1" width="28" style="3" hidden="1" customWidth="1"/>
+    <col min="2" max="10" width="28" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8" style="3" customWidth="1"/>
+    <col min="13" max="13" width="28" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.14285714285714" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="3" customFormat="1">
-      <c r="A1" s="3" t="s">
+    <row r="1" s="2" customFormat="1" spans="1:13">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="16.5" spans="1:13">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1" t="s">
+      <c r="J2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="16.5" spans="1:13">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1" t="s">
+      <c r="J3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="33" spans="1:13">
+      <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="1" t="s">
+      <c r="J4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L4" s="1" t="s">
+      <c r="L4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="16.5" spans="1:13">
+      <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="3" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+    <row r="6" ht="30" spans="1:13">
+      <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+    <row r="7" ht="30" spans="1:13">
+      <c r="A7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="J7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L7" s="1" t="s">
+      <c r="L7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="30" spans="1:13">
+      <c r="A8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="1" t="s">
+      <c r="J8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L8" s="1" t="s">
+      <c r="L8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
+    <row r="9" ht="30" spans="1:13">
+      <c r="A9" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="1" t="s">
+      <c r="J9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L9" s="1" t="s">
+      <c r="L9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+    <row r="10" ht="30" spans="1:13">
+      <c r="A10" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="1" t="s">
+      <c r="J10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="3" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="30" spans="1:13">
+      <c r="A11" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="1" t="s">
+      <c r="J11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="3" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
+    <row r="12" ht="30" spans="1:13">
+      <c r="A12" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="1" t="s">
+      <c r="J12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="3" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
+    <row r="13" ht="16.5" spans="1:13">
+      <c r="A13" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="1" t="s">
+      <c r="J13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+    <row r="14" ht="16.5" spans="1:13">
+      <c r="A14" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="1" t="s">
+      <c r="J14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="3" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
+    <row r="15" ht="16.5" spans="1:13">
+      <c r="A15" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" s="3" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
+    <row r="16" ht="16.5" spans="1:13">
+      <c r="A16" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="1" t="s">
+      <c r="J16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+    <row r="17" ht="16.5" spans="1:13">
+      <c r="A17" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="1" t="s">
+      <c r="J17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
+    <row r="18" ht="30" spans="1:13">
+      <c r="A18" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K18" s="1" t="s">
+      <c r="J18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L18" s="1" t="s">
+      <c r="L18" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="M18" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
+    <row r="19" ht="16.5" spans="1:13">
+      <c r="A19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="1" t="s">
+      <c r="J19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L19" s="1" t="s">
+      <c r="L19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="M19" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
+    <row r="20" ht="16.5" spans="1:13">
+      <c r="A20" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="1" t="s">
+      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L20" s="1" t="s">
+      <c r="L20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="M20" s="3" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
+    <row r="21" ht="16.5" spans="1:13">
+      <c r="A21" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="1" t="s">
+      <c r="J21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L21" s="1" t="s">
+      <c r="L21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="3" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="s">
+    <row r="22" ht="16.5" spans="1:13">
+      <c r="A22" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="1" t="s">
+      <c r="J22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="1" t="s">
+      <c r="L22" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" s="3" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="s">
+    <row r="23" ht="16.5" spans="1:13">
+      <c r="A23" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="1" t="s">
+      <c r="J23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L23" s="1" t="s">
+      <c r="L23" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="M23" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="s">
+    <row r="24" ht="45" spans="1:13">
+      <c r="A24" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" s="1" t="s">
+      <c r="J24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L24" s="1" t="s">
+      <c r="L24" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="M24" s="3" t="s">
         <v>187</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
+    <row r="25" ht="16.5" spans="1:13">
+      <c r="A25" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="1" t="s">
+      <c r="J25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L25" s="1" t="s">
+      <c r="L25" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M25" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="s">
+    <row r="26" ht="16.5" spans="1:13">
+      <c r="A26" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="1" t="s">
+      <c r="J26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L26" s="1" t="s">
+      <c r="L26" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="M26" s="3" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="s">
+    <row r="27" ht="16.5" spans="1:13">
+      <c r="A27" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="1" t="s">
+      <c r="J27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L27" s="1" t="s">
+      <c r="L27" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="M27" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
+    <row r="28" ht="16.5" spans="1:13">
+      <c r="A28" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="1" t="s">
+      <c r="J28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L28" s="1" t="s">
+      <c r="L28" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="M28" s="3" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="s">
+    <row r="29" ht="30" spans="1:13">
+      <c r="A29" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="1" t="s">
+      <c r="J29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L29" s="1" t="s">
+      <c r="L29" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="M29" s="3" t="s">
         <v>217</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="s">
+    <row r="30" ht="16.5" spans="1:13">
+      <c r="A30" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="1" t="s">
+      <c r="J30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L30" s="1" t="s">
+      <c r="L30" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="M30" s="3" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="s">
+    <row r="31" ht="16.5" spans="1:13">
+      <c r="A31" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="1" t="s">
+      <c r="J31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L31" s="1" t="s">
+      <c r="L31" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="M31" s="3" t="s">
         <v>234</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="s">
+    <row r="32" ht="33" spans="1:13">
+      <c r="A32" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="B32" s="2" t="s">
+      <c r="B32" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F32" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="G32" s="2" t="s">
+      <c r="G32" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="H32" s="2" t="s">
+      <c r="H32" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="I32" s="2" t="s">
+      <c r="I32" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="J32" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="2" t="s">
+      <c r="J32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="L32" s="2" t="s">
+      <c r="L32" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="M32" s="3" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="s">
+    <row r="33" ht="30" spans="1:13">
+      <c r="A33" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="1" t="s">
+      <c r="J33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L33" s="1" t="s">
+      <c r="L33" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="M33" s="3" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="s">
+    <row r="34" ht="30" spans="1:13">
+      <c r="A34" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="1" t="s">
+      <c r="J34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L34" s="1" t="s">
+      <c r="L34" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="M34" s="3" t="s">
         <v>262</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="s">
+    <row r="35" ht="30" spans="1:13">
+      <c r="A35" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="1" t="s">
+      <c r="J35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L35" s="1" t="s">
+      <c r="L35" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="M35" s="3" t="s">
         <v>270</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="s">
+    <row r="36" ht="30" spans="1:13">
+      <c r="A36" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="1" t="s">
+      <c r="J36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L36" s="1" t="s">
+      <c r="L36" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="M36" s="3" t="s">
         <v>279</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="s">
+    <row r="37" ht="16.5" spans="1:13">
+      <c r="A37" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="1" t="s">
+      <c r="J37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L37" s="1" t="s">
+      <c r="L37" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M37" s="1" t="s">
+      <c r="M37" s="3" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="s">
+    <row r="38" ht="16.5" spans="1:13">
+      <c r="A38" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="1" t="s">
+      <c r="J38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L38" s="1" t="s">
+      <c r="L38" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="M38" s="3" t="s">
         <v>289</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="s">
+    <row r="39" ht="16.5" spans="1:13">
+      <c r="A39" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="1" t="s">
+      <c r="J39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L39" s="1" t="s">
+      <c r="L39" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M39" s="1" t="s">
+      <c r="M39" s="3" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="s">
+    <row r="40" ht="30" spans="1:13">
+      <c r="A40" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="1" t="s">
+      <c r="J40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L40" s="1" t="s">
+      <c r="L40" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="M40" s="3" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="s">
+    <row r="41" ht="28.5" spans="1:13">
+      <c r="A41" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="1" t="s">
+      <c r="J41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L41" s="1" t="s">
+      <c r="L41" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="M41" s="3" t="s">
         <v>308</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="s">
+    <row r="42" ht="45" spans="1:13">
+      <c r="A42" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="1" t="s">
+      <c r="J42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L42" s="1" t="s">
+      <c r="L42" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M42" s="1" t="s">
+      <c r="M42" s="3" t="s">
         <v>317</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="s">
+    <row r="43" ht="30" spans="1:13">
+      <c r="A43" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="1" t="s">
+      <c r="J43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L43" s="1" t="s">
+      <c r="L43" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="M43" s="3" t="s">
         <v>326</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="s">
+    <row r="44" ht="30" spans="1:13">
+      <c r="A44" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="1" t="s">
+      <c r="J44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L44" s="1" t="s">
+      <c r="L44" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M44" s="1" t="s">
+      <c r="M44" s="3" t="s">
         <v>334</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="s">
+    <row r="45" ht="30" spans="1:13">
+      <c r="A45" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="1" t="s">
+      <c r="J45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L45" s="1" t="s">
+      <c r="L45" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="M45" s="3" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="s">
+    <row r="46" ht="33" spans="1:13">
+      <c r="A46" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="1" t="s">
+      <c r="J46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L46" s="1" t="s">
+      <c r="L46" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M46" s="1" t="s">
+      <c r="M46" s="3" t="s">
         <v>352</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="s">
+    <row r="47" ht="16.5" spans="1:13">
+      <c r="A47" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="1" t="s">
+      <c r="J47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L47" s="1" t="s">
+      <c r="L47" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="M47" s="3" t="s">
         <v>361</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="s">
+    <row r="48" ht="30" spans="1:13">
+      <c r="A48" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="1" t="s">
+      <c r="J48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L48" s="1" t="s">
+      <c r="L48" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="1" t="s">
+      <c r="M48" s="3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="s">
+    <row r="49" ht="16.5" spans="1:13">
+      <c r="A49" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="1" t="s">
+      <c r="J49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L49" s="1" t="s">
+      <c r="L49" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="M49" s="3" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="s">
+    <row r="50" ht="30" spans="1:13">
+      <c r="A50" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K50" s="1" t="s">
+      <c r="J50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L50" s="1" t="s">
+      <c r="L50" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M50" s="1" t="s">
+      <c r="M50" s="3" t="s">
         <v>387</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="s">
+    <row r="51" ht="49.5" spans="1:13">
+      <c r="A51" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K51" s="1" t="s">
+      <c r="J51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L51" s="1" t="s">
+      <c r="L51" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="M51" s="3" t="s">
         <v>396</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="s">
+    <row r="52" ht="33" spans="1:13">
+      <c r="A52" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H52" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K52" s="1" t="s">
+      <c r="J52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L52" s="1" t="s">
+      <c r="L52" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="M52" s="3" t="s">
         <v>405</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="s">
+    <row r="53" ht="16.5" spans="1:13">
+      <c r="A53" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="1" t="s">
+      <c r="J53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L53" s="1" t="s">
+      <c r="L53" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M53" s="1" t="s">
+      <c r="M53" s="3" t="s">
         <v>414</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="s">
+    <row r="54" ht="30" spans="1:13">
+      <c r="A54" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H54" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="1" t="s">
+      <c r="J54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L54" s="1" t="s">
+      <c r="L54" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M54" s="3" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="s">
+    <row r="55" ht="33" spans="1:13">
+      <c r="A55" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K55" s="1" t="s">
+      <c r="J55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L55" s="1" t="s">
+      <c r="L55" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="M55" s="3" t="s">
         <v>432</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="s">
+    <row r="56" ht="33" spans="1:13">
+      <c r="A56" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="1" t="s">
+      <c r="J56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L56" s="1" t="s">
+      <c r="L56" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M56" s="3" t="s">
         <v>441</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="s">
+    <row r="57" ht="16.5" spans="1:13">
+      <c r="A57" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="1" t="s">
+      <c r="J57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L57" s="1" t="s">
+      <c r="L57" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M57" s="3" t="s">
         <v>450</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="s">
+    <row r="58" ht="16.5" spans="1:13">
+      <c r="A58" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="1" t="s">
+      <c r="J58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L58" s="1" t="s">
+      <c r="L58" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="M58" s="3" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="s">
+    <row r="59" ht="16.5" spans="1:13">
+      <c r="A59" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K59" s="1" t="s">
+      <c r="J59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L59" s="1" t="s">
+      <c r="L59" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="M59" s="3" t="s">
         <v>467</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="s">
+    <row r="60" ht="16.5" spans="1:13">
+      <c r="A60" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K60" s="1" t="s">
+      <c r="J60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K60" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L60" s="1" t="s">
+      <c r="L60" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M60" s="3" t="s">
         <v>474</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="s">
+    <row r="61" ht="45" spans="1:13">
+      <c r="A61" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G61" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K61" s="1" t="s">
+      <c r="J61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L61" s="1" t="s">
+      <c r="L61" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="M61" s="3" t="s">
         <v>481</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="s">
+    <row r="62" ht="33" spans="1:13">
+      <c r="A62" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G62" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I62" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K62" s="1" t="s">
+      <c r="J62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L62" s="1" t="s">
+      <c r="L62" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="M62" s="3" t="s">
         <v>490</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="s">
+    <row r="63" ht="16.5" spans="1:13">
+      <c r="A63" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G63" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="I63" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K63" s="1" t="s">
+      <c r="J63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L63" s="1" t="s">
+      <c r="L63" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="M63" s="3" t="s">
         <v>498</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="s">
+    <row r="64" ht="16.5" spans="1:13">
+      <c r="A64" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="H64" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="I64" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K64" s="1" t="s">
+      <c r="J64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L64" s="1" t="s">
+      <c r="L64" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M64" s="1" t="s">
+      <c r="M64" s="3" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="s">
+    <row r="65" ht="30" spans="1:13">
+      <c r="A65" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="I65" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K65" s="1" t="s">
+      <c r="J65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L65" s="1" t="s">
+      <c r="L65" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M65" s="1" t="s">
+      <c r="M65" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="s">
+    <row r="66" ht="16.5" spans="1:13">
+      <c r="A66" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="I66" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K66" s="1" t="s">
+      <c r="J66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L66" s="1" t="s">
+      <c r="L66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M66" s="1" t="s">
+      <c r="M66" s="3" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="s">
+    <row r="67" ht="28.5" spans="1:13">
+      <c r="A67" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I67" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="J67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K67" s="1" t="s">
+      <c r="J67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L67" s="1" t="s">
+      <c r="L67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M67" s="1" t="s">
+      <c r="M67" s="3" t="s">
         <v>516</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="1" t="s">
+    <row r="68" ht="16.5" spans="1:13">
+      <c r="A68" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K68" s="1" t="s">
+      <c r="J68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L68" s="1" t="s">
+      <c r="L68" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="M68" s="3" t="s">
         <v>459</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="s">
+    <row r="69" ht="16.5" spans="1:13">
+      <c r="A69" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="G69" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H69" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="I69" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K69" s="1" t="s">
+      <c r="J69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L69" s="1" t="s">
+      <c r="L69" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="M69" s="3" t="s">
         <v>526</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="1" t="s">
+    <row r="70" ht="16.5" spans="1:13">
+      <c r="A70" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="B70" s="1" t="s">
+      <c r="B70" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="C70" s="1" t="s">
+      <c r="C70" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="E70" s="1" t="s">
+      <c r="E70" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="G70" s="1" t="s">
+      <c r="G70" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="H70" s="1" t="s">
+      <c r="H70" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="I70" s="1" t="s">
+      <c r="I70" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="J70" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K70" s="1" t="s">
+      <c r="J70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L70" s="1" t="s">
+      <c r="L70" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M70" s="1" t="s">
+      <c r="M70" s="3" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="1" t="s">
+    <row r="71" ht="16.5" spans="1:13">
+      <c r="A71" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="B71" s="1" t="s">
+      <c r="B71" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="C71" s="1" t="s">
+      <c r="C71" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="E71" s="1" t="s">
+      <c r="E71" s="3" t="s">
         <v>546</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="3" t="s">
         <v>547</v>
       </c>
-      <c r="G71" s="1" t="s">
+      <c r="G71" s="3" t="s">
         <v>548</v>
       </c>
-      <c r="H71" s="1" t="s">
+      <c r="H71" s="3" t="s">
         <v>549</v>
       </c>
-      <c r="I71" s="1" t="s">
+      <c r="I71" s="3" t="s">
         <v>550</v>
       </c>
-      <c r="J71" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K71" s="1" t="s">
+      <c r="J71" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K71" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L71" s="1" t="s">
+      <c r="L71" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M71" s="1" t="s">
+      <c r="M71" s="3" t="s">
         <v>543</v>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="1" t="s">
+    <row r="72" ht="16.5" spans="1:13">
+      <c r="A72" s="3" t="s">
         <v>551</v>
       </c>
-      <c r="B72" s="1" t="s">
+      <c r="B72" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="C72" s="1" t="s">
+      <c r="C72" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="E72" s="1" t="s">
+      <c r="E72" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="F72" s="1" t="s">
+      <c r="F72" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="G72" s="1" t="s">
+      <c r="G72" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="H72" s="1" t="s">
+      <c r="H72" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="I72" s="1" t="s">
+      <c r="I72" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="J72" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K72" s="1" t="s">
+      <c r="J72" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K72" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L72" s="1" t="s">
+      <c r="L72" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M72" s="1" t="s">
+      <c r="M72" s="3" t="s">
         <v>508</v>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="1" t="s">
+    <row r="73" ht="16.5" spans="1:13">
+      <c r="A73" s="3" t="s">
         <v>552</v>
       </c>
-      <c r="B73" s="1" t="s">
+      <c r="B73" s="3" t="s">
         <v>553</v>
       </c>
-      <c r="C73" s="1" t="s">
+      <c r="C73" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="3" t="s">
         <v>554</v>
       </c>
-      <c r="E73" s="1" t="s">
+      <c r="E73" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="F73" s="1" t="s">
+      <c r="F73" s="3" t="s">
         <v>556</v>
       </c>
-      <c r="G73" s="1" t="s">
+      <c r="G73" s="3" t="s">
         <v>557</v>
       </c>
-      <c r="H73" s="1" t="s">
+      <c r="H73" s="3" t="s">
         <v>558</v>
       </c>
-      <c r="I73" s="1" t="s">
+      <c r="I73" s="3" t="s">
         <v>559</v>
       </c>
-      <c r="J73" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K73" s="1" t="s">
+      <c r="J73" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K73" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L73" s="1" t="s">
+      <c r="L73" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M73" s="1" t="s">
+      <c r="M73" s="3" t="s">
         <v>553</v>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="1" t="s">
+    <row r="74" ht="16.5" spans="1:13">
+      <c r="A74" s="3" t="s">
         <v>560</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B74" s="3" t="s">
         <v>561</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="3" t="s">
         <v>562</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="3" t="s">
         <v>563</v>
       </c>
-      <c r="E74" s="1" t="s">
+      <c r="E74" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="G74" s="1" t="s">
+      <c r="G74" s="3" t="s">
         <v>564</v>
       </c>
-      <c r="H74" s="1" t="s">
+      <c r="H74" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="I74" s="1" t="s">
+      <c r="I74" s="3" t="s">
         <v>565</v>
       </c>
-      <c r="J74" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K74" s="1" t="s">
+      <c r="J74" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K74" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L74" s="1" t="s">
+      <c r="L74" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M74" s="1" t="s">
+      <c r="M74" s="3" t="s">
         <v>561</v>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="1" t="s">
+    <row r="75" ht="30" spans="1:13">
+      <c r="A75" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="B75" s="1" t="s">
+      <c r="B75" s="3" t="s">
         <v>567</v>
       </c>
-      <c r="C75" s="1" t="s">
+      <c r="C75" s="3" t="s">
         <v>568</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="3" t="s">
         <v>569</v>
       </c>
-      <c r="E75" s="1" t="s">
+      <c r="E75" s="3" t="s">
         <v>570</v>
       </c>
-      <c r="F75" s="1" t="s">
+      <c r="F75" s="3" t="s">
         <v>571</v>
       </c>
-      <c r="G75" s="1" t="s">
+      <c r="G75" s="3" t="s">
         <v>572</v>
       </c>
-      <c r="H75" s="1" t="s">
+      <c r="H75" s="3" t="s">
         <v>573</v>
       </c>
-      <c r="I75" s="1" t="s">
+      <c r="I75" s="3" t="s">
         <v>574</v>
       </c>
-      <c r="J75" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K75" s="1" t="s">
+      <c r="J75" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K75" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L75" s="1" t="s">
+      <c r="L75" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M75" s="1" t="s">
+      <c r="M75" s="3" t="s">
         <v>567</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="1" t="s">
+    <row r="76" ht="16.5" spans="1:13">
+      <c r="A76" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="B76" s="1" t="s">
+      <c r="B76" s="3" t="s">
         <v>576</v>
       </c>
-      <c r="C76" s="1" t="s">
+      <c r="C76" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="E76" s="1" t="s">
+      <c r="E76" s="3" t="s">
         <v>577</v>
       </c>
-      <c r="F76" s="1" t="s">
+      <c r="F76" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="G76" s="1" t="s">
+      <c r="G76" s="3" t="s">
         <v>579</v>
       </c>
-      <c r="H76" s="1" t="s">
+      <c r="H76" s="3" t="s">
         <v>580</v>
       </c>
-      <c r="I76" s="1" t="s">
+      <c r="I76" s="3" t="s">
         <v>581</v>
       </c>
-      <c r="J76" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K76" s="1" t="s">
+      <c r="J76" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K76" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L76" s="1" t="s">
+      <c r="L76" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M76" s="1" t="s">
+      <c r="M76" s="3" t="s">
         <v>576</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="1" t="s">
+    <row r="77" ht="16.5" spans="1:13">
+      <c r="A77" s="3" t="s">
         <v>582</v>
       </c>
-      <c r="B77" s="1" t="s">
+      <c r="B77" s="3" t="s">
         <v>583</v>
       </c>
-      <c r="C77" s="1" t="s">
+      <c r="C77" s="3" t="s">
         <v>584</v>
       </c>
-      <c r="D77" s="1" t="s">
+      <c r="D77" s="3" t="s">
         <v>585</v>
       </c>
-      <c r="E77" s="1" t="s">
+      <c r="E77" s="3" t="s">
         <v>586</v>
       </c>
-      <c r="F77" s="1" t="s">
+      <c r="F77" s="3" t="s">
         <v>587</v>
       </c>
-      <c r="G77" s="1" t="s">
+      <c r="G77" s="3" t="s">
         <v>588</v>
       </c>
-      <c r="H77" s="1" t="s">
+      <c r="H77" s="3" t="s">
         <v>589</v>
       </c>
-      <c r="I77" s="1" t="s">
+      <c r="I77" s="3" t="s">
         <v>590</v>
       </c>
-      <c r="J77" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K77" s="1" t="s">
+      <c r="J77" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K77" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L77" s="1" t="s">
+      <c r="L77" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M77" s="1" t="s">
+      <c r="M77" s="3" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="1" t="s">
+    <row r="78" ht="16.5" spans="1:13">
+      <c r="A78" s="3" t="s">
         <v>591</v>
       </c>
-      <c r="B78" s="1" t="s">
+      <c r="B78" s="3" t="s">
         <v>592</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C78" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="D78" s="1" t="s">
+      <c r="D78" s="3" t="s">
         <v>593</v>
       </c>
-      <c r="E78" s="1" t="s">
+      <c r="E78" s="3" t="s">
         <v>594</v>
       </c>
-      <c r="F78" s="1" t="s">
+      <c r="F78" s="3" t="s">
         <v>595</v>
       </c>
-      <c r="G78" s="1" t="s">
+      <c r="G78" s="3" t="s">
         <v>596</v>
       </c>
-      <c r="H78" s="1" t="s">
+      <c r="H78" s="3" t="s">
         <v>597</v>
       </c>
-      <c r="I78" s="1" t="s">
+      <c r="I78" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="J78" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K78" s="1" t="s">
+      <c r="J78" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K78" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L78" s="1" t="s">
+      <c r="L78" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M78" s="1" t="s">
+      <c r="M78" s="3" t="s">
         <v>592</v>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="1" t="s">
+    <row r="79" ht="16.5" spans="1:13">
+      <c r="A79" s="3" t="s">
         <v>599</v>
       </c>
-      <c r="B79" s="1" t="s">
+      <c r="B79" s="3" t="s">
         <v>600</v>
       </c>
-      <c r="C79" s="1" t="s">
+      <c r="C79" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="D79" s="1" t="s">
+      <c r="D79" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="E79" s="1" t="s">
+      <c r="E79" s="3" t="s">
         <v>601</v>
       </c>
-      <c r="F79" s="1" t="s">
+      <c r="F79" s="3" t="s">
         <v>602</v>
       </c>
-      <c r="G79" s="1" t="s">
+      <c r="G79" s="3" t="s">
         <v>603</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H79" s="3" t="s">
         <v>604</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="I79" s="3" t="s">
         <v>605</v>
       </c>
-      <c r="J79" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K79" s="1" t="s">
+      <c r="J79" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K79" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L79" s="1" t="s">
+      <c r="L79" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M79" s="1" t="s">
+      <c r="M79" s="3" t="s">
         <v>600</v>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="1" t="s">
+    <row r="80" ht="60" spans="1:13">
+      <c r="A80" s="3" t="s">
         <v>606</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B80" s="3" t="s">
         <v>607</v>
       </c>
-      <c r="C80" s="1" t="s">
+      <c r="C80" s="3" t="s">
         <v>608</v>
       </c>
-      <c r="D80" s="1" t="s">
+      <c r="D80" s="3" t="s">
         <v>609</v>
       </c>
-      <c r="E80" s="1" t="s">
+      <c r="E80" s="3" t="s">
         <v>610</v>
       </c>
-      <c r="F80" s="1" t="s">
+      <c r="F80" s="3" t="s">
         <v>611</v>
       </c>
-      <c r="G80" s="1" t="s">
+      <c r="G80" s="3" t="s">
         <v>612</v>
       </c>
-      <c r="H80" s="1" t="s">
+      <c r="H80" s="3" t="s">
         <v>613</v>
       </c>
-      <c r="I80" s="1" t="s">
+      <c r="I80" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="J80" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K80" s="1" t="s">
+      <c r="J80" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K80" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L80" s="1" t="s">
+      <c r="L80" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M80" s="1" t="s">
+      <c r="M80" s="3" t="s">
         <v>607</v>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="1" t="s">
+    <row r="81" ht="16.5" spans="1:13">
+      <c r="A81" s="3" t="s">
         <v>615</v>
       </c>
-      <c r="B81" s="1" t="s">
+      <c r="B81" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="C81" s="1" t="s">
+      <c r="C81" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D81" s="1" t="s">
+      <c r="D81" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E81" s="1" t="s">
+      <c r="E81" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="F81" s="1" t="s">
+      <c r="F81" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="G81" s="1" t="s">
+      <c r="G81" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="H81" s="1" t="s">
+      <c r="H81" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I81" s="1" t="s">
+      <c r="I81" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J81" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K81" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="L81" s="1" t="s">
+      <c r="J81" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K81" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L81" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M81" s="1" t="s">
+      <c r="M81" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="1" t="s">
+    <row r="82" ht="45" spans="1:13">
+      <c r="A82" s="3" t="s">
         <v>616</v>
       </c>
-      <c r="B82" s="1" t="s">
+      <c r="B82" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="C82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J82" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K82" s="1" t="s">
+      <c r="C82" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="E82" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="J82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K82" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L82" s="1" t="s">
+      <c r="L82" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="M82" s="1" t="s">
+      <c r="M82" s="3" t="s">
         <v>617</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="1" t="s">
-        <v>618</v>
-      </c>
-      <c r="B83" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="C83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J83" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K83" s="1" t="s">
+    <row r="83" ht="16.5" spans="1:13">
+      <c r="A83" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="B83" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="C83" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K83" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L83" s="1" t="s">
+      <c r="L83" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M83" s="1" t="s">
-        <v>619</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="1" t="s">
-        <v>620</v>
-      </c>
-      <c r="B84" s="1" t="s">
-        <v>621</v>
-      </c>
-      <c r="C84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="H84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="I84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="J84" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K84" s="1" t="s">
+      <c r="M83" s="3" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="84" ht="30" spans="1:13">
+      <c r="A84" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="B84" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="C84" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="H84" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="J84" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K84" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="L84" s="1" t="s">
+      <c r="L84" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M84" s="1" t="s">
-        <v>621</v>
+      <c r="M84" s="3" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="85" ht="16.5" spans="1:13">
+      <c r="A85" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="B85" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="H85" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="J85" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K85" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M85" s="3" t="s">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="86" ht="16.5" spans="1:13">
+      <c r="A86" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="B86" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="H86" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="J86" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K86" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L86" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M86" s="3" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="87" ht="30" spans="1:13">
+      <c r="A87" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="B87" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="H87" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="J87" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K87" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L87" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="M87" s="3" t="s">
+        <v>660</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L84"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L87" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K84" xr:uid="{8DABD7B3-D640-48FF-A348-40544460443A}">
+    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K87">
       <formula1>"正常,待复核,已复核,待清理"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C86"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C89"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
-        <v>622</v>
-      </c>
-      <c r="B1" s="0" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>668</v>
+      </c>
+      <c r="B1" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>623</v>
-      </c>
-      <c r="B2" s="0" t="s">
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>669</v>
+      </c>
+      <c r="B2" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="0" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
+      <c r="C2" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>671</v>
+      </c>
+      <c r="B3" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>395</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>458</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>489</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83" t="s">
+        <v>615</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" t="s">
         <v>625</v>
       </c>
-      <c r="B3" s="0" t="s">
-        <v>626</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>333</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="0" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="0" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="0" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="0" t="s">
-        <v>458</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="s">
-        <v>466</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="s">
-        <v>473</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="0" t="s">
-        <v>480</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="s">
-        <v>489</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="s">
-        <v>505</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="s">
-        <v>507</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="s">
-        <v>515</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="0" t="s">
-        <v>533</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="0" t="s">
-        <v>542</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="0" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="0" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="0" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="0" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="0" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="0" t="s">
-        <v>582</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="0" t="s">
-        <v>591</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="0" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="0" t="s">
-        <v>606</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" s="0" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="0" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="0" t="s">
-        <v>618</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="0" t="s">
-        <v>620</v>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" t="s">
+        <v>643</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" t="s">
+        <v>659</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1" style="4"/>
-    <col min="2" max="16384" width="9.140625" customWidth="1" style="4"/>
+    <col min="1" max="1" width="110" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.14285714285714" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="s">
-        <v>627</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="s">
-        <v>628</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="s">
-        <v>629</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="4" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="4" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="4" t="s">
-        <v>633</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="s">
-        <v>634</v>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>680</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/Translations/Localization.xlsx
+++ b/AAAGameData/Translations/Localization.xlsx
@@ -1,23 +1,43 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\unityPro\smash\AAAGameData\Translations\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="Translations" sheetId="1" r:id="rId1"/>
-    <sheet name="_Metadata" sheetId="2" r:id="rId3" state="veryHidden"/>
-    <sheet name="填写说明" sheetId="3" r:id="rId4"/>
+    <sheet name="_Metadata" sheetId="2" state="veryHidden" r:id="rId2"/>
+    <sheet name="填写说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$69</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$70</definedName>
   </definedNames>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="568">
   <si>
     <t>Key</t>
   </si>
@@ -1657,6 +1677,33 @@
     <t>आपके उदार दान के लिए धन्यवाद!</t>
   </si>
   <si>
+    <t>giftHint</t>
+  </si>
+  <si>
+    <t>Collect treasure chests</t>
+  </si>
+  <si>
+    <t>Colete baús de tesouro</t>
+  </si>
+  <si>
+    <t>Recolha baús de tesouro</t>
+  </si>
+  <si>
+    <t>Recoge cofres del tesoro</t>
+  </si>
+  <si>
+    <t>Collectez des coffres au trésor</t>
+  </si>
+  <si>
+    <t>Собирайте сундуки с сокровищами</t>
+  </si>
+  <si>
+    <t>宝箱を集めよう</t>
+  </si>
+  <si>
+    <t>खज़ाने के संदूक इकट्ठा करें</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
@@ -1669,7 +1716,7 @@
     <t>Keys (do not edit)</t>
   </si>
   <si>
-    <t>65208614aa0c422f906d629ed962df96</t>
+    <t>efad80e27375404ca19bd9002a7089ae</t>
   </si>
   <si>
     <t>请在 Translations 工作表填写译文；可以整行排序，不要单独排序某一列。</t>
@@ -1699,28 +1746,372 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1728,51 +2119,808 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFill="0" applyBorder="0"/>
+    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" xfId="0"/>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" applyNumberFormat="1" fontId="1" applyFont="1" xfId="0" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" xfId="0">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="17">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="double">
+          <color theme="4"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <left style="thin">
+          <color theme="4"/>
+        </left>
+        <right style="thin">
+          <color theme="4"/>
+        </right>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+        <horizontal style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+    </tableStyle>
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+    </tableStyle>
+  </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="4472C4"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Traditional Arabic"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable=" xr">
-  <dimension ref="A1:M69"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:M70"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" hidden="1" width="28" customWidth="1" style="1"/>
-    <col min="2" max="2" width="28" customWidth="1" style="1"/>
-    <col min="3" max="3" width="28" customWidth="1" style="1"/>
-    <col min="4" max="4" width="28" customWidth="1" style="1"/>
-    <col min="5" max="5" width="28" customWidth="1" style="1"/>
-    <col min="6" max="6" width="28" customWidth="1" style="1"/>
-    <col min="7" max="7" width="28" customWidth="1" style="1"/>
-    <col min="8" max="8" width="28" customWidth="1" style="1"/>
-    <col min="9" max="9" width="28" customWidth="1" style="1"/>
-    <col min="10" max="10" width="28" customWidth="1" style="1"/>
-    <col min="11" max="11" width="12" customWidth="1" style="1"/>
-    <col min="12" max="12" width="8" customWidth="1" style="1"/>
-    <col min="13" max="13" hidden="1" width="28" customWidth="1" style="1"/>
-    <col min="14" max="16384" width="9.140625" customWidth="1" style="1"/>
+    <col min="1" max="1" width="28" style="3" hidden="1" customWidth="1"/>
+    <col min="2" max="10" width="28" style="3" customWidth="1"/>
+    <col min="11" max="11" width="12" style="3" customWidth="1"/>
+    <col min="12" max="12" width="8" style="3" customWidth="1"/>
+    <col min="13" max="13" width="28" style="3" hidden="1" customWidth="1"/>
+    <col min="14" max="16384" width="9.14285714285714" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1">
+    <row r="1" s="2" customFormat="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1813,3232 +2961,3285 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="1" t="s">
+    <row r="2" ht="16.5" spans="1:13">
+      <c r="A2" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="1" t="s">
+      <c r="J2" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L2" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="3" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
+    <row r="3" ht="16.5" spans="1:13">
+      <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="1" t="s">
+      <c r="J3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="M3" s="3" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="s">
+    <row r="4" ht="30" spans="1:13">
+      <c r="A4" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B4" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="E4" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G4" s="1" t="s">
+      <c r="G4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="H4" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I4" s="1" t="s">
+      <c r="I4" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L4" s="1" t="s">
+      <c r="J4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L4" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="M4" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="s">
+    <row r="5" ht="30" spans="1:13">
+      <c r="A5" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B5" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="E5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="G5" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="H5" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="1" t="s">
+      <c r="I5" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="1" t="s">
+      <c r="J5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M5" s="1" t="s">
+      <c r="M5" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="s">
+    <row r="6" ht="16.5" spans="1:13">
+      <c r="A6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="E6" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="1" t="s">
+      <c r="G6" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="H6" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I6" s="1" t="s">
+      <c r="I6" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="1" t="s">
+      <c r="J6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L6" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="M6" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="s">
+    <row r="7" ht="16.5" spans="1:13">
+      <c r="A7" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B7" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="E7" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="G7" s="1" t="s">
+      <c r="G7" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="H7" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="I7" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="1" t="s">
+      <c r="J7" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L7" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="3" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="s">
+    <row r="8" ht="16.5" spans="1:13">
+      <c r="A8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="E8" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="F8" s="1" t="s">
+      <c r="F8" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="G8" s="1" t="s">
+      <c r="G8" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="H8" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="I8" s="1" t="s">
+      <c r="I8" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="1" t="s">
+      <c r="J8" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="3" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="s">
+    <row r="9" ht="16.5" spans="1:13">
+      <c r="A9" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="B9" s="1" t="s">
+      <c r="B9" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="E9" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G9" s="1" t="s">
+      <c r="G9" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="H9" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I9" s="1" t="s">
+      <c r="I9" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J9" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="1" t="s">
+      <c r="J9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="M9" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="s">
+    <row r="10" ht="45" spans="1:13">
+      <c r="A10" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B10" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="E10" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="F10" s="1" t="s">
+      <c r="F10" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="H10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="I10" s="1" t="s">
+      <c r="I10" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="J10" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="1" t="s">
+      <c r="J10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L10" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="3" t="s">
         <v>82</v>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="s">
+    <row r="11" ht="16.5" spans="1:13">
+      <c r="A11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B11" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="C11" s="1" t="s">
+      <c r="C11" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="E11" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="H11" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I11" s="1" t="s">
+      <c r="I11" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="1" t="s">
+      <c r="J11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="3" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="s">
+    <row r="12" ht="16.5" spans="1:13">
+      <c r="A12" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E12" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="H12" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="I12" s="1" t="s">
+      <c r="I12" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="J12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="1" t="s">
+      <c r="J12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="3" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="s">
+    <row r="13" ht="16.5" spans="1:13">
+      <c r="A13" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="C13" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="E13" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="H13" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="I13" s="1" t="s">
+      <c r="I13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="J13" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="1" t="s">
+      <c r="J13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L13" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="3" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="s">
+    <row r="14" ht="16.5" spans="1:13">
+      <c r="A14" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="C14" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="E14" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="H14" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I14" s="1" t="s">
+      <c r="I14" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J14" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="1" t="s">
+      <c r="J14" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L14" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="3" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="s">
+    <row r="15" ht="30" spans="1:13">
+      <c r="A15" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B15" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="1" t="s">
+      <c r="C15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="E15" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F15" s="1" t="s">
+      <c r="F15" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="H15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="I15" s="1" t="s">
+      <c r="I15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="1" t="s">
+      <c r="J15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L15" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" s="3" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="s">
+    <row r="16" ht="16.5" spans="1:13">
+      <c r="A16" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="B16" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="C16" s="1" t="s">
+      <c r="C16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="E16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F16" s="1" t="s">
+      <c r="F16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="H16" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="I16" s="1" t="s">
+      <c r="I16" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="J16" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="1" t="s">
+      <c r="J16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L16" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="3" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="s">
+    <row r="17" ht="16.5" spans="1:13">
+      <c r="A17" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B17" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="C17" s="1" t="s">
+      <c r="C17" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="E17" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="H17" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I17" s="1" t="s">
+      <c r="I17" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="1" t="s">
+      <c r="J17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L17" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="3" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="s">
+    <row r="18" ht="33" spans="1:13">
+      <c r="A18" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="C18" s="1" t="s">
+      <c r="C18" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="E18" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="G18" s="1" t="s">
+      <c r="G18" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="H18" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="I18" s="1" t="s">
+      <c r="I18" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J18" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" s="1" t="s">
+      <c r="J18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L18" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="M18" s="3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="s">
+    <row r="19" ht="16.5" spans="1:13">
+      <c r="A19" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B19" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="C19" s="1" t="s">
+      <c r="C19" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="E19" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="G19" s="1" t="s">
+      <c r="G19" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="H19" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="I19" s="1" t="s">
+      <c r="I19" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J19" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="1" t="s">
+      <c r="J19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L19" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="M19" s="3" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="s">
+    <row r="20" ht="16.5" spans="1:13">
+      <c r="A20" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="B20" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="1" t="s">
+      <c r="C20" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="E20" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="G20" s="1" t="s">
+      <c r="G20" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="H20" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="I20" s="1" t="s">
+      <c r="I20" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="J20" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="1" t="s">
+      <c r="J20" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L20" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="M20" s="3" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="s">
+    <row r="21" ht="16.5" spans="1:13">
+      <c r="A21" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="B21" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="C21" s="1" t="s">
+      <c r="C21" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="E21" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="F21" s="1" t="s">
+      <c r="F21" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="G21" s="1" t="s">
+      <c r="G21" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="H21" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="I21" s="1" t="s">
+      <c r="I21" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="J21" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="1" t="s">
+      <c r="J21" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L21" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="M21" s="3" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="s">
+    <row r="22" ht="30" spans="1:13">
+      <c r="A22" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B22" s="1" t="s">
+      <c r="B22" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="D22" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="E22" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G22" s="1" t="s">
+      <c r="G22" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="H22" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I22" s="1" t="s">
+      <c r="I22" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="J22" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" s="1" t="s">
+      <c r="J22" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="M22" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="s">
+    <row r="23" ht="28.5" spans="1:13">
+      <c r="A23" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B23" s="1" t="s">
+      <c r="B23" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="E23" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="G23" s="1" t="s">
+      <c r="G23" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="H23" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I23" s="1" t="s">
+      <c r="I23" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J23" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" s="1" t="s">
+      <c r="J23" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L23" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="M23" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="s">
+    <row r="24" ht="45" spans="1:13">
+      <c r="A24" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="B24" s="1" t="s">
+      <c r="B24" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="C24" s="1" t="s">
+      <c r="C24" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="E24" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="G24" s="1" t="s">
+      <c r="G24" s="3" t="s">
         <v>194</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="H24" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="I24" s="1" t="s">
+      <c r="I24" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="J24" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" s="1" t="s">
+      <c r="J24" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L24" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="M24" s="3" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="s">
+    <row r="25" ht="30" spans="1:13">
+      <c r="A25" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="B25" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="C25" s="1" t="s">
+      <c r="C25" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="E25" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="G25" s="1" t="s">
+      <c r="G25" s="3" t="s">
         <v>202</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="H25" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="I25" s="1" t="s">
+      <c r="I25" s="3" t="s">
         <v>204</v>
       </c>
-      <c r="J25" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" s="1" t="s">
+      <c r="J25" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L25" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="M25" s="3" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="s">
+    <row r="26" ht="30" spans="1:13">
+      <c r="A26" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="B26" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="C26" s="1" t="s">
+      <c r="C26" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="E26" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="F26" s="1" t="s">
+      <c r="F26" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="G26" s="1" t="s">
+      <c r="G26" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="H26" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="I26" s="1" t="s">
+      <c r="I26" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="J26" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" s="1" t="s">
+      <c r="J26" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L26" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="M26" s="3" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="s">
+    <row r="27" ht="30" spans="1:13">
+      <c r="A27" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="B27" s="1" t="s">
+      <c r="B27" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="C27" s="1" t="s">
+      <c r="C27" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="E27" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="F27" s="1" t="s">
+      <c r="F27" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="G27" s="1" t="s">
+      <c r="G27" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="H27" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I27" s="1" t="s">
+      <c r="I27" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J27" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27" s="1" t="s">
+      <c r="J27" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="M27" s="3" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="s">
+    <row r="28" ht="33" spans="1:13">
+      <c r="A28" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="B28" s="1" t="s">
+      <c r="B28" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="C28" s="1" t="s">
+      <c r="C28" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="E28" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="F28" s="1" t="s">
+      <c r="F28" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="G28" s="1" t="s">
+      <c r="G28" s="3" t="s">
         <v>229</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="H28" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="I28" s="1" t="s">
+      <c r="I28" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="J28" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28" s="1" t="s">
+      <c r="J28" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L28" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="M28" s="3" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="s">
+    <row r="29" ht="16.5" spans="1:13">
+      <c r="A29" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="B29" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="C29" s="1" t="s">
+      <c r="C29" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="E29" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="G29" s="1" t="s">
+      <c r="G29" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="H29" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="I29" s="1" t="s">
+      <c r="I29" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="J29" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" s="1" t="s">
+      <c r="J29" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L29" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="M29" s="3" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="s">
+    <row r="30" ht="30" spans="1:13">
+      <c r="A30" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="B30" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="C30" s="1" t="s">
+      <c r="C30" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="E30" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="G30" s="1" t="s">
+      <c r="G30" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="H30" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="I30" s="1" t="s">
+      <c r="I30" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="J30" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" s="1" t="s">
+      <c r="J30" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="M30" s="3" t="s">
         <v>242</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="s">
+    <row r="31" ht="16.5" spans="1:13">
+      <c r="A31" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="B31" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="C31" s="1" t="s">
+      <c r="C31" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="E31" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="F31" s="1" t="s">
+      <c r="F31" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="G31" s="1" t="s">
+      <c r="G31" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="H31" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="I31" s="1" t="s">
+      <c r="I31" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="J31" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="1" t="s">
+      <c r="J31" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L31" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="M31" s="3" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="s">
+    <row r="32" ht="30" spans="1:13">
+      <c r="A32" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="B32" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="C32" s="1" t="s">
+      <c r="C32" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="E32" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="G32" s="1" t="s">
+      <c r="G32" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="H32" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="I32" s="1" t="s">
+      <c r="I32" s="3" t="s">
         <v>266</v>
       </c>
-      <c r="J32" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L32" s="1" t="s">
+      <c r="J32" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L32" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="M32" s="3" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="s">
+    <row r="33" ht="49.5" spans="1:13">
+      <c r="A33" s="3" t="s">
         <v>267</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="B33" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="3" t="s">
         <v>270</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="E33" s="3" t="s">
         <v>271</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="3" t="s">
         <v>272</v>
       </c>
-      <c r="G33" s="1" t="s">
+      <c r="G33" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="H33" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="I33" s="1" t="s">
+      <c r="I33" s="3" t="s">
         <v>275</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="1" t="s">
+      <c r="J33" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="M33" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="1" t="s">
+    <row r="34" ht="33" spans="1:13">
+      <c r="A34" s="3" t="s">
         <v>276</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="B34" s="3" t="s">
         <v>277</v>
       </c>
-      <c r="C34" s="1" t="s">
+      <c r="C34" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="E34" s="3" t="s">
         <v>280</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="3" t="s">
         <v>281</v>
       </c>
-      <c r="G34" s="1" t="s">
+      <c r="G34" s="3" t="s">
         <v>282</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="H34" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="I34" s="1" t="s">
+      <c r="I34" s="3" t="s">
         <v>284</v>
       </c>
-      <c r="J34" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L34" s="1" t="s">
+      <c r="J34" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="M34" s="3" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="1" t="s">
+    <row r="35" ht="16.5" spans="1:13">
+      <c r="A35" s="3" t="s">
         <v>285</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B35" s="3" t="s">
         <v>286</v>
       </c>
-      <c r="C35" s="1" t="s">
+      <c r="C35" s="3" t="s">
         <v>287</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="E35" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="3" t="s">
         <v>290</v>
       </c>
-      <c r="G35" s="1" t="s">
+      <c r="G35" s="3" t="s">
         <v>291</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="H35" s="3" t="s">
         <v>292</v>
       </c>
-      <c r="I35" s="1" t="s">
+      <c r="I35" s="3" t="s">
         <v>293</v>
       </c>
-      <c r="J35" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L35" s="1" t="s">
+      <c r="J35" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="M35" s="3" t="s">
         <v>286</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="1" t="s">
+    <row r="36" ht="30" spans="1:13">
+      <c r="A36" s="3" t="s">
         <v>294</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="B36" s="3" t="s">
         <v>295</v>
       </c>
-      <c r="C36" s="1" t="s">
+      <c r="C36" s="3" t="s">
         <v>296</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="3" t="s">
         <v>297</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="E36" s="3" t="s">
         <v>298</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="G36" s="1" t="s">
+      <c r="G36" s="3" t="s">
         <v>300</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="H36" s="3" t="s">
         <v>301</v>
       </c>
-      <c r="I36" s="1" t="s">
+      <c r="I36" s="3" t="s">
         <v>302</v>
       </c>
-      <c r="J36" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L36" s="1" t="s">
+      <c r="J36" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="M36" s="3" t="s">
         <v>295</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="1" t="s">
+    <row r="37" ht="33" spans="1:13">
+      <c r="A37" s="3" t="s">
         <v>303</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="B37" s="3" t="s">
         <v>304</v>
       </c>
-      <c r="C37" s="1" t="s">
+      <c r="C37" s="3" t="s">
         <v>305</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="3" t="s">
         <v>306</v>
       </c>
-      <c r="E37" s="1" t="s">
+      <c r="E37" s="3" t="s">
         <v>307</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="3" t="s">
         <v>308</v>
       </c>
-      <c r="G37" s="1" t="s">
+      <c r="G37" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="H37" s="1" t="s">
+      <c r="H37" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="I37" s="1" t="s">
+      <c r="I37" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="J37" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L37" s="1" t="s">
+      <c r="J37" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M37" s="1" t="s">
+      <c r="M37" s="3" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="1" t="s">
+    <row r="38" ht="33" spans="1:13">
+      <c r="A38" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="B38" s="1" t="s">
+      <c r="B38" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="C38" s="1" t="s">
+      <c r="C38" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="E38" s="1" t="s">
+      <c r="E38" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="F38" s="1" t="s">
+      <c r="F38" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="G38" s="1" t="s">
+      <c r="G38" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="H38" s="1" t="s">
+      <c r="H38" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="I38" s="1" t="s">
+      <c r="I38" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="J38" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L38" s="1" t="s">
+      <c r="J38" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L38" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M38" s="1" t="s">
+      <c r="M38" s="3" t="s">
         <v>313</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="1" t="s">
+    <row r="39" ht="16.5" spans="1:13">
+      <c r="A39" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="B39" s="1" t="s">
+      <c r="B39" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="C39" s="1" t="s">
+      <c r="C39" s="3" t="s">
         <v>323</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="3" t="s">
         <v>324</v>
       </c>
-      <c r="E39" s="1" t="s">
+      <c r="E39" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="F39" s="1" t="s">
+      <c r="F39" s="3" t="s">
         <v>326</v>
       </c>
-      <c r="G39" s="1" t="s">
+      <c r="G39" s="3" t="s">
         <v>327</v>
       </c>
-      <c r="H39" s="1" t="s">
+      <c r="H39" s="3" t="s">
         <v>328</v>
       </c>
-      <c r="I39" s="1" t="s">
+      <c r="I39" s="3" t="s">
         <v>329</v>
       </c>
-      <c r="J39" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L39" s="1" t="s">
+      <c r="J39" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L39" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M39" s="1" t="s">
+      <c r="M39" s="3" t="s">
         <v>322</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="1" t="s">
+    <row r="40" ht="16.5" spans="1:13">
+      <c r="A40" s="3" t="s">
         <v>330</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B40" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C40" s="1" t="s">
+      <c r="C40" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E40" s="1" t="s">
+      <c r="E40" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G40" s="1" t="s">
+      <c r="G40" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="H40" s="1" t="s">
+      <c r="H40" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="I40" s="1" t="s">
+      <c r="I40" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="J40" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" s="1" t="s">
+      <c r="J40" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L40" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M40" s="1" t="s">
+      <c r="M40" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="1" t="s">
+    <row r="41" ht="16.5" spans="1:13">
+      <c r="A41" s="3" t="s">
         <v>338</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="B41" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="C41" s="1" t="s">
+      <c r="C41" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="3" t="s">
         <v>340</v>
       </c>
-      <c r="E41" s="1" t="s">
+      <c r="E41" s="3" t="s">
         <v>341</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="3" t="s">
         <v>342</v>
       </c>
-      <c r="G41" s="1" t="s">
+      <c r="G41" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="H41" s="1" t="s">
+      <c r="H41" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I41" s="1" t="s">
+      <c r="I41" s="3" t="s">
         <v>344</v>
       </c>
-      <c r="J41" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L41" s="1" t="s">
+      <c r="J41" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M41" s="1" t="s">
+      <c r="M41" s="3" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="1" t="s">
+    <row r="42" ht="16.5" spans="1:13">
+      <c r="A42" s="3" t="s">
         <v>345</v>
       </c>
-      <c r="B42" s="1" t="s">
+      <c r="B42" s="3" t="s">
         <v>346</v>
       </c>
-      <c r="C42" s="1" t="s">
+      <c r="C42" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="E42" s="1" t="s">
+      <c r="E42" s="3" t="s">
         <v>347</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="3" t="s">
         <v>348</v>
       </c>
-      <c r="G42" s="1" t="s">
+      <c r="G42" s="3" t="s">
         <v>349</v>
       </c>
-      <c r="H42" s="1" t="s">
+      <c r="H42" s="3" t="s">
         <v>350</v>
       </c>
-      <c r="I42" s="1" t="s">
+      <c r="I42" s="3" t="s">
         <v>351</v>
       </c>
-      <c r="J42" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L42" s="1" t="s">
+      <c r="J42" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L42" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M42" s="1" t="s">
+      <c r="M42" s="3" t="s">
         <v>346</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="1" t="s">
+    <row r="43" ht="45" spans="1:13">
+      <c r="A43" s="3" t="s">
         <v>352</v>
       </c>
-      <c r="B43" s="1" t="s">
+      <c r="B43" s="3" t="s">
         <v>353</v>
       </c>
-      <c r="C43" s="1" t="s">
+      <c r="C43" s="3" t="s">
         <v>354</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="3" t="s">
         <v>355</v>
       </c>
-      <c r="E43" s="1" t="s">
+      <c r="E43" s="3" t="s">
         <v>356</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="3" t="s">
         <v>357</v>
       </c>
-      <c r="G43" s="1" t="s">
+      <c r="G43" s="3" t="s">
         <v>358</v>
       </c>
-      <c r="H43" s="1" t="s">
+      <c r="H43" s="3" t="s">
         <v>359</v>
       </c>
-      <c r="I43" s="1" t="s">
+      <c r="I43" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="J43" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="J43" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M43" s="1" t="s">
+      <c r="M43" s="3" t="s">
         <v>353</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="1" t="s">
+    <row r="44" ht="33" spans="1:13">
+      <c r="A44" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B44" s="1" t="s">
+      <c r="B44" s="3" t="s">
         <v>362</v>
       </c>
-      <c r="C44" s="1" t="s">
+      <c r="C44" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="E44" s="1" t="s">
+      <c r="E44" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="G44" s="1" t="s">
+      <c r="G44" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="H44" s="1" t="s">
+      <c r="H44" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="I44" s="1" t="s">
+      <c r="I44" s="3" t="s">
         <v>368</v>
       </c>
-      <c r="J44" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L44" s="1" t="s">
+      <c r="J44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L44" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M44" s="1" t="s">
+      <c r="M44" s="3" t="s">
         <v>362</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="1" t="s">
+    <row r="45" ht="16.5" spans="1:13">
+      <c r="A45" s="3" t="s">
         <v>369</v>
       </c>
-      <c r="B45" s="1" t="s">
+      <c r="B45" s="3" t="s">
         <v>370</v>
       </c>
-      <c r="C45" s="1" t="s">
+      <c r="C45" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="3" t="s">
         <v>371</v>
       </c>
-      <c r="E45" s="1" t="s">
+      <c r="E45" s="3" t="s">
         <v>372</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="3" t="s">
         <v>373</v>
       </c>
-      <c r="G45" s="1" t="s">
+      <c r="G45" s="3" t="s">
         <v>374</v>
       </c>
-      <c r="H45" s="1" t="s">
+      <c r="H45" s="3" t="s">
         <v>375</v>
       </c>
-      <c r="I45" s="1" t="s">
+      <c r="I45" s="3" t="s">
         <v>376</v>
       </c>
-      <c r="J45" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L45" s="1" t="s">
+      <c r="J45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L45" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M45" s="1" t="s">
+      <c r="M45" s="3" t="s">
         <v>370</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="1" t="s">
+    <row r="46" ht="16.5" spans="1:13">
+      <c r="A46" s="3" t="s">
         <v>377</v>
       </c>
-      <c r="B46" s="1" t="s">
+      <c r="B46" s="3" t="s">
         <v>378</v>
       </c>
-      <c r="C46" s="1" t="s">
+      <c r="C46" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="D46" s="1" t="s">
+      <c r="D46" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="E46" s="1" t="s">
+      <c r="E46" s="3" t="s">
         <v>379</v>
       </c>
-      <c r="F46" s="1" t="s">
+      <c r="F46" s="3" t="s">
         <v>380</v>
       </c>
-      <c r="G46" s="1" t="s">
+      <c r="G46" s="3" t="s">
         <v>381</v>
       </c>
-      <c r="H46" s="1" t="s">
+      <c r="H46" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="I46" s="1" t="s">
+      <c r="I46" s="3" t="s">
         <v>383</v>
       </c>
-      <c r="J46" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L46" s="1" t="s">
+      <c r="J46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L46" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M46" s="1" t="s">
+      <c r="M46" s="3" t="s">
         <v>378</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="1" t="s">
+    <row r="47" ht="30" spans="1:13">
+      <c r="A47" s="3" t="s">
         <v>384</v>
       </c>
-      <c r="B47" s="1" t="s">
+      <c r="B47" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C47" s="1" t="s">
+      <c r="C47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="E47" s="1" t="s">
+      <c r="E47" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="F47" s="1" t="s">
+      <c r="F47" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="G47" s="1" t="s">
+      <c r="G47" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="H47" s="1" t="s">
+      <c r="H47" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="I47" s="1" t="s">
+      <c r="I47" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="J47" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L47" s="1" t="s">
+      <c r="J47" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K47" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L47" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M47" s="1" t="s">
+      <c r="M47" s="3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="1" t="s">
+    <row r="48" ht="16.5" spans="1:13">
+      <c r="A48" s="3" t="s">
         <v>385</v>
       </c>
-      <c r="B48" s="1" t="s">
+      <c r="B48" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C48" s="1" t="s">
+      <c r="C48" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E48" s="1" t="s">
+      <c r="E48" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="G48" s="1" t="s">
+      <c r="G48" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="H48" s="1" t="s">
+      <c r="H48" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="I48" s="1" t="s">
+      <c r="I48" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="J48" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L48" s="1" t="s">
+      <c r="J48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L48" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M48" s="1" t="s">
+      <c r="M48" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="1" t="s">
+    <row r="49" ht="28.5" spans="1:13">
+      <c r="A49" s="3" t="s">
         <v>393</v>
       </c>
-      <c r="B49" s="1" t="s">
+      <c r="B49" s="3" t="s">
         <v>394</v>
       </c>
-      <c r="C49" s="1" t="s">
+      <c r="C49" s="3" t="s">
         <v>395</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="3" t="s">
         <v>396</v>
       </c>
-      <c r="E49" s="1" t="s">
+      <c r="E49" s="3" t="s">
         <v>397</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="G49" s="1" t="s">
+      <c r="G49" s="3" t="s">
         <v>399</v>
       </c>
-      <c r="H49" s="1" t="s">
+      <c r="H49" s="3" t="s">
         <v>400</v>
       </c>
-      <c r="I49" s="1" t="s">
+      <c r="I49" s="3" t="s">
         <v>401</v>
       </c>
-      <c r="J49" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L49" s="1" t="s">
+      <c r="J49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L49" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M49" s="1" t="s">
+      <c r="M49" s="3" t="s">
         <v>394</v>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="1" t="s">
+    <row r="50" ht="16.5" spans="1:13">
+      <c r="A50" s="3" t="s">
         <v>402</v>
       </c>
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="C50" s="1" t="s">
+      <c r="C50" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="E50" s="1" t="s">
+      <c r="E50" s="3" t="s">
         <v>333</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="3" t="s">
         <v>334</v>
       </c>
-      <c r="G50" s="1" t="s">
+      <c r="G50" s="3" t="s">
         <v>335</v>
       </c>
-      <c r="H50" s="1" t="s">
+      <c r="H50" s="3" t="s">
         <v>336</v>
       </c>
-      <c r="I50" s="1" t="s">
+      <c r="I50" s="3" t="s">
         <v>337</v>
       </c>
-      <c r="J50" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K50" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L50" s="1" t="s">
+      <c r="J50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L50" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M50" s="1" t="s">
+      <c r="M50" s="3" t="s">
         <v>331</v>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="1" t="s">
+    <row r="51" ht="16.5" spans="1:13">
+      <c r="A51" s="3" t="s">
         <v>403</v>
       </c>
-      <c r="B51" s="1" t="s">
+      <c r="B51" s="3" t="s">
         <v>404</v>
       </c>
-      <c r="C51" s="1" t="s">
+      <c r="C51" s="3" t="s">
         <v>405</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="E51" s="1" t="s">
+      <c r="E51" s="3" t="s">
         <v>406</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="G51" s="1" t="s">
+      <c r="G51" s="3" t="s">
         <v>408</v>
       </c>
-      <c r="H51" s="1" t="s">
+      <c r="H51" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="I51" s="1" t="s">
+      <c r="I51" s="3" t="s">
         <v>410</v>
       </c>
-      <c r="J51" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K51" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L51" s="1" t="s">
+      <c r="J51" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L51" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M51" s="1" t="s">
+      <c r="M51" s="3" t="s">
         <v>404</v>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="1" t="s">
+    <row r="52" ht="16.5" spans="1:13">
+      <c r="A52" s="3" t="s">
         <v>411</v>
       </c>
-      <c r="B52" s="1" t="s">
+      <c r="B52" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="C52" s="1" t="s">
+      <c r="C52" s="3" t="s">
         <v>413</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="3" t="s">
         <v>414</v>
       </c>
-      <c r="E52" s="1" t="s">
+      <c r="E52" s="3" t="s">
         <v>415</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="3" t="s">
         <v>416</v>
       </c>
-      <c r="G52" s="1" t="s">
+      <c r="G52" s="3" t="s">
         <v>417</v>
       </c>
-      <c r="H52" s="1" t="s">
+      <c r="H52" s="3" t="s">
         <v>418</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="I52" s="3" t="s">
         <v>419</v>
       </c>
-      <c r="J52" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K52" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L52" s="1" t="s">
+      <c r="J52" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L52" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M52" s="1" t="s">
+      <c r="M52" s="3" t="s">
         <v>412</v>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="1" t="s">
+    <row r="53" ht="16.5" spans="1:13">
+      <c r="A53" s="3" t="s">
         <v>420</v>
       </c>
-      <c r="B53" s="1" t="s">
+      <c r="B53" s="3" t="s">
         <v>421</v>
       </c>
-      <c r="C53" s="1" t="s">
+      <c r="C53" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="3" t="s">
         <v>423</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="E53" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="3" t="s">
         <v>425</v>
       </c>
-      <c r="G53" s="1" t="s">
+      <c r="G53" s="3" t="s">
         <v>426</v>
       </c>
-      <c r="H53" s="1" t="s">
+      <c r="H53" s="3" t="s">
         <v>427</v>
       </c>
-      <c r="I53" s="1" t="s">
+      <c r="I53" s="3" t="s">
         <v>428</v>
       </c>
-      <c r="J53" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L53" s="1" t="s">
+      <c r="J53" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L53" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M53" s="1" t="s">
+      <c r="M53" s="3" t="s">
         <v>421</v>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="1" t="s">
+    <row r="54" ht="16.5" spans="1:13">
+      <c r="A54" s="3" t="s">
         <v>429</v>
       </c>
-      <c r="B54" s="1" t="s">
+      <c r="B54" s="3" t="s">
         <v>386</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C54" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="3" t="s">
         <v>387</v>
       </c>
-      <c r="E54" s="1" t="s">
+      <c r="E54" s="3" t="s">
         <v>388</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="3" t="s">
         <v>389</v>
       </c>
-      <c r="G54" s="1" t="s">
+      <c r="G54" s="3" t="s">
         <v>390</v>
       </c>
-      <c r="H54" s="1" t="s">
+      <c r="H54" s="3" t="s">
         <v>391</v>
       </c>
-      <c r="I54" s="1" t="s">
+      <c r="I54" s="3" t="s">
         <v>392</v>
       </c>
-      <c r="J54" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L54" s="1" t="s">
+      <c r="J54" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L54" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M54" s="1" t="s">
+      <c r="M54" s="3" t="s">
         <v>386</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="1" t="s">
+    <row r="55" ht="16.5" spans="1:13">
+      <c r="A55" s="3" t="s">
         <v>430</v>
       </c>
-      <c r="B55" s="1" t="s">
+      <c r="B55" s="3" t="s">
         <v>431</v>
       </c>
-      <c r="C55" s="1" t="s">
+      <c r="C55" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="3" t="s">
         <v>432</v>
       </c>
-      <c r="E55" s="1" t="s">
+      <c r="E55" s="3" t="s">
         <v>433</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="3" t="s">
         <v>434</v>
       </c>
-      <c r="G55" s="1" t="s">
+      <c r="G55" s="3" t="s">
         <v>435</v>
       </c>
-      <c r="H55" s="1" t="s">
+      <c r="H55" s="3" t="s">
         <v>436</v>
       </c>
-      <c r="I55" s="1" t="s">
+      <c r="I55" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="J55" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K55" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L55" s="1" t="s">
+      <c r="J55" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L55" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M55" s="1" t="s">
+      <c r="M55" s="3" t="s">
         <v>431</v>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="1" t="s">
+    <row r="56" ht="16.5" spans="1:13">
+      <c r="A56" s="3" t="s">
         <v>438</v>
       </c>
-      <c r="B56" s="1" t="s">
+      <c r="B56" s="3" t="s">
         <v>439</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="3" t="s">
         <v>440</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="E56" s="1" t="s">
+      <c r="E56" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="F56" s="1" t="s">
+      <c r="F56" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="G56" s="1" t="s">
+      <c r="G56" s="3" t="s">
         <v>442</v>
       </c>
-      <c r="H56" s="1" t="s">
+      <c r="H56" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="I56" s="1" t="s">
+      <c r="I56" s="3" t="s">
         <v>443</v>
       </c>
-      <c r="J56" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L56" s="1" t="s">
+      <c r="J56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L56" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M56" s="1" t="s">
+      <c r="M56" s="3" t="s">
         <v>439</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="1" t="s">
+    <row r="57" ht="30" spans="1:13">
+      <c r="A57" s="3" t="s">
         <v>444</v>
       </c>
-      <c r="B57" s="1" t="s">
+      <c r="B57" s="3" t="s">
         <v>445</v>
       </c>
-      <c r="C57" s="1" t="s">
+      <c r="C57" s="3" t="s">
         <v>446</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="3" t="s">
         <v>447</v>
       </c>
-      <c r="E57" s="1" t="s">
+      <c r="E57" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="F57" s="1" t="s">
+      <c r="F57" s="3" t="s">
         <v>449</v>
       </c>
-      <c r="G57" s="1" t="s">
+      <c r="G57" s="3" t="s">
         <v>450</v>
       </c>
-      <c r="H57" s="1" t="s">
+      <c r="H57" s="3" t="s">
         <v>451</v>
       </c>
-      <c r="I57" s="1" t="s">
+      <c r="I57" s="3" t="s">
         <v>452</v>
       </c>
-      <c r="J57" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L57" s="1" t="s">
+      <c r="J57" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M57" s="1" t="s">
+      <c r="M57" s="3" t="s">
         <v>445</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="1" t="s">
+    <row r="58" ht="16.5" spans="1:13">
+      <c r="A58" s="3" t="s">
         <v>453</v>
       </c>
-      <c r="B58" s="1" t="s">
+      <c r="B58" s="3" t="s">
         <v>454</v>
       </c>
-      <c r="C58" s="1" t="s">
+      <c r="C58" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="E58" s="1" t="s">
+      <c r="E58" s="3" t="s">
         <v>455</v>
       </c>
-      <c r="F58" s="1" t="s">
+      <c r="F58" s="3" t="s">
         <v>456</v>
       </c>
-      <c r="G58" s="1" t="s">
+      <c r="G58" s="3" t="s">
         <v>457</v>
       </c>
-      <c r="H58" s="1" t="s">
+      <c r="H58" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="I58" s="1" t="s">
+      <c r="I58" s="3" t="s">
         <v>459</v>
       </c>
-      <c r="J58" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L58" s="1" t="s">
+      <c r="J58" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L58" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M58" s="1" t="s">
+      <c r="M58" s="3" t="s">
         <v>454</v>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="1" t="s">
+    <row r="59" ht="16.5" spans="1:13">
+      <c r="A59" s="3" t="s">
         <v>460</v>
       </c>
-      <c r="B59" s="1" t="s">
+      <c r="B59" s="3" t="s">
         <v>461</v>
       </c>
-      <c r="C59" s="1" t="s">
+      <c r="C59" s="3" t="s">
         <v>462</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="3" t="s">
         <v>463</v>
       </c>
-      <c r="E59" s="1" t="s">
+      <c r="E59" s="3" t="s">
         <v>464</v>
       </c>
-      <c r="F59" s="1" t="s">
+      <c r="F59" s="3" t="s">
         <v>465</v>
       </c>
-      <c r="G59" s="1" t="s">
+      <c r="G59" s="3" t="s">
         <v>466</v>
       </c>
-      <c r="H59" s="1" t="s">
+      <c r="H59" s="3" t="s">
         <v>467</v>
       </c>
-      <c r="I59" s="1" t="s">
+      <c r="I59" s="3" t="s">
         <v>468</v>
       </c>
-      <c r="J59" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K59" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L59" s="1" t="s">
+      <c r="J59" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L59" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M59" s="1" t="s">
+      <c r="M59" s="3" t="s">
         <v>461</v>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="1" t="s">
+    <row r="60" ht="16.5" spans="1:13">
+      <c r="A60" s="3" t="s">
         <v>469</v>
       </c>
-      <c r="B60" s="1" t="s">
+      <c r="B60" s="3" t="s">
         <v>470</v>
       </c>
-      <c r="C60" s="1" t="s">
+      <c r="C60" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="3" t="s">
         <v>471</v>
       </c>
-      <c r="E60" s="1" t="s">
+      <c r="E60" s="3" t="s">
         <v>472</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="3" t="s">
         <v>473</v>
       </c>
-      <c r="G60" s="1" t="s">
+      <c r="G60" s="3" t="s">
         <v>474</v>
       </c>
-      <c r="H60" s="1" t="s">
+      <c r="H60" s="3" t="s">
         <v>475</v>
       </c>
-      <c r="I60" s="1" t="s">
+      <c r="I60" s="3" t="s">
         <v>476</v>
       </c>
-      <c r="J60" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K60" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L60" s="1" t="s">
+      <c r="J60" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L60" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M60" s="1" t="s">
+      <c r="M60" s="3" t="s">
         <v>470</v>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="1" t="s">
+    <row r="61" ht="16.5" spans="1:13">
+      <c r="A61" s="3" t="s">
         <v>477</v>
       </c>
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="3" t="s">
         <v>478</v>
       </c>
-      <c r="C61" s="1" t="s">
+      <c r="C61" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="E61" s="1" t="s">
+      <c r="E61" s="3" t="s">
         <v>479</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="3" t="s">
         <v>480</v>
       </c>
-      <c r="G61" s="1" t="s">
+      <c r="G61" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="H61" s="1" t="s">
+      <c r="H61" s="3" t="s">
         <v>482</v>
       </c>
-      <c r="I61" s="1" t="s">
+      <c r="I61" s="3" t="s">
         <v>483</v>
       </c>
-      <c r="J61" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L61" s="1" t="s">
+      <c r="J61" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L61" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M61" s="1" t="s">
+      <c r="M61" s="3" t="s">
         <v>478</v>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="1" t="s">
+    <row r="62" ht="60" spans="1:13">
+      <c r="A62" s="3" t="s">
         <v>484</v>
       </c>
-      <c r="B62" s="1" t="s">
+      <c r="B62" s="3" t="s">
         <v>485</v>
       </c>
-      <c r="C62" s="1" t="s">
+      <c r="C62" s="3" t="s">
         <v>486</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="3" t="s">
         <v>487</v>
       </c>
-      <c r="E62" s="1" t="s">
+      <c r="E62" s="3" t="s">
         <v>488</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="3" t="s">
         <v>489</v>
       </c>
-      <c r="G62" s="1" t="s">
+      <c r="G62" s="3" t="s">
         <v>490</v>
       </c>
-      <c r="H62" s="1" t="s">
+      <c r="H62" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="I62" s="1" t="s">
+      <c r="I62" s="3" t="s">
         <v>492</v>
       </c>
-      <c r="J62" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K62" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L62" s="1" t="s">
+      <c r="J62" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L62" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M62" s="1" t="s">
+      <c r="M62" s="3" t="s">
         <v>485</v>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="1" t="s">
+    <row r="63" ht="16.5" spans="1:13">
+      <c r="A63" s="3" t="s">
         <v>493</v>
       </c>
-      <c r="B63" s="1" t="s">
+      <c r="B63" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="C63" s="1" t="s">
+      <c r="C63" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E63" s="1" t="s">
+      <c r="E63" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="G63" s="1" t="s">
+      <c r="G63" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="H63" s="1" t="s">
+      <c r="H63" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="I63" s="1" t="s">
+      <c r="I63" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="J63" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K63" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L63" s="1" t="s">
+      <c r="J63" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K63" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L63" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M63" s="1" t="s">
+      <c r="M63" s="3" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="1" t="s">
+    <row r="64" ht="45" spans="1:13">
+      <c r="A64" s="3" t="s">
         <v>494</v>
       </c>
-      <c r="B64" s="1" t="s">
+      <c r="B64" s="3" t="s">
         <v>495</v>
       </c>
-      <c r="C64" s="1" t="s">
+      <c r="C64" s="3" t="s">
         <v>496</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="3" t="s">
         <v>497</v>
       </c>
-      <c r="E64" s="1" t="s">
+      <c r="E64" s="3" t="s">
         <v>498</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="3" t="s">
         <v>499</v>
       </c>
-      <c r="G64" s="1" t="s">
+      <c r="G64" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="H64" s="1" t="s">
+      <c r="H64" s="3" t="s">
         <v>501</v>
       </c>
-      <c r="I64" s="1" t="s">
+      <c r="I64" s="3" t="s">
         <v>502</v>
       </c>
-      <c r="J64" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K64" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L64" s="1" t="s">
+      <c r="J64" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L64" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="M64" s="1" t="s">
+      <c r="M64" s="3" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="1" t="s">
+    <row r="65" ht="16.5" spans="1:13">
+      <c r="A65" s="3" t="s">
         <v>503</v>
       </c>
-      <c r="B65" s="1" t="s">
+      <c r="B65" s="3" t="s">
         <v>504</v>
       </c>
-      <c r="C65" s="1" t="s">
+      <c r="C65" s="3" t="s">
         <v>505</v>
       </c>
-      <c r="D65" s="1" t="s">
+      <c r="D65" s="3" t="s">
         <v>506</v>
       </c>
-      <c r="E65" s="1" t="s">
+      <c r="E65" s="3" t="s">
         <v>507</v>
       </c>
-      <c r="F65" s="1" t="s">
+      <c r="F65" s="3" t="s">
         <v>508</v>
       </c>
-      <c r="G65" s="1" t="s">
+      <c r="G65" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="H65" s="1" t="s">
+      <c r="H65" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="I65" s="1" t="s">
+      <c r="I65" s="3" t="s">
         <v>511</v>
       </c>
-      <c r="J65" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L65" s="1" t="s">
+      <c r="J65" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L65" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M65" s="1" t="s">
+      <c r="M65" s="3" t="s">
         <v>504</v>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="1" t="s">
+    <row r="66" ht="30" spans="1:13">
+      <c r="A66" s="3" t="s">
         <v>512</v>
       </c>
-      <c r="B66" s="1" t="s">
+      <c r="B66" s="3" t="s">
         <v>513</v>
       </c>
-      <c r="C66" s="1" t="s">
+      <c r="C66" s="3" t="s">
         <v>514</v>
       </c>
-      <c r="D66" s="1" t="s">
+      <c r="D66" s="3" t="s">
         <v>515</v>
       </c>
-      <c r="E66" s="1" t="s">
+      <c r="E66" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="F66" s="1" t="s">
+      <c r="F66" s="3" t="s">
         <v>517</v>
       </c>
-      <c r="G66" s="1" t="s">
+      <c r="G66" s="3" t="s">
         <v>518</v>
       </c>
-      <c r="H66" s="1" t="s">
+      <c r="H66" s="3" t="s">
         <v>519</v>
       </c>
-      <c r="I66" s="1" t="s">
+      <c r="I66" s="3" t="s">
         <v>520</v>
       </c>
-      <c r="J66" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K66" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L66" s="1" t="s">
+      <c r="J66" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M66" s="1" t="s">
+      <c r="M66" s="3" t="s">
         <v>513</v>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="1" t="s">
+    <row r="67" ht="16.5" spans="1:13">
+      <c r="A67" s="3" t="s">
         <v>521</v>
       </c>
-      <c r="B67" s="1" t="s">
+      <c r="B67" s="3" t="s">
         <v>522</v>
       </c>
-      <c r="C67" s="1" t="s">
+      <c r="C67" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="3" t="s">
         <v>523</v>
       </c>
-      <c r="E67" s="1" t="s">
+      <c r="E67" s="3" t="s">
         <v>524</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="3" t="s">
         <v>525</v>
       </c>
-      <c r="G67" s="1" t="s">
+      <c r="G67" s="3" t="s">
         <v>526</v>
       </c>
-      <c r="H67" s="1" t="s">
+      <c r="H67" s="3" t="s">
         <v>527</v>
       </c>
-      <c r="I67" s="1" t="s">
+      <c r="I67" s="3" t="s">
         <v>528</v>
       </c>
-      <c r="J67" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K67" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L67" s="1" t="s">
+      <c r="J67" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M67" s="1" t="s">
+      <c r="M67" s="3" t="s">
         <v>522</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="1" t="s">
+    <row r="68" ht="16.5" spans="1:13">
+      <c r="A68" s="3" t="s">
         <v>529</v>
       </c>
-      <c r="B68" s="1" t="s">
+      <c r="B68" s="3" t="s">
         <v>530</v>
       </c>
-      <c r="C68" s="1" t="s">
+      <c r="C68" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="3" t="s">
         <v>531</v>
       </c>
-      <c r="E68" s="1" t="s">
+      <c r="E68" s="3" t="s">
         <v>532</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="3" t="s">
         <v>533</v>
       </c>
-      <c r="G68" s="1" t="s">
+      <c r="G68" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="H68" s="1" t="s">
+      <c r="H68" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="I68" s="1" t="s">
+      <c r="I68" s="3" t="s">
         <v>536</v>
       </c>
-      <c r="J68" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L68" s="1" t="s">
+      <c r="J68" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L68" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M68" s="1" t="s">
+      <c r="M68" s="3" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="1" t="s">
+    <row r="69" ht="30" spans="1:13">
+      <c r="A69" s="3" t="s">
         <v>537</v>
       </c>
-      <c r="B69" s="1" t="s">
+      <c r="B69" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="C69" s="1" t="s">
+      <c r="C69" s="3" t="s">
         <v>539</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="3" t="s">
         <v>540</v>
       </c>
-      <c r="E69" s="1" t="s">
+      <c r="E69" s="3" t="s">
         <v>541</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="3" t="s">
         <v>542</v>
       </c>
-      <c r="G69" s="1" t="s">
+      <c r="G69" s="3" t="s">
         <v>543</v>
       </c>
-      <c r="H69" s="1" t="s">
+      <c r="H69" s="3" t="s">
         <v>544</v>
       </c>
-      <c r="I69" s="1" t="s">
+      <c r="I69" s="3" t="s">
         <v>545</v>
       </c>
-      <c r="J69" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="L69" s="1" t="s">
+      <c r="J69" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L69" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="M69" s="1" t="s">
+      <c r="M69" s="3" t="s">
         <v>538</v>
       </c>
     </row>
+    <row r="70" ht="30" spans="1:13">
+      <c r="A70" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="E70" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="F70" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="G70" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="H70" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="I70" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="J70" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="K70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="L70" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="M70" s="3" t="s">
+        <v>547</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:L69"/>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L70" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K2:K69" xr:uid="{897BFE2A-EDA5-4D45-8354-27BB9051A17C}">
+    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K70 K2:K69">
       <formula1>"正常,待复核,已复核,待清理"</formula1>
     </dataValidation>
   </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C71"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C72"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="2"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="0" t="s">
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>555</v>
+      </c>
+      <c r="B1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>558</v>
+      </c>
+      <c r="B3" t="s">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="A12" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="A13" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="A14" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="A15" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3">
+      <c r="A16" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" t="s">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>494</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>503</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>512</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
+        <v>521</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72" t="s">
         <v>546</v>
       </c>
-      <c r="B1" s="0" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="0" t="s">
-        <v>547</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="0" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="0" t="s">
-        <v>549</v>
-      </c>
-      <c r="B3" s="0" t="s">
-        <v>550</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="0" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="0" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="0" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="0" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="0" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="0" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="0" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="0" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="0" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="0" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="0" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="0" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="0" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="0" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="0" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="0" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="0" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="0" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="0" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="0" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="0" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="0" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="0" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="0" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="0" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="0" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="0" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="0" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="0" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="0" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="0" t="s">
-        <v>267</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="0" t="s">
-        <v>276</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="0" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="0" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="0" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="0" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="0" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="0" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="0" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="0" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="0" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="0" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="0" t="s">
-        <v>369</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="0" t="s">
-        <v>377</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="0" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="0" t="s">
-        <v>385</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="0" t="s">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="0" t="s">
-        <v>402</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="0" t="s">
-        <v>403</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="0" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="0" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="0" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="0" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="0" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="0" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="0" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="0" t="s">
-        <v>460</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="0" t="s">
-        <v>469</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="0" t="s">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="0" t="s">
-        <v>484</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="0" t="s">
-        <v>493</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="0" t="s">
-        <v>494</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="0" t="s">
-        <v>503</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="0" t="s">
-        <v>512</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="0" t="s">
-        <v>521</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="0" t="s">
-        <v>529</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="0" t="s">
-        <v>537</v>
-      </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:A8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelRow="7"/>
   <cols>
-    <col min="1" max="1" width="110" customWidth="1" style="3"/>
-    <col min="2" max="16384" width="9.140625" customWidth="1" style="3"/>
+    <col min="1" max="1" width="110" style="1" customWidth="1"/>
+    <col min="2" max="16384" width="9.14285714285714" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>551</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>552</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3" t="s">
-        <v>553</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>558</v>
+    <row r="1" spans="1:1">
+      <c r="A1" s="1" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="1" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="1" t="s">
+        <v>562</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="1" t="s">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="1" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="1" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="1" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="1" t="s">
+        <v>567</v>
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/AAAGameData/Translations/Localization.xlsx
+++ b/AAAGameData/Translations/Localization.xlsx
@@ -17,7 +17,7 @@
     <sheet name="填写说明" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$L$70</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Translations!$A$1:$P$70</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="994" uniqueCount="568">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1274" uniqueCount="812">
   <si>
     <t>Key</t>
   </si>
@@ -66,6 +66,18 @@
     <t>Hindi</t>
   </si>
   <si>
+    <t>Indonesian</t>
+  </si>
+  <si>
+    <t>Filipino</t>
+  </si>
+  <si>
+    <t>Turkish</t>
+  </si>
+  <si>
+    <t>Thai</t>
+  </si>
+  <si>
     <t>说明</t>
   </si>
   <si>
@@ -99,6 +111,15 @@
     <t>+5 गेंदें</t>
   </si>
   <si>
+    <t>+5 Bola</t>
+  </si>
+  <si>
+    <t>+5 Top</t>
+  </si>
+  <si>
+    <t>ลูกบอล +5 ลูก</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -132,6 +153,18 @@
     <t>जारी रखें?</t>
   </si>
   <si>
+    <t>Lanjutkan?</t>
+  </si>
+  <si>
+    <t>Magpatuloy?</t>
+  </si>
+  <si>
+    <t>Devam edilsin mi?</t>
+  </si>
+  <si>
+    <t>เล่นต่อไหม?</t>
+  </si>
+  <si>
     <t>ArrowPrivacyPolicyUIForm.title</t>
   </si>
   <si>
@@ -156,6 +189,18 @@
     <t>गोपनीयता नीति</t>
   </si>
   <si>
+    <t>Kebijakan Privasi</t>
+  </si>
+  <si>
+    <t>Patakaran sa Privacy</t>
+  </si>
+  <si>
+    <t>Gizlilik Politikası</t>
+  </si>
+  <si>
+    <t>นโยบายความเป็นส่วนตัว</t>
+  </si>
+  <si>
     <t>ArrowRewardDialogUIForm.claim</t>
   </si>
   <si>
@@ -183,6 +228,18 @@
     <t>प्राप्त करें</t>
   </si>
   <si>
+    <t>Klaim</t>
+  </si>
+  <si>
+    <t>Kunin</t>
+  </si>
+  <si>
+    <t>Al</t>
+  </si>
+  <si>
+    <t>รับ</t>
+  </si>
+  <si>
     <t>ArrowRewardUIForm.titletxt</t>
   </si>
   <si>
@@ -207,6 +264,18 @@
     <t>बधाई हो</t>
   </si>
   <si>
+    <t>Selamat</t>
+  </si>
+  <si>
+    <t>Binabati kita</t>
+  </si>
+  <si>
+    <t>Tebrikler</t>
+  </si>
+  <si>
+    <t>ยินดีด้วย</t>
+  </si>
+  <si>
     <t>ArrowSettingController.OFF</t>
   </si>
   <si>
@@ -231,6 +300,18 @@
     <t>बंद</t>
   </si>
   <si>
+    <t>nonaktif</t>
+  </si>
+  <si>
+    <t>naka-off</t>
+  </si>
+  <si>
+    <t>kapalı</t>
+  </si>
+  <si>
+    <t>ปิด</t>
+  </si>
+  <si>
     <t>ArrowSettingController.ON</t>
   </si>
   <si>
@@ -255,6 +336,18 @@
     <t>चालू</t>
   </si>
   <si>
+    <t>aktif</t>
+  </si>
+  <si>
+    <t>naka-on</t>
+  </si>
+  <si>
+    <t>açık</t>
+  </si>
+  <si>
+    <t>เปิด</t>
+  </si>
+  <si>
     <t>ArrowUITopbar.cashOut</t>
   </si>
   <si>
@@ -282,6 +375,18 @@
     <t>निकासी करें</t>
   </si>
   <si>
+    <t>Tarik Dana</t>
+  </si>
+  <si>
+    <t>Mag-withdraw</t>
+  </si>
+  <si>
+    <t>Para Çek</t>
+  </si>
+  <si>
+    <t>ถอนเงิน</t>
+  </si>
+  <si>
     <t>ArrowWithdrawalInfoItem.infoTxt</t>
   </si>
   <si>
@@ -309,6 +414,18 @@
     <t>खिलाड़ी {0} को ({1}) पार करने और {2} प्राप्त करने पर बधाई।</t>
   </si>
   <si>
+    <t>Selamat kepada pemain {0} karena telah menyelesaikan ({1}) dan mengklaim {2}.</t>
+  </si>
+  <si>
+    <t>Binabati namin ang manlalarong {0} sa pagpasa sa ({1}) at pagkuha ng {2}.</t>
+  </si>
+  <si>
+    <t>({1}) aşamasını geçip {2} alan {0} adlı oyuncuyu tebrik ederiz.</t>
+  </si>
+  <si>
+    <t>ยินดีกับผู้เล่น {0} ที่ผ่าน ({1}) และรับ {2}</t>
+  </si>
+  <si>
     <t>claim</t>
   </si>
   <si>
@@ -342,6 +459,18 @@
     <t>अपना खाता दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan akun Anda</t>
+  </si>
+  <si>
+    <t>Ilagay ang iyong account</t>
+  </si>
+  <si>
+    <t>Hesabınızı girin</t>
+  </si>
+  <si>
+    <t>กรอกบัญชีของคุณ</t>
+  </si>
+  <si>
     <t>1</t>
   </si>
   <si>
@@ -372,6 +501,18 @@
     <t>CPF दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan CPF</t>
+  </si>
+  <si>
+    <t>Ilagay ang CPF</t>
+  </si>
+  <si>
+    <t>CPF girin</t>
+  </si>
+  <si>
+    <t>กรอก CPF</t>
+  </si>
+  <si>
     <t>Enteremail</t>
   </si>
   <si>
@@ -396,6 +537,18 @@
     <t>ईमेल की पुष्टि करें</t>
   </si>
   <si>
+    <t>Konfirmasi email</t>
+  </si>
+  <si>
+    <t>Kumpirmahin ang email</t>
+  </si>
+  <si>
+    <t>E-postayı doğrulayın</t>
+  </si>
+  <si>
+    <t>ยืนยันอีเมล</t>
+  </si>
+  <si>
     <t>EnterFullName</t>
   </si>
   <si>
@@ -423,6 +576,18 @@
     <t>पूरा नाम दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan Nama Lengkap</t>
+  </si>
+  <si>
+    <t>Ilagay ang Buong Pangalan</t>
+  </si>
+  <si>
+    <t>Adınızı ve Soyadınızı Girin</t>
+  </si>
+  <si>
+    <t>กรอกชื่อและนามสกุล</t>
+  </si>
+  <si>
     <t>EnterPayPalaccount</t>
   </si>
   <si>
@@ -450,6 +615,18 @@
     <t>PayPal खाता दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan akun PayPal</t>
+  </si>
+  <si>
+    <t>Ilagay ang PayPal account</t>
+  </si>
+  <si>
+    <t>PayPal hesabınızı girin</t>
+  </si>
+  <si>
+    <t>กรอกบัญชี PayPal</t>
+  </si>
+  <si>
     <t>GuidTxt1</t>
   </si>
   <si>
@@ -474,6 +651,18 @@
     <t>उस वस्तु पर टैप करें और तोप चलाएँ!</t>
   </si>
   <si>
+    <t>Ketuk benda itu dan tembakkan meriam!</t>
+  </si>
+  <si>
+    <t>I-tap ang bagay na iyon at paputukin ang kanyon!</t>
+  </si>
+  <si>
+    <t>O nesneye dokun ve topu ateşle!</t>
+  </si>
+  <si>
+    <t>แตะวัตถุนั้นแล้วยิงปืนใหญ่เลย!</t>
+  </si>
+  <si>
     <t>HallTabUIForm.home</t>
   </si>
   <si>
@@ -498,6 +687,15 @@
     <t>होम</t>
   </si>
   <si>
+    <t>Beranda</t>
+  </si>
+  <si>
+    <t>Ana Sayfa</t>
+  </si>
+  <si>
+    <t>หน้าหลัก</t>
+  </si>
+  <si>
     <t>HallTabUIForm.setting</t>
   </si>
   <si>
@@ -525,6 +723,18 @@
     <t>सेटिंग्स</t>
   </si>
   <si>
+    <t>Pengaturan</t>
+  </si>
+  <si>
+    <t>Mga Setting</t>
+  </si>
+  <si>
+    <t>Ayarlar</t>
+  </si>
+  <si>
+    <t>การตั้งค่า</t>
+  </si>
+  <si>
     <t>HallTabUIForm.task</t>
   </si>
   <si>
@@ -549,6 +759,18 @@
     <t>कार्य</t>
   </si>
   <si>
+    <t>Misi</t>
+  </si>
+  <si>
+    <t>Misyon</t>
+  </si>
+  <si>
+    <t>Görev</t>
+  </si>
+  <si>
+    <t>ภารกิจ</t>
+  </si>
+  <si>
     <t>InfoErrTips1</t>
   </si>
   <si>
@@ -576,6 +798,18 @@
     <t>कृपया एक मान्य ईमेल पता दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan alamat email yang valid</t>
+  </si>
+  <si>
+    <t>Maglagay ng wastong email address</t>
+  </si>
+  <si>
+    <t>Lütfen geçerli bir e-posta adresi girin</t>
+  </si>
+  <si>
+    <t>โปรดกรอกที่อยู่อีเมลที่ถูกต้อง</t>
+  </si>
+  <si>
     <t>InfoErrTips2</t>
   </si>
   <si>
@@ -603,6 +837,18 @@
     <t>कृपया एक मान्य CPF दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan CPF yang valid</t>
+  </si>
+  <si>
+    <t>Maglagay ng wastong CPF</t>
+  </si>
+  <si>
+    <t>Lütfen geçerli bir CPF girin</t>
+  </si>
+  <si>
+    <t>โปรดกรอก CPF ที่ถูกต้อง</t>
+  </si>
+  <si>
     <t>InfoErrTips3</t>
   </si>
   <si>
@@ -630,6 +876,18 @@
     <t>PayPal खाते के लिए एक मान्य ईमेल पता आवश्यक है</t>
   </si>
   <si>
+    <t>Akun PayPal harus berupa alamat email yang valid</t>
+  </si>
+  <si>
+    <t>Dapat wastong email address ang PayPal account</t>
+  </si>
+  <si>
+    <t>PayPal hesabı geçerli bir e-posta adresi olmalıdır</t>
+  </si>
+  <si>
+    <t>บัญชี PayPal ต้องเป็นที่อยู่อีเมลที่ถูกต้อง</t>
+  </si>
+  <si>
     <t>InfoErrTips4</t>
   </si>
   <si>
@@ -654,6 +912,18 @@
     <t>कृपया अपना पूरा नाम दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan nama lengkap Anda</t>
+  </si>
+  <si>
+    <t>Ilagay ang iyong buong pangalan</t>
+  </si>
+  <si>
+    <t>Lütfen adınızı ve soyadınızı girin</t>
+  </si>
+  <si>
+    <t>โปรดกรอกชื่อและนามสกุลของคุณ</t>
+  </si>
+  <si>
     <t>InfoErrTips5</t>
   </si>
   <si>
@@ -681,6 +951,18 @@
     <t>कृपया अपना खाता नंबर दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan nomor rekening Anda</t>
+  </si>
+  <si>
+    <t>Ilagay ang numero ng iyong account</t>
+  </si>
+  <si>
+    <t>Lütfen hesap numaranızı girin</t>
+  </si>
+  <si>
+    <t>โปรดกรอกหมายเลขบัญชีของคุณ</t>
+  </si>
+  <si>
     <t>InfoErrTips6</t>
   </si>
   <si>
@@ -708,6 +990,18 @@
     <t>कृपया भुगतान का तरीका चुनें</t>
   </si>
   <si>
+    <t>Pilih metode pembayaran</t>
+  </si>
+  <si>
+    <t>Pumili ng paraan ng pagbabayad</t>
+  </si>
+  <si>
+    <t>Lütfen bir ödeme yöntemi seçin</t>
+  </si>
+  <si>
+    <t>โปรดเลือกวิธีชำระเงิน</t>
+  </si>
+  <si>
     <t>InfoErrTips7</t>
   </si>
   <si>
@@ -735,6 +1029,18 @@
     <t>भुगतान की जानकारी सफलतापूर्वक सहेजी गई</t>
   </si>
   <si>
+    <t>Informasi pembayaran berhasil disimpan</t>
+  </si>
+  <si>
+    <t>Matagumpay na na-save ang impormasyon sa pagbabayad</t>
+  </si>
+  <si>
+    <t>Ödeme bilgileri başarıyla kaydedildi</t>
+  </si>
+  <si>
+    <t>บันทึกข้อมูลการชำระเงินสำเร็จ</t>
+  </si>
+  <si>
     <t>level</t>
   </si>
   <si>
@@ -762,6 +1068,15 @@
     <t>स्तर {0}</t>
   </si>
   <si>
+    <t>Antas {0}</t>
+  </si>
+  <si>
+    <t>Bölüm {0}</t>
+  </si>
+  <si>
+    <t>ด่าน {0}</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.complete</t>
   </si>
   <si>
@@ -786,6 +1101,18 @@
     <t>पूरा हुआ</t>
   </si>
   <si>
+    <t>Selesai</t>
+  </si>
+  <si>
+    <t>Nakumpleto</t>
+  </si>
+  <si>
+    <t>Tamamlandı</t>
+  </si>
+  <si>
+    <t>สำเร็จ</t>
+  </si>
+  <si>
     <t>LevelCompleteUIForm.next</t>
   </si>
   <si>
@@ -813,6 +1140,18 @@
     <t>अगला</t>
   </si>
   <si>
+    <t>Berikutnya</t>
+  </si>
+  <si>
+    <t>Susunod</t>
+  </si>
+  <si>
+    <t>İleri</t>
+  </si>
+  <si>
+    <t>ถัดไป</t>
+  </si>
+  <si>
     <t>MakeUpFail</t>
   </si>
   <si>
@@ -840,6 +1179,18 @@
     <t>हमें खेद है, रिडीम नहीं हो सका।</t>
   </si>
   <si>
+    <t>Maaf, penukaran gagal.</t>
+  </si>
+  <si>
+    <t>Paumanhin, nabigo ang pagpapalit.</t>
+  </si>
+  <si>
+    <t>Üzgünüz, takas işlemi başarısız oldu.</t>
+  </si>
+  <si>
+    <t>ขออภัย การแลกไม่สำเร็จ</t>
+  </si>
+  <si>
     <t>makeupInfoHint1</t>
   </si>
   <si>
@@ -867,6 +1218,18 @@
     <t>कृपया सुनिश्चित करें कि दोनों बार दर्ज किया गया PayPal खाता एक जैसा है।</t>
   </si>
   <si>
+    <t>Pastikan akun PayPal yang dimasukkan di kedua kolom sama.</t>
+  </si>
+  <si>
+    <t>Tiyaking magkapareho ang PayPal account na inilagay sa dalawang field.</t>
+  </si>
+  <si>
+    <t>Lütfen iki kez girdiğiniz PayPal hesabının aynı olduğundan emin olun.</t>
+  </si>
+  <si>
+    <t>โปรดตรวจสอบว่าบัญชี PayPal ที่กรอกทั้งสองครั้งตรงกัน</t>
+  </si>
+  <si>
     <t>makeupInfoHint2</t>
   </si>
   <si>
@@ -894,6 +1257,18 @@
     <t>कृपया ईमेल सही प्रारूप में दर्ज करें।</t>
   </si>
   <si>
+    <t>Masukkan email dengan format yang benar.</t>
+  </si>
+  <si>
+    <t>Ilagay ang email sa tamang format.</t>
+  </si>
+  <si>
+    <t>Lütfen e-posta adresini doğru biçimde girin.</t>
+  </si>
+  <si>
+    <t>โปรดกรอกอีเมลในรูปแบบที่ถูกต้อง</t>
+  </si>
+  <si>
     <t>MakeupPaymentUIForm.desc</t>
   </si>
   <si>
@@ -921,6 +1296,18 @@
     <t>निकासी जारी है</t>
   </si>
   <si>
+    <t>Penarikan sedang diproses</t>
+  </si>
+  <si>
+    <t>Pinoproseso ang pag-withdraw</t>
+  </si>
+  <si>
+    <t>Para çekme işlemi sürüyor</t>
+  </si>
+  <si>
+    <t>กำลังดำเนินการถอนเงิน</t>
+  </si>
+  <si>
     <t>MakeupPaymentUIForm.titletxt</t>
   </si>
   <si>
@@ -948,6 +1335,18 @@
     <t>भुगतान का तरीका</t>
   </si>
   <si>
+    <t>Metode Pembayaran</t>
+  </si>
+  <si>
+    <t>Paraan ng Pagbabayad</t>
+  </si>
+  <si>
+    <t>Ödeme Yöntemi</t>
+  </si>
+  <si>
+    <t>วิธีชำระเงิน</t>
+  </si>
+  <si>
     <t>MakeUpStep1</t>
   </si>
   <si>
@@ -975,6 +1374,18 @@
     <t>पैसे निकालने के लिए स्तर {0} पार करें</t>
   </si>
   <si>
+    <t>Selesaikan level {0} untuk menarik dana</t>
+  </si>
+  <si>
+    <t>Ipasa ang antas {0} para makapag-withdraw</t>
+  </si>
+  <si>
+    <t>Para çekmek için {0}. bölümü geç</t>
+  </si>
+  <si>
+    <t>ผ่านด่าน {0} เพื่อถอนเงิน</t>
+  </si>
+  <si>
     <t>MakeUpStep2</t>
   </si>
   <si>
@@ -1002,6 +1413,18 @@
     <t>पैसे निकालने के लिए {0} और इकट्ठा करें</t>
   </si>
   <si>
+    <t>Kumpulkan {0} lagi untuk menarik dana</t>
+  </si>
+  <si>
+    <t>Mangolekta pa ng {0} para makapag-withdraw</t>
+  </si>
+  <si>
+    <t>Para çekmek için {0} daha topla</t>
+  </si>
+  <si>
+    <t>สะสมเพิ่มอีก {0} เพื่อถอนเงิน</t>
+  </si>
+  <si>
     <t>MakeupUIForm.input</t>
   </si>
   <si>
@@ -1029,6 +1452,18 @@
     <t>दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan</t>
+  </si>
+  <si>
+    <t>Ilagay</t>
+  </si>
+  <si>
+    <t>Gir</t>
+  </si>
+  <si>
+    <t>กรอก</t>
+  </si>
+  <si>
     <t>MakeupUIForm.record</t>
   </si>
   <si>
@@ -1053,6 +1488,18 @@
     <t>इतिहास</t>
   </si>
   <si>
+    <t>Riwayat</t>
+  </si>
+  <si>
+    <t>Kasaysayan</t>
+  </si>
+  <si>
+    <t>Geçmiş</t>
+  </si>
+  <si>
+    <t>ประวัติ</t>
+  </si>
+  <si>
     <t>MakeupUIForm.title</t>
   </si>
   <si>
@@ -1095,6 +1542,15 @@
     <t>बैलेंस {0}=$1</t>
   </si>
   <si>
+    <t>Balanse {0}=$1</t>
+  </si>
+  <si>
+    <t>Bakiye {0}=$1</t>
+  </si>
+  <si>
+    <t>ยอดคงเหลือ {0}=$1</t>
+  </si>
+  <si>
     <t>PcardGiftUIForm.desc</t>
   </si>
   <si>
@@ -1122,6 +1578,18 @@
     <t>विज्ञापन देखें और संदूक से गेम की वस्तुएँ पाएँ।</t>
   </si>
   <si>
+    <t>Tonton iklan untuk mendapatkan item game dari peti.</t>
+  </si>
+  <si>
+    <t>Manood ng mga ad para makakuha ng mga item sa laro mula sa kaban.</t>
+  </si>
+  <si>
+    <t>Sandıktan oyun eşyaları almak için reklam izle.</t>
+  </si>
+  <si>
+    <t>ดูโฆษณาเพื่อรับไอเทมในเกมจากหีบ</t>
+  </si>
+  <si>
     <t>QuitConfirmUIForm.desc</t>
   </si>
   <si>
@@ -1146,6 +1614,18 @@
     <t>अभी छोड़ने पर एक जीवन कम हो जाएगा।</t>
   </si>
   <si>
+    <t>Keluar sekarang akan membuat Anda kehilangan satu nyawa.</t>
+  </si>
+  <si>
+    <t>Mawawalan ka ng isang buhay kung aalis ka ngayon.</t>
+  </si>
+  <si>
+    <t>Şimdi çıkarsan bir can kaybedersin.</t>
+  </si>
+  <si>
+    <t>หากออกตอนนี้ คุณจะเสียหนึ่งชีวิต</t>
+  </si>
+  <si>
     <t>QuitConfirmUIForm.quitTxt</t>
   </si>
   <si>
@@ -1170,6 +1650,18 @@
     <t>छोड़ें?</t>
   </si>
   <si>
+    <t>Keluar?</t>
+  </si>
+  <si>
+    <t>Umalis?</t>
+  </si>
+  <si>
+    <t>Çıkılsın mı?</t>
+  </si>
+  <si>
+    <t>ออกไหม?</t>
+  </si>
+  <si>
     <t>SettingPageUIForm.continue</t>
   </si>
   <si>
@@ -1191,6 +1683,18 @@
     <t>जारी रखें</t>
   </si>
   <si>
+    <t>Lanjutkan</t>
+  </si>
+  <si>
+    <t>Magpatuloy</t>
+  </si>
+  <si>
+    <t>Devam Et</t>
+  </si>
+  <si>
+    <t>เล่นต่อ</t>
+  </si>
+  <si>
     <t>SettingPageUIForm.privacy</t>
   </si>
   <si>
@@ -1218,6 +1722,18 @@
     <t>छोड़ें</t>
   </si>
   <si>
+    <t>Keluar</t>
+  </si>
+  <si>
+    <t>Umalis</t>
+  </si>
+  <si>
+    <t>Çık</t>
+  </si>
+  <si>
+    <t>ออก</t>
+  </si>
+  <si>
     <t>TaskItem.infoTxt</t>
   </si>
   <si>
@@ -1245,6 +1761,18 @@
     <t>{0} स्तर जीतें!</t>
   </si>
   <si>
+    <t>Selesaikan {0} level!</t>
+  </si>
+  <si>
+    <t>Ipasa ang {0} antas!</t>
+  </si>
+  <si>
+    <t>{0} bölüm geç!</t>
+  </si>
+  <si>
+    <t>ผ่านให้ได้ {0} ด่าน!</t>
+  </si>
+  <si>
     <t>MakeupRecordUIForm.title</t>
   </si>
   <si>
@@ -1272,6 +1800,18 @@
     <t>अतिरिक्त जीवन</t>
   </si>
   <si>
+    <t>Nyawa Tambahan</t>
+  </si>
+  <si>
+    <t>Mga Dagdag na Buhay</t>
+  </si>
+  <si>
+    <t>Ek Canlar</t>
+  </si>
+  <si>
+    <t>ชีวิตเพิ่มเติม</t>
+  </si>
+  <si>
     <t>AddPropUIForm.titleTxt</t>
   </si>
   <si>
@@ -1299,6 +1839,12 @@
     <t>रॉकेट</t>
   </si>
   <si>
+    <t>Roket</t>
+  </si>
+  <si>
+    <t>จรวด</t>
+  </si>
+  <si>
     <t>PlayLoadingUIForm.loading</t>
   </si>
   <si>
@@ -1326,6 +1872,18 @@
     <t>लोड हो रहा है...</t>
   </si>
   <si>
+    <t>Memuat...</t>
+  </si>
+  <si>
+    <t>Naglo-load...</t>
+  </si>
+  <si>
+    <t>Yükleniyor...</t>
+  </si>
+  <si>
+    <t>กำลังโหลด...</t>
+  </si>
+  <si>
     <t>QuitConfirmUIForm.quit</t>
   </si>
   <si>
@@ -1353,6 +1911,18 @@
     <t>अवतार चुनें:</t>
   </si>
   <si>
+    <t>Pilih avatar:</t>
+  </si>
+  <si>
+    <t>Pumili ng avatar:</t>
+  </si>
+  <si>
+    <t>Bir avatar seçin:</t>
+  </si>
+  <si>
+    <t>เลือกอวาตาร์:</t>
+  </si>
+  <si>
     <t>MakeupInfoUIForm.enterDesc</t>
   </si>
   <si>
@@ -1371,6 +1941,15 @@
     <t>अपना PayPal खाता दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan akun PayPal Anda</t>
+  </si>
+  <si>
+    <t>Ilagay ang iyong PayPal account</t>
+  </si>
+  <si>
+    <t>กรอกบัญชี PayPal ของคุณ</t>
+  </si>
+  <si>
     <t>MakeupInfoUIForm.enterAgainDesc</t>
   </si>
   <si>
@@ -1398,6 +1977,18 @@
     <t>PayPal खाता फिर से दर्ज करें</t>
   </si>
   <si>
+    <t>Masukkan kembali akun PayPal</t>
+  </si>
+  <si>
+    <t>Ilagay muli ang PayPal account</t>
+  </si>
+  <si>
+    <t>PayPal hesabınızı tekrar girin</t>
+  </si>
+  <si>
+    <t>กรอกบัญชี PayPal อีกครั้ง</t>
+  </si>
+  <si>
     <t>MakeupInfoUIForm.confirm</t>
   </si>
   <si>
@@ -1419,6 +2010,18 @@
     <t>पुष्टि करें</t>
   </si>
   <si>
+    <t>Konfirmasi</t>
+  </si>
+  <si>
+    <t>Kumpirmahin</t>
+  </si>
+  <si>
+    <t>Onayla</t>
+  </si>
+  <si>
+    <t>ยืนยัน</t>
+  </si>
+  <si>
     <t>TaskItem.adTxt</t>
   </si>
   <si>
@@ -1446,6 +2049,18 @@
     <t>विज्ञापन देखें!</t>
   </si>
   <si>
+    <t>Tonton iklan!</t>
+  </si>
+  <si>
+    <t>Manood ng ad!</t>
+  </si>
+  <si>
+    <t>Reklam izle!</t>
+  </si>
+  <si>
+    <t>ดูโฆษณา!</t>
+  </si>
+  <si>
     <t>free</t>
   </si>
   <si>
@@ -1470,6 +2085,15 @@
     <t>मुफ़्त</t>
   </si>
   <si>
+    <t>Libre</t>
+  </si>
+  <si>
+    <t>Ücretsiz</t>
+  </si>
+  <si>
+    <t>ฟรี</t>
+  </si>
+  <si>
     <t>TaskItem.go</t>
   </si>
   <si>
@@ -1491,6 +2115,18 @@
     <t>जाएँ</t>
   </si>
   <si>
+    <t>Mulai</t>
+  </si>
+  <si>
+    <t>Pumunta</t>
+  </si>
+  <si>
+    <t>Git</t>
+  </si>
+  <si>
+    <t>ไป</t>
+  </si>
+  <si>
     <t>cashoutHint</t>
   </si>
   <si>
@@ -1518,6 +2154,18 @@
     <t>इसे प्राप्त करने के लिए आपको {0} स्तर पार करने होंगे और अपना बैलेंस {1} तक पहुँचाना होगा।</t>
   </si>
   <si>
+    <t>Anda harus menyelesaikan {0} level dan mengumpulkan saldo sebesar {1} sebelum dapat mengklaimnya.</t>
+  </si>
+  <si>
+    <t>Kailangan mong ipasa ang {0} antas at makaipon ng balanseng {1} bago mo ito makuha.</t>
+  </si>
+  <si>
+    <t>Ödülü almak için {0} bölüm geçmeli ve bakiyeni {1} tutarına ulaştırmalısın.</t>
+  </si>
+  <si>
+    <t>คุณต้องผ่าน {0} ด่านและสะสมยอดคงเหลือให้ถึง {1} จึงจะรับได้</t>
+  </si>
+  <si>
     <t>MakeupItem.cashout</t>
   </si>
   <si>
@@ -1548,6 +2196,18 @@
     <t>गोले खत्म होने से पहले सभी वस्तुएँ हटाएँ!</t>
   </si>
   <si>
+    <t>Hancurkan semua benda sebelum tembakan habis!</t>
+  </si>
+  <si>
+    <t>Alisin ang lahat ng bagay bago maubos ang iyong mga bala!</t>
+  </si>
+  <si>
+    <t>Atışların bitmeden tüm nesneleri temizle!</t>
+  </si>
+  <si>
+    <t>กำจัดวัตถุทั้งหมดก่อนกระสุนจะหมด!</t>
+  </si>
+  <si>
     <t>MakeupRecordItem.bouns</t>
   </si>
   <si>
@@ -1575,6 +2235,18 @@
     <t>आज की कुल पुरस्कार राशि</t>
   </si>
   <si>
+    <t>Total Hadiah Hari Ini</t>
+  </si>
+  <si>
+    <t>Kabuuang Premyo Ngayon</t>
+  </si>
+  <si>
+    <t>Bugünün Ödül Havuzu</t>
+  </si>
+  <si>
+    <t>เงินรางวัลรวมวันนี้</t>
+  </si>
+  <si>
     <t>PlayUIForm.txtHint</t>
   </si>
   <si>
@@ -1602,6 +2274,18 @@
     <t>मेज़ पर रखी वस्तुओं पर टैप करें</t>
   </si>
   <si>
+    <t>Ketuk benda-benda di atas meja</t>
+  </si>
+  <si>
+    <t>I-tap ang mga bagay sa mesa</t>
+  </si>
+  <si>
+    <t>Masanın üzerindeki nesnelere dokun</t>
+  </si>
+  <si>
+    <t>แตะวัตถุบนโต๊ะ</t>
+  </si>
+  <si>
     <t>MakeupItem.reach</t>
   </si>
   <si>
@@ -1626,6 +2310,18 @@
     <t>आवश्यक बैलेंस</t>
   </si>
   <si>
+    <t>Saldo yang Diperlukan</t>
+  </si>
+  <si>
+    <t>Kinakailangang Balanse</t>
+  </si>
+  <si>
+    <t>Gerekli Bakiye</t>
+  </si>
+  <si>
+    <t>ยอดคงเหลือที่ต้องมี</t>
+  </si>
+  <si>
     <t>PrelevelUIForm.desc</t>
   </si>
   <si>
@@ -1650,6 +2346,18 @@
     <t>बूस्टर चुनें:</t>
   </si>
   <si>
+    <t>Pilih Booster:</t>
+  </si>
+  <si>
+    <t>Pumili ng Booster:</t>
+  </si>
+  <si>
+    <t>Güçlendirici Seç:</t>
+  </si>
+  <si>
+    <t>เลือกบูสเตอร์:</t>
+  </si>
+  <si>
     <t>MakeupPaymentEndUIForm.desc</t>
   </si>
   <si>
@@ -1677,6 +2385,18 @@
     <t>आपके उदार दान के लिए धन्यवाद!</t>
   </si>
   <si>
+    <t>Terima kasih atas donasi Anda yang murah hati!</t>
+  </si>
+  <si>
+    <t>Salamat sa iyong bukas-palad na donasyon!</t>
+  </si>
+  <si>
+    <t>Cömert bağışınız için teşekkür ederiz!</t>
+  </si>
+  <si>
+    <t>ขอบคุณสำหรับการบริจาคอันเอื้อเฟื้อของคุณ!</t>
+  </si>
+  <si>
     <t>giftHint</t>
   </si>
   <si>
@@ -1704,19 +2424,31 @@
     <t>खज़ाने के संदूक इकट्ठा करें</t>
   </si>
   <si>
+    <t>Kumpulkan peti harta karun</t>
+  </si>
+  <si>
+    <t>Mangolekta ng mga kaban ng kayamanan</t>
+  </si>
+  <si>
+    <t>Hazine sandıkları topla</t>
+  </si>
+  <si>
+    <t>สะสมหีบสมบัติ</t>
+  </si>
+  <si>
     <t>Version</t>
   </si>
   <si>
     <t>SourceLanguage</t>
   </si>
   <si>
-    <t>English,PortugueseBrazil,PortuguesePortugal,Spanish,French,Russian,Japanese,Hindi</t>
+    <t>English,PortugueseBrazil,PortuguesePortugal,Spanish,French,Russian,Japanese,Hindi,Indonesian,Filipino,Turkish,Thai</t>
   </si>
   <si>
     <t>Keys (do not edit)</t>
   </si>
   <si>
-    <t>efad80e27375404ca19bd9002a7089ae</t>
+    <t>87714c572956488a960623fed022bf42</t>
   </si>
   <si>
     <t>请在 Translations 工作表填写译文；可以整行排序，不要单独排序某一列。</t>
@@ -2909,18 +3641,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M70"/>
+  <dimension ref="A1:Q70"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" style="3" hidden="1" customWidth="1"/>
-    <col min="2" max="10" width="28" style="3" customWidth="1"/>
-    <col min="11" max="11" width="12" style="3" customWidth="1"/>
-    <col min="12" max="12" width="8" style="3" customWidth="1"/>
-    <col min="13" max="13" width="28" style="3" hidden="1" customWidth="1"/>
-    <col min="14" max="16384" width="9.14285714285714" style="3" customWidth="1"/>
+    <col min="2" max="14" width="28" style="3" customWidth="1"/>
+    <col min="15" max="15" width="12" style="3" customWidth="1"/>
+    <col min="16" max="16" width="8" style="3" customWidth="1"/>
+    <col min="17" max="17" width="28" style="3" hidden="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.14285714285714" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:13">
+    <row r="1" s="2" customFormat="1" spans="1:17">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -2960,2842 +3692,3682 @@
       <c r="M1" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" ht="16.5" spans="1:13">
+      <c r="N1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" ht="16.5" spans="1:17">
       <c r="A2" s="3" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="L2" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P2" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q2" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M2" s="3" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="3" ht="16.5" spans="1:13">
+    </row>
+    <row r="3" ht="16.5" spans="1:17">
       <c r="A3" s="3" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="F3" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="N3" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="O3" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="P3" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="I3" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" ht="30" spans="1:13">
+      <c r="Q3" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" ht="30" spans="1:17">
       <c r="A4" s="3" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>32</v>
+        <v>43</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>22</v>
+        <v>52</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="5" ht="30" spans="1:13">
+        <v>53</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="5" ht="30" spans="1:17">
       <c r="A5" s="3" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>41</v>
+        <v>56</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>42</v>
+        <v>57</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P5" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q5" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" ht="16.5" spans="1:17">
+      <c r="A6" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F6" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N6" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O6" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q6" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="7" ht="16.5" spans="1:17">
+      <c r="A7" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="M7" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="N7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q7" s="3" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="8" ht="16.5" spans="1:17">
+      <c r="A8" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="J8" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O8" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P8" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q8" s="3" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="9" ht="16.5" spans="1:17">
+      <c r="A9" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G9" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="H9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I9" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="J9" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K9" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M9" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P9" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q9" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="10" ht="45" spans="1:17">
+      <c r="A10" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="M10" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P10" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q10" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="11" ht="16.5" spans="1:17">
+      <c r="A11" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="I11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="M11" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="N11" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q11" s="3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" ht="16.5" spans="1:17">
+      <c r="A12" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="G12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="N12" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O12" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P12" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q12" s="3" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" ht="16.5" spans="1:17">
+      <c r="A13" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="G13" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I13" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="M13" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O13" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P13" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q13" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="14" ht="16.5" spans="1:17">
+      <c r="A14" s="3" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C14" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="M14" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="N14" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q14" s="3" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="15" ht="30" spans="1:17">
+      <c r="A15" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F15" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="G15" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="M15" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="N15" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O15" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P15" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q15" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="16" ht="16.5" spans="1:17">
+      <c r="A16" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="M16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="N16" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P16" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q16" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="17" ht="16.5" spans="1:17">
+      <c r="A17" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F17" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G17" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="M17" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="N17" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O17" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P17" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q17" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="18" ht="33" spans="1:17">
+      <c r="A18" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>198</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="F18" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="G18" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="H18" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I18" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>205</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="M18" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="N18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P18" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q18" s="3" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" ht="16.5" spans="1:17">
+      <c r="A19" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="F19" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G19" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="H19" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="I19" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="M19" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="N19" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P19" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q19" s="3" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="20" ht="16.5" spans="1:17">
+      <c r="A20" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="D20" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="F20" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="G20" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="H20" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I20" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="J20" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="K20" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="M20" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="N20" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O20" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q20" s="3" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" ht="16.5" spans="1:17">
+      <c r="A21" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="F21" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="G21" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="H21" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="I21" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J21" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="K21" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="L21" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="M21" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="N21" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O21" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P21" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q21" s="3" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="22" ht="30" spans="1:17">
+      <c r="A22" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="H22" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="I22" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="M22" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="N22" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O22" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P22" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q22" s="3" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" ht="28.5" spans="1:17">
+      <c r="A23" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="F23" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="G23" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="H23" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="I23" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="J23" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="M23" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="N23" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O23" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P23" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q23" s="3" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="24" ht="45" spans="1:17">
+      <c r="A24" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>271</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>274</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="G24" s="3" t="s">
+        <v>276</v>
+      </c>
+      <c r="H24" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="I24" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>279</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>280</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>281</v>
+      </c>
+      <c r="M24" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="N24" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O24" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P24" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q24" s="3" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="25" ht="30" spans="1:17">
+      <c r="A25" s="3" t="s">
+        <v>283</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>285</v>
+      </c>
+      <c r="D25" s="3" t="s">
+        <v>286</v>
+      </c>
+      <c r="E25" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="F25" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>288</v>
+      </c>
+      <c r="H25" s="3" t="s">
+        <v>289</v>
+      </c>
+      <c r="I25" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="M25" s="3" t="s">
+        <v>294</v>
+      </c>
+      <c r="N25" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O25" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P25" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q25" s="3" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="26" ht="30" spans="1:17">
+      <c r="A26" s="3" t="s">
+        <v>295</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C26" s="3" t="s">
+        <v>297</v>
+      </c>
+      <c r="D26" s="3" t="s">
+        <v>298</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="F26" s="3" t="s">
+        <v>300</v>
+      </c>
+      <c r="G26" s="3" t="s">
+        <v>301</v>
+      </c>
+      <c r="H26" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="I26" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="J26" s="3" t="s">
+        <v>304</v>
+      </c>
+      <c r="K26" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="L26" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="M26" s="3" t="s">
+        <v>307</v>
+      </c>
+      <c r="N26" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O26" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P26" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q26" s="3" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="27" ht="30" spans="1:17">
+      <c r="A27" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>310</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>311</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="F27" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="G27" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="H27" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="I27" s="3" t="s">
+        <v>316</v>
+      </c>
+      <c r="J27" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="K27" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="L27" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="M27" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="N27" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O27" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P27" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q27" s="3" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="28" ht="33" spans="1:17">
+      <c r="A28" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>323</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>325</v>
+      </c>
+      <c r="F28" s="3" t="s">
+        <v>326</v>
+      </c>
+      <c r="G28" s="3" t="s">
+        <v>327</v>
+      </c>
+      <c r="H28" s="3" t="s">
+        <v>328</v>
+      </c>
+      <c r="I28" s="3" t="s">
+        <v>329</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>331</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>332</v>
+      </c>
+      <c r="M28" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="N28" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O28" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P28" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q28" s="3" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="29" ht="16.5" spans="1:17">
+      <c r="A29" s="3" t="s">
+        <v>334</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>336</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>337</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>338</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>339</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>340</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>341</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>342</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>335</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>344</v>
+      </c>
+      <c r="M29" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="N29" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O29" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P29" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q29" s="3" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="30" ht="30" spans="1:17">
+      <c r="A30" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="F30" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="G30" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="H30" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="I30" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="M30" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="N30" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O30" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P30" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q30" s="3" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="31" ht="16.5" spans="1:17">
+      <c r="A31" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="C31" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="D31" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E31" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="F31" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="H31" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="I31" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>369</v>
+      </c>
+      <c r="M31" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="N31" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O31" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P31" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q31" s="3" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="32" ht="30" spans="1:17">
+      <c r="A32" s="3" t="s">
+        <v>371</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>374</v>
+      </c>
+      <c r="E32" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="F32" s="3" t="s">
+        <v>376</v>
+      </c>
+      <c r="G32" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="I32" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="J32" s="3" t="s">
+        <v>380</v>
+      </c>
+      <c r="K32" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="L32" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="M32" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="N32" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O32" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P32" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q32" s="3" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="33" ht="49.5" spans="1:17">
+      <c r="A33" s="3" t="s">
+        <v>384</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>386</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="E33" s="3" t="s">
+        <v>388</v>
+      </c>
+      <c r="F33" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="G33" s="3" t="s">
+        <v>390</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="I33" s="3" t="s">
+        <v>392</v>
+      </c>
+      <c r="J33" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="K33" s="3" t="s">
+        <v>394</v>
+      </c>
+      <c r="L33" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="M33" s="3" t="s">
+        <v>396</v>
+      </c>
+      <c r="N33" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O33" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P33" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q33" s="3" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="34" ht="33" spans="1:17">
+      <c r="A34" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>398</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>399</v>
+      </c>
+      <c r="D34" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="E34" s="3" t="s">
+        <v>401</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>403</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>405</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="K34" s="3" t="s">
+        <v>407</v>
+      </c>
+      <c r="L34" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="M34" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="N34" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O34" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P34" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="35" ht="16.5" spans="1:17">
+      <c r="A35" s="3" t="s">
+        <v>410</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="D35" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="E35" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="F35" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="G35" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="H35" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="I35" s="3" t="s">
+        <v>418</v>
+      </c>
+      <c r="J35" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="K35" s="3" t="s">
+        <v>420</v>
+      </c>
+      <c r="L35" s="3" t="s">
+        <v>421</v>
+      </c>
+      <c r="M35" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="N35" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O35" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P35" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="36" ht="30" spans="1:17">
+      <c r="A36" s="3" t="s">
+        <v>423</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>425</v>
+      </c>
+      <c r="D36" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="E36" s="3" t="s">
+        <v>427</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="G36" s="3" t="s">
+        <v>429</v>
+      </c>
+      <c r="H36" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="I36" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="J36" s="3" t="s">
+        <v>432</v>
+      </c>
+      <c r="K36" s="3" t="s">
+        <v>433</v>
+      </c>
+      <c r="L36" s="3" t="s">
+        <v>434</v>
+      </c>
+      <c r="M36" s="3" t="s">
+        <v>435</v>
+      </c>
+      <c r="N36" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O36" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P36" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="37" ht="33" spans="1:17">
+      <c r="A37" s="3" t="s">
+        <v>436</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>437</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>438</v>
+      </c>
+      <c r="D37" s="3" t="s">
+        <v>439</v>
+      </c>
+      <c r="E37" s="3" t="s">
+        <v>440</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>441</v>
+      </c>
+      <c r="G37" s="3" t="s">
+        <v>442</v>
+      </c>
+      <c r="H37" s="3" t="s">
+        <v>443</v>
+      </c>
+      <c r="I37" s="3" t="s">
+        <v>444</v>
+      </c>
+      <c r="J37" s="3" t="s">
+        <v>445</v>
+      </c>
+      <c r="K37" s="3" t="s">
+        <v>446</v>
+      </c>
+      <c r="L37" s="3" t="s">
+        <v>447</v>
+      </c>
+      <c r="M37" s="3" t="s">
+        <v>448</v>
+      </c>
+      <c r="N37" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P37" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="38" ht="33" spans="1:17">
+      <c r="A38" s="3" t="s">
+        <v>449</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>450</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>451</v>
+      </c>
+      <c r="D38" s="3" t="s">
+        <v>452</v>
+      </c>
+      <c r="E38" s="3" t="s">
+        <v>453</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>454</v>
+      </c>
+      <c r="G38" s="3" t="s">
+        <v>455</v>
+      </c>
+      <c r="H38" s="3" t="s">
+        <v>456</v>
+      </c>
+      <c r="I38" s="3" t="s">
+        <v>457</v>
+      </c>
+      <c r="J38" s="3" t="s">
+        <v>458</v>
+      </c>
+      <c r="K38" s="3" t="s">
+        <v>459</v>
+      </c>
+      <c r="L38" s="3" t="s">
+        <v>460</v>
+      </c>
+      <c r="M38" s="3" t="s">
+        <v>461</v>
+      </c>
+      <c r="N38" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P38" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="39" ht="16.5" spans="1:17">
+      <c r="A39" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>464</v>
+      </c>
+      <c r="D39" s="3" t="s">
+        <v>465</v>
+      </c>
+      <c r="E39" s="3" t="s">
+        <v>466</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>467</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>468</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>469</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>470</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>471</v>
+      </c>
+      <c r="K39" s="3" t="s">
+        <v>472</v>
+      </c>
+      <c r="L39" s="3" t="s">
+        <v>473</v>
+      </c>
+      <c r="M39" s="3" t="s">
+        <v>474</v>
+      </c>
+      <c r="N39" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O39" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P39" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="40" ht="16.5" spans="1:17">
+      <c r="A40" s="3" t="s">
+        <v>475</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="E40" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K40" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="L40" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="M40" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="N40" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O40" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P40" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q40" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="41" ht="16.5" spans="1:17">
+      <c r="A41" s="3" t="s">
+        <v>487</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>488</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="E41" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>492</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="K41" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="L41" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="M41" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="N41" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O41" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P41" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q41" s="3" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="42" ht="16.5" spans="1:17">
+      <c r="A42" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="E42" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>500</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="K42" s="3" t="s">
+        <v>501</v>
+      </c>
+      <c r="L42" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="M42" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="N42" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O42" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P42" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q42" s="3" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="43" ht="45" spans="1:17">
+      <c r="A43" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>506</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="E43" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>512</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>513</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>514</v>
+      </c>
+      <c r="L43" s="3" t="s">
+        <v>515</v>
+      </c>
+      <c r="M43" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="N43" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P43" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q43" s="3" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="44" ht="45" spans="1:17">
+      <c r="A44" s="3" t="s">
+        <v>517</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>518</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>519</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>520</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>521</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>522</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>523</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>524</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>525</v>
+      </c>
+      <c r="K44" s="3" t="s">
+        <v>526</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>527</v>
+      </c>
+      <c r="M44" s="3" t="s">
+        <v>528</v>
+      </c>
+      <c r="N44" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O44" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q44" s="3" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="45" ht="16.5" spans="1:17">
+      <c r="A45" s="3" t="s">
+        <v>529</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>530</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>532</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>535</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>537</v>
+      </c>
+      <c r="K45" s="3" t="s">
+        <v>538</v>
+      </c>
+      <c r="L45" s="3" t="s">
+        <v>539</v>
+      </c>
+      <c r="M45" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="N45" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O45" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P45" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q45" s="3" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="46" ht="16.5" spans="1:17">
+      <c r="A46" s="3" t="s">
+        <v>541</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>542</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="E46" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="F46" s="3" t="s">
+        <v>544</v>
+      </c>
+      <c r="G46" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="H46" s="3" t="s">
+        <v>546</v>
+      </c>
+      <c r="I46" s="3" t="s">
+        <v>547</v>
+      </c>
+      <c r="J46" s="3" t="s">
+        <v>548</v>
+      </c>
+      <c r="K46" s="3" t="s">
+        <v>549</v>
+      </c>
+      <c r="L46" s="3" t="s">
+        <v>550</v>
+      </c>
+      <c r="M46" s="3" t="s">
+        <v>551</v>
+      </c>
+      <c r="N46" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O46" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P46" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q46" s="3" t="s">
+        <v>542</v>
+      </c>
+    </row>
+    <row r="47" ht="30" spans="1:17">
+      <c r="A47" s="3" t="s">
+        <v>552</v>
+      </c>
+      <c r="B47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="C47" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="D47" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="E47" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="F47" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="G47" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="J5" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M5" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" ht="16.5" spans="1:13">
-      <c r="A6" s="3" t="s">
+      <c r="H47" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="I47" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="J47" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E6" s="3" t="s">
+      <c r="K47" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="L47" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="M47" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="H6" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M6" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" ht="16.5" spans="1:13">
-      <c r="A7" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="G7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M7" s="3" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="8" ht="16.5" spans="1:13">
-      <c r="A8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" ht="16.5" spans="1:13">
-      <c r="A9" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H9" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I9" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M9" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="10" ht="45" spans="1:13">
-      <c r="A10" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="H10" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M10" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" ht="16.5" spans="1:13">
-      <c r="A11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="E11" s="3" t="s">
+      <c r="N47" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O47" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P47" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q47" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="G11" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="H11" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="I11" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M11" s="3" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="12" ht="16.5" spans="1:13">
-      <c r="A12" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="G12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="H12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M12" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" ht="16.5" spans="1:13">
-      <c r="A13" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="G13" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="H13" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M13" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="14" ht="16.5" spans="1:13">
-      <c r="A14" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="C14" s="3" t="s">
+    </row>
+    <row r="48" ht="16.5" spans="1:17">
+      <c r="A48" s="3" t="s">
+        <v>553</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E48" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F48" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G48" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="H48" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="I48" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J48" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="M48" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="N48" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O48" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P48" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q48" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="49" ht="28.5" spans="1:17">
+      <c r="A49" s="3" t="s">
+        <v>565</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>566</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>567</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>568</v>
+      </c>
+      <c r="E49" s="3" t="s">
+        <v>569</v>
+      </c>
+      <c r="F49" s="3" t="s">
+        <v>570</v>
+      </c>
+      <c r="G49" s="3" t="s">
+        <v>571</v>
+      </c>
+      <c r="H49" s="3" t="s">
+        <v>572</v>
+      </c>
+      <c r="I49" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="J49" s="3" t="s">
+        <v>574</v>
+      </c>
+      <c r="K49" s="3" t="s">
+        <v>575</v>
+      </c>
+      <c r="L49" s="3" t="s">
+        <v>576</v>
+      </c>
+      <c r="M49" s="3" t="s">
+        <v>577</v>
+      </c>
+      <c r="N49" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O49" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P49" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q49" s="3" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="50" ht="16.5" spans="1:17">
+      <c r="A50" s="3" t="s">
+        <v>578</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>476</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>477</v>
+      </c>
+      <c r="E50" s="3" t="s">
+        <v>478</v>
+      </c>
+      <c r="F50" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="G50" s="3" t="s">
+        <v>480</v>
+      </c>
+      <c r="H50" s="3" t="s">
+        <v>481</v>
+      </c>
+      <c r="I50" s="3" t="s">
+        <v>482</v>
+      </c>
+      <c r="J50" s="3" t="s">
+        <v>483</v>
+      </c>
+      <c r="K50" s="3" t="s">
+        <v>484</v>
+      </c>
+      <c r="L50" s="3" t="s">
+        <v>485</v>
+      </c>
+      <c r="M50" s="3" t="s">
+        <v>486</v>
+      </c>
+      <c r="N50" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O50" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P50" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q50" s="3" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="51" ht="16.5" spans="1:17">
+      <c r="A51" s="3" t="s">
+        <v>579</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>580</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>581</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="E51" s="3" t="s">
+        <v>582</v>
+      </c>
+      <c r="F51" s="3" t="s">
+        <v>583</v>
+      </c>
+      <c r="G51" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="H51" s="3" t="s">
+        <v>585</v>
+      </c>
+      <c r="I51" s="3" t="s">
+        <v>586</v>
+      </c>
+      <c r="J51" s="3" t="s">
+        <v>587</v>
+      </c>
+      <c r="K51" s="3" t="s">
+        <v>588</v>
+      </c>
+      <c r="L51" s="3" t="s">
+        <v>589</v>
+      </c>
+      <c r="M51" s="3" t="s">
+        <v>590</v>
+      </c>
+      <c r="N51" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O51" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P51" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q51" s="3" t="s">
+        <v>580</v>
+      </c>
+    </row>
+    <row r="52" ht="16.5" spans="1:17">
+      <c r="A52" s="3" t="s">
+        <v>591</v>
+      </c>
+      <c r="B52" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>593</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>594</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>595</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>596</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>597</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>598</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>599</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="K52" s="3" t="s">
+        <v>592</v>
+      </c>
+      <c r="L52" s="3" t="s">
+        <v>600</v>
+      </c>
+      <c r="M52" s="3" t="s">
+        <v>601</v>
+      </c>
+      <c r="N52" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O52" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P52" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q52" s="3" t="s">
+        <v>592</v>
+      </c>
+    </row>
+    <row r="53" ht="16.5" spans="1:17">
+      <c r="A53" s="3" t="s">
+        <v>602</v>
+      </c>
+      <c r="B53" s="3" t="s">
+        <v>603</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>604</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>605</v>
+      </c>
+      <c r="E53" s="3" t="s">
+        <v>606</v>
+      </c>
+      <c r="F53" s="3" t="s">
+        <v>607</v>
+      </c>
+      <c r="G53" s="3" t="s">
+        <v>608</v>
+      </c>
+      <c r="H53" s="3" t="s">
+        <v>609</v>
+      </c>
+      <c r="I53" s="3" t="s">
+        <v>610</v>
+      </c>
+      <c r="J53" s="3" t="s">
+        <v>611</v>
+      </c>
+      <c r="K53" s="3" t="s">
+        <v>612</v>
+      </c>
+      <c r="L53" s="3" t="s">
+        <v>613</v>
+      </c>
+      <c r="M53" s="3" t="s">
+        <v>614</v>
+      </c>
+      <c r="N53" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O53" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P53" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q53" s="3" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="54" ht="16.5" spans="1:17">
+      <c r="A54" s="3" t="s">
+        <v>615</v>
+      </c>
+      <c r="B54" s="3" t="s">
+        <v>554</v>
+      </c>
+      <c r="C54" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="D54" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="E54" s="3" t="s">
+        <v>556</v>
+      </c>
+      <c r="F54" s="3" t="s">
+        <v>557</v>
+      </c>
+      <c r="G54" s="3" t="s">
+        <v>558</v>
+      </c>
+      <c r="H54" s="3" t="s">
+        <v>559</v>
+      </c>
+      <c r="I54" s="3" t="s">
+        <v>560</v>
+      </c>
+      <c r="J54" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="K54" s="3" t="s">
+        <v>562</v>
+      </c>
+      <c r="L54" s="3" t="s">
+        <v>563</v>
+      </c>
+      <c r="M54" s="3" t="s">
+        <v>564</v>
+      </c>
+      <c r="N54" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P54" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q54" s="3" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="55" ht="16.5" spans="1:17">
+      <c r="A55" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="B55" s="3" t="s">
+        <v>617</v>
+      </c>
+      <c r="C55" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="D55" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="E55" s="3" t="s">
+        <v>619</v>
+      </c>
+      <c r="F55" s="3" t="s">
+        <v>620</v>
+      </c>
+      <c r="G55" s="3" t="s">
+        <v>621</v>
+      </c>
+      <c r="H55" s="3" t="s">
+        <v>622</v>
+      </c>
+      <c r="I55" s="3" t="s">
+        <v>623</v>
+      </c>
+      <c r="J55" s="3" t="s">
+        <v>624</v>
+      </c>
+      <c r="K55" s="3" t="s">
+        <v>625</v>
+      </c>
+      <c r="L55" s="3" t="s">
+        <v>626</v>
+      </c>
+      <c r="M55" s="3" t="s">
+        <v>627</v>
+      </c>
+      <c r="N55" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O55" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P55" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q55" s="3" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="56" ht="30" spans="1:17">
+      <c r="A56" s="3" t="s">
+        <v>628</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>629</v>
+      </c>
+      <c r="C56" s="3" t="s">
+        <v>630</v>
+      </c>
+      <c r="D56" s="3" t="s">
+        <v>631</v>
+      </c>
+      <c r="E56" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F56" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="G56" s="3" t="s">
+        <v>632</v>
+      </c>
+      <c r="H56" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="I56" s="3" t="s">
+        <v>633</v>
+      </c>
+      <c r="J56" s="3" t="s">
+        <v>634</v>
+      </c>
+      <c r="K56" s="3" t="s">
+        <v>635</v>
+      </c>
+      <c r="L56" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="M56" s="3" t="s">
+        <v>636</v>
+      </c>
+      <c r="N56" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O56" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P56" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q56" s="3" t="s">
+        <v>629</v>
+      </c>
+    </row>
+    <row r="57" ht="30" spans="1:17">
+      <c r="A57" s="3" t="s">
+        <v>637</v>
+      </c>
+      <c r="B57" s="3" t="s">
+        <v>638</v>
+      </c>
+      <c r="C57" s="3" t="s">
+        <v>639</v>
+      </c>
+      <c r="D57" s="3" t="s">
+        <v>640</v>
+      </c>
+      <c r="E57" s="3" t="s">
+        <v>641</v>
+      </c>
+      <c r="F57" s="3" t="s">
+        <v>642</v>
+      </c>
+      <c r="G57" s="3" t="s">
+        <v>643</v>
+      </c>
+      <c r="H57" s="3" t="s">
+        <v>644</v>
+      </c>
+      <c r="I57" s="3" t="s">
+        <v>645</v>
+      </c>
+      <c r="J57" s="3" t="s">
+        <v>646</v>
+      </c>
+      <c r="K57" s="3" t="s">
+        <v>647</v>
+      </c>
+      <c r="L57" s="3" t="s">
+        <v>648</v>
+      </c>
+      <c r="M57" s="3" t="s">
+        <v>649</v>
+      </c>
+      <c r="N57" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O57" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P57" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q57" s="3" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="58" ht="16.5" spans="1:17">
+      <c r="A58" s="3" t="s">
+        <v>650</v>
+      </c>
+      <c r="B58" s="3" t="s">
+        <v>651</v>
+      </c>
+      <c r="C58" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="D58" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="E58" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="F58" s="3" t="s">
+        <v>653</v>
+      </c>
+      <c r="G58" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="H58" s="3" t="s">
+        <v>655</v>
+      </c>
+      <c r="I58" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="J58" s="3" t="s">
+        <v>657</v>
+      </c>
+      <c r="K58" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="L58" s="3" t="s">
+        <v>659</v>
+      </c>
+      <c r="M58" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="N58" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O58" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P58" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q58" s="3" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="59" ht="16.5" spans="1:17">
+      <c r="A59" s="3" t="s">
+        <v>661</v>
+      </c>
+      <c r="B59" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>663</v>
+      </c>
+      <c r="D59" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="E59" s="3" t="s">
+        <v>665</v>
+      </c>
+      <c r="F59" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="G59" s="3" t="s">
+        <v>667</v>
+      </c>
+      <c r="H59" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="I59" s="3" t="s">
+        <v>669</v>
+      </c>
+      <c r="J59" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="K59" s="3" t="s">
+        <v>671</v>
+      </c>
+      <c r="L59" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="M59" s="3" t="s">
+        <v>673</v>
+      </c>
+      <c r="N59" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O59" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P59" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q59" s="3" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="60" ht="16.5" spans="1:17">
+      <c r="A60" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B60" s="3" t="s">
+        <v>675</v>
+      </c>
+      <c r="C60" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="D60" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="E60" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="F60" s="3" t="s">
+        <v>678</v>
+      </c>
+      <c r="G60" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="H60" s="3" t="s">
+        <v>680</v>
+      </c>
+      <c r="I60" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="J60" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="K60" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="L60" s="3" t="s">
+        <v>683</v>
+      </c>
+      <c r="M60" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="N60" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O60" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P60" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q60" s="3" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="61" ht="16.5" spans="1:17">
+      <c r="A61" s="3" t="s">
+        <v>685</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="C61" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="D61" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="E61" s="3" t="s">
+        <v>687</v>
+      </c>
+      <c r="F61" s="3" t="s">
+        <v>688</v>
+      </c>
+      <c r="G61" s="3" t="s">
+        <v>689</v>
+      </c>
+      <c r="H61" s="3" t="s">
+        <v>690</v>
+      </c>
+      <c r="I61" s="3" t="s">
+        <v>691</v>
+      </c>
+      <c r="J61" s="3" t="s">
+        <v>692</v>
+      </c>
+      <c r="K61" s="3" t="s">
+        <v>693</v>
+      </c>
+      <c r="L61" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="M61" s="3" t="s">
+        <v>695</v>
+      </c>
+      <c r="N61" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O61" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P61" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q61" s="3" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="62" ht="60" spans="1:17">
+      <c r="A62" s="3" t="s">
+        <v>696</v>
+      </c>
+      <c r="B62" s="3" t="s">
+        <v>697</v>
+      </c>
+      <c r="C62" s="3" t="s">
+        <v>698</v>
+      </c>
+      <c r="D62" s="3" t="s">
+        <v>699</v>
+      </c>
+      <c r="E62" s="3" t="s">
+        <v>700</v>
+      </c>
+      <c r="F62" s="3" t="s">
+        <v>701</v>
+      </c>
+      <c r="G62" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="H62" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="I62" s="3" t="s">
+        <v>704</v>
+      </c>
+      <c r="J62" s="3" t="s">
+        <v>705</v>
+      </c>
+      <c r="K62" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="L62" s="3" t="s">
+        <v>707</v>
+      </c>
+      <c r="M62" s="3" t="s">
+        <v>708</v>
+      </c>
+      <c r="N62" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O62" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P62" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q62" s="3" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="63" ht="16.5" spans="1:17">
+      <c r="A63" s="3" t="s">
+        <v>709</v>
+      </c>
+      <c r="B63" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="C63" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="E14" s="3" t="s">
+      <c r="D63" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="E63" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="F63" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="G63" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="H63" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M14" s="3" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="15" ht="30" spans="1:13">
-      <c r="A15" s="3" t="s">
+      <c r="I63" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="J63" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="K63" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="3" t="s">
+      <c r="L63" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="F15" s="3" t="s">
+      <c r="M63" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>118</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="16" ht="16.5" spans="1:13">
-      <c r="A16" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="G16" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M16" s="3" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="17" ht="16.5" spans="1:13">
-      <c r="A17" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G17" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M17" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="18" ht="33" spans="1:13">
-      <c r="A18" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="F18" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G18" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="H18" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="I18" s="3" t="s">
+      <c r="N63" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O63" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P63" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q63" s="3" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="64" ht="45" spans="1:17">
+      <c r="A64" s="3" t="s">
+        <v>710</v>
+      </c>
+      <c r="B64" s="3" t="s">
+        <v>711</v>
+      </c>
+      <c r="C64" s="3" t="s">
+        <v>712</v>
+      </c>
+      <c r="D64" s="3" t="s">
+        <v>713</v>
+      </c>
+      <c r="E64" s="3" t="s">
+        <v>714</v>
+      </c>
+      <c r="F64" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="G64" s="3" t="s">
+        <v>716</v>
+      </c>
+      <c r="H64" s="3" t="s">
+        <v>717</v>
+      </c>
+      <c r="I64" s="3" t="s">
+        <v>718</v>
+      </c>
+      <c r="J64" s="3" t="s">
+        <v>719</v>
+      </c>
+      <c r="K64" s="3" t="s">
+        <v>720</v>
+      </c>
+      <c r="L64" s="3" t="s">
+        <v>721</v>
+      </c>
+      <c r="M64" s="3" t="s">
+        <v>722</v>
+      </c>
+      <c r="N64" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O64" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P64" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M18" s="3" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="19" ht="16.5" spans="1:13">
-      <c r="A19" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="G19" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="H19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M19" s="3" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="20" ht="16.5" spans="1:13">
-      <c r="A20" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="G20" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="H20" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M20" s="3" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="21" ht="16.5" spans="1:13">
-      <c r="A21" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="F21" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="G21" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="H21" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M21" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="22" ht="30" spans="1:13">
-      <c r="A22" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M22" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="23" ht="28.5" spans="1:13">
-      <c r="A23" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="F23" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="G23" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="H23" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M23" s="3" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="24" ht="45" spans="1:13">
-      <c r="A24" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="G24" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="H24" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M24" s="3" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="25" ht="30" spans="1:13">
-      <c r="A25" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F25" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="G25" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="H25" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M25" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="26" ht="30" spans="1:13">
-      <c r="A26" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G26" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="H26" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M26" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="27" ht="30" spans="1:13">
-      <c r="A27" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F27" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="G27" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="H27" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M27" s="3" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="28" ht="33" spans="1:13">
-      <c r="A28" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>225</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="F28" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="G28" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="H28" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M28" s="3" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="29" ht="16.5" spans="1:13">
-      <c r="A29" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M29" s="3" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="30" ht="30" spans="1:13">
-      <c r="A30" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="F30" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="H30" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M30" s="3" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="31" ht="16.5" spans="1:13">
-      <c r="A31" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="F31" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="G31" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="H31" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M31" s="3" t="s">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="32" ht="30" spans="1:13">
-      <c r="A32" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="G32" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M32" s="3" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="33" ht="49.5" spans="1:13">
-      <c r="A33" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C33" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="D33" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="G33" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M33" s="3" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="34" ht="33" spans="1:13">
-      <c r="A34" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>277</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>278</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>279</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>280</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>281</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>282</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>283</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M34" s="3" t="s">
-        <v>277</v>
-      </c>
-    </row>
-    <row r="35" ht="16.5" spans="1:13">
-      <c r="A35" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>286</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>287</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>288</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>289</v>
-      </c>
-      <c r="F35" s="3" t="s">
-        <v>290</v>
-      </c>
-      <c r="G35" s="3" t="s">
-        <v>291</v>
-      </c>
-      <c r="H35" s="3" t="s">
-        <v>292</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>293</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M35" s="3" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="36" ht="30" spans="1:13">
-      <c r="A36" s="3" t="s">
-        <v>294</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>295</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>296</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>297</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>298</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>299</v>
-      </c>
-      <c r="G36" s="3" t="s">
-        <v>300</v>
-      </c>
-      <c r="H36" s="3" t="s">
-        <v>301</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>302</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M36" s="3" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="37" ht="33" spans="1:13">
-      <c r="A37" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>304</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>305</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>306</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>307</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>308</v>
-      </c>
-      <c r="G37" s="3" t="s">
-        <v>309</v>
-      </c>
-      <c r="H37" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>311</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M37" s="3" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="38" ht="33" spans="1:13">
-      <c r="A38" s="3" t="s">
-        <v>312</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>313</v>
-      </c>
-      <c r="C38" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="D38" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>316</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>317</v>
-      </c>
-      <c r="G38" s="3" t="s">
-        <v>318</v>
-      </c>
-      <c r="H38" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>320</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M38" s="3" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="39" ht="16.5" spans="1:13">
-      <c r="A39" s="3" t="s">
-        <v>321</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>322</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>323</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>324</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>325</v>
-      </c>
-      <c r="F39" s="3" t="s">
-        <v>326</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>327</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>328</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>329</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M39" s="3" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="40" ht="16.5" spans="1:13">
-      <c r="A40" s="3" t="s">
-        <v>330</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F40" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G40" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H40" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M40" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="41" ht="16.5" spans="1:13">
-      <c r="A41" s="3" t="s">
-        <v>338</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>339</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>340</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="F41" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="G41" s="3" t="s">
-        <v>343</v>
-      </c>
-      <c r="H41" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M41" s="3" t="s">
-        <v>339</v>
-      </c>
-    </row>
-    <row r="42" ht="16.5" spans="1:13">
-      <c r="A42" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="H42" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M42" s="3" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="43" ht="45" spans="1:13">
-      <c r="A43" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="F43" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="G43" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M43" s="3" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="44" ht="33" spans="1:13">
-      <c r="A44" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="D44" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="F44" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="G44" s="3" t="s">
-        <v>366</v>
-      </c>
-      <c r="H44" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M44" s="3" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="45" ht="16.5" spans="1:13">
-      <c r="A45" s="3" t="s">
-        <v>369</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>372</v>
-      </c>
-      <c r="F45" s="3" t="s">
-        <v>373</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>374</v>
-      </c>
-      <c r="H45" s="3" t="s">
-        <v>375</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>376</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M45" s="3" t="s">
-        <v>370</v>
-      </c>
-    </row>
-    <row r="46" ht="16.5" spans="1:13">
-      <c r="A46" s="3" t="s">
-        <v>377</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>378</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>379</v>
-      </c>
-      <c r="F46" s="3" t="s">
-        <v>380</v>
-      </c>
-      <c r="G46" s="3" t="s">
-        <v>381</v>
-      </c>
-      <c r="H46" s="3" t="s">
-        <v>382</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M46" s="3" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="47" ht="30" spans="1:13">
-      <c r="A47" s="3" t="s">
-        <v>384</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="G47" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="H47" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M47" s="3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" spans="1:13">
-      <c r="A48" s="3" t="s">
-        <v>385</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="F48" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="G48" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="H48" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M48" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="49" ht="28.5" spans="1:13">
-      <c r="A49" s="3" t="s">
-        <v>393</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>394</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>395</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>396</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>397</v>
-      </c>
-      <c r="F49" s="3" t="s">
-        <v>398</v>
-      </c>
-      <c r="G49" s="3" t="s">
-        <v>399</v>
-      </c>
-      <c r="H49" s="3" t="s">
-        <v>400</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>401</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M49" s="3" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="50" ht="16.5" spans="1:13">
-      <c r="A50" s="3" t="s">
-        <v>402</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>331</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>332</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>333</v>
-      </c>
-      <c r="F50" s="3" t="s">
-        <v>334</v>
-      </c>
-      <c r="G50" s="3" t="s">
-        <v>335</v>
-      </c>
-      <c r="H50" s="3" t="s">
-        <v>336</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>337</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M50" s="3" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="51" ht="16.5" spans="1:13">
-      <c r="A51" s="3" t="s">
-        <v>403</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>405</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>406</v>
-      </c>
-      <c r="F51" s="3" t="s">
-        <v>407</v>
-      </c>
-      <c r="G51" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="H51" s="3" t="s">
-        <v>409</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>410</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M51" s="3" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="52" ht="16.5" spans="1:13">
-      <c r="A52" s="3" t="s">
-        <v>411</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>412</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>413</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>414</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>415</v>
-      </c>
-      <c r="F52" s="3" t="s">
-        <v>416</v>
-      </c>
-      <c r="G52" s="3" t="s">
-        <v>417</v>
-      </c>
-      <c r="H52" s="3" t="s">
-        <v>418</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>419</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M52" s="3" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="53" ht="16.5" spans="1:13">
-      <c r="A53" s="3" t="s">
-        <v>420</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>421</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>422</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>423</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>424</v>
-      </c>
-      <c r="F53" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="G53" s="3" t="s">
-        <v>426</v>
-      </c>
-      <c r="H53" s="3" t="s">
-        <v>427</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>428</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M53" s="3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="54" ht="16.5" spans="1:13">
-      <c r="A54" s="3" t="s">
-        <v>429</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>386</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>387</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>388</v>
-      </c>
-      <c r="F54" s="3" t="s">
-        <v>389</v>
-      </c>
-      <c r="G54" s="3" t="s">
-        <v>390</v>
-      </c>
-      <c r="H54" s="3" t="s">
-        <v>391</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>392</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M54" s="3" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="55" ht="16.5" spans="1:13">
-      <c r="A55" s="3" t="s">
-        <v>430</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>431</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>432</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>433</v>
-      </c>
-      <c r="F55" s="3" t="s">
-        <v>434</v>
-      </c>
-      <c r="G55" s="3" t="s">
-        <v>435</v>
-      </c>
-      <c r="H55" s="3" t="s">
-        <v>436</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>437</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M55" s="3" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="56" ht="16.5" spans="1:13">
-      <c r="A56" s="3" t="s">
-        <v>438</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>439</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>440</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>441</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="F56" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G56" s="3" t="s">
-        <v>442</v>
-      </c>
-      <c r="H56" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>443</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M56" s="3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-    <row r="57" ht="30" spans="1:13">
-      <c r="A57" s="3" t="s">
-        <v>444</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>445</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>446</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>447</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>448</v>
-      </c>
-      <c r="F57" s="3" t="s">
-        <v>449</v>
-      </c>
-      <c r="G57" s="3" t="s">
-        <v>450</v>
-      </c>
-      <c r="H57" s="3" t="s">
-        <v>451</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>452</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M57" s="3" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="58" ht="16.5" spans="1:13">
-      <c r="A58" s="3" t="s">
-        <v>453</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>454</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>455</v>
-      </c>
-      <c r="F58" s="3" t="s">
-        <v>456</v>
-      </c>
-      <c r="G58" s="3" t="s">
-        <v>457</v>
-      </c>
-      <c r="H58" s="3" t="s">
-        <v>458</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>459</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M58" s="3" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="59" ht="16.5" spans="1:13">
-      <c r="A59" s="3" t="s">
-        <v>460</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>461</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>462</v>
-      </c>
-      <c r="D59" s="3" t="s">
-        <v>463</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>464</v>
-      </c>
-      <c r="F59" s="3" t="s">
-        <v>465</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>466</v>
-      </c>
-      <c r="H59" s="3" t="s">
-        <v>467</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>468</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M59" s="3" t="s">
-        <v>461</v>
-      </c>
-    </row>
-    <row r="60" ht="16.5" spans="1:13">
-      <c r="A60" s="3" t="s">
-        <v>469</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>470</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>471</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>472</v>
-      </c>
-      <c r="F60" s="3" t="s">
-        <v>473</v>
-      </c>
-      <c r="G60" s="3" t="s">
-        <v>474</v>
-      </c>
-      <c r="H60" s="3" t="s">
-        <v>475</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>476</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M60" s="3" t="s">
-        <v>470</v>
-      </c>
-    </row>
-    <row r="61" ht="16.5" spans="1:13">
-      <c r="A61" s="3" t="s">
-        <v>477</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>478</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>479</v>
-      </c>
-      <c r="F61" s="3" t="s">
-        <v>480</v>
-      </c>
-      <c r="G61" s="3" t="s">
-        <v>481</v>
-      </c>
-      <c r="H61" s="3" t="s">
-        <v>482</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>483</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M61" s="3" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="62" ht="60" spans="1:13">
-      <c r="A62" s="3" t="s">
-        <v>484</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>485</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>486</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="E62" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="F62" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="G62" s="3" t="s">
-        <v>490</v>
-      </c>
-      <c r="H62" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M62" s="3" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="63" ht="16.5" spans="1:13">
-      <c r="A63" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="E63" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="F63" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="G63" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="H63" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="M63" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="64" ht="45" spans="1:13">
-      <c r="A64" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>497</v>
-      </c>
-      <c r="E64" s="3" t="s">
-        <v>498</v>
-      </c>
-      <c r="F64" s="3" t="s">
-        <v>499</v>
-      </c>
-      <c r="G64" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="H64" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="M64" s="3" t="s">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="65" ht="16.5" spans="1:13">
+      <c r="Q64" s="3" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="65" ht="16.5" spans="1:17">
       <c r="A65" s="3" t="s">
-        <v>503</v>
+        <v>723</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>504</v>
+        <v>724</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>505</v>
+        <v>725</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>506</v>
+        <v>726</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>507</v>
+        <v>727</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>508</v>
+        <v>728</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>509</v>
+        <v>729</v>
       </c>
       <c r="H65" s="3" t="s">
-        <v>510</v>
+        <v>730</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>511</v>
+        <v>731</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>20</v>
+        <v>732</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>21</v>
+        <v>733</v>
       </c>
       <c r="L65" s="3" t="s">
-        <v>22</v>
+        <v>734</v>
       </c>
       <c r="M65" s="3" t="s">
-        <v>504</v>
-      </c>
-    </row>
-    <row r="66" ht="30" spans="1:13">
+        <v>735</v>
+      </c>
+      <c r="N65" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O65" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P65" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q65" s="3" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="66" ht="30" spans="1:17">
       <c r="A66" s="3" t="s">
-        <v>512</v>
+        <v>736</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>513</v>
+        <v>737</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>514</v>
+        <v>738</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>515</v>
+        <v>739</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>516</v>
+        <v>740</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>517</v>
+        <v>741</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>518</v>
+        <v>742</v>
       </c>
       <c r="H66" s="3" t="s">
-        <v>519</v>
+        <v>743</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>520</v>
+        <v>744</v>
       </c>
       <c r="J66" s="3" t="s">
-        <v>20</v>
+        <v>745</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>21</v>
+        <v>746</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>22</v>
+        <v>747</v>
       </c>
       <c r="M66" s="3" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="67" ht="16.5" spans="1:13">
+        <v>748</v>
+      </c>
+      <c r="N66" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O66" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P66" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q66" s="3" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="67" ht="16.5" spans="1:17">
       <c r="A67" s="3" t="s">
-        <v>521</v>
+        <v>749</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>522</v>
+        <v>750</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>523</v>
+        <v>751</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>523</v>
+        <v>751</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>524</v>
+        <v>752</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>525</v>
+        <v>753</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>526</v>
+        <v>754</v>
       </c>
       <c r="H67" s="3" t="s">
-        <v>527</v>
+        <v>755</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>528</v>
+        <v>756</v>
       </c>
       <c r="J67" s="3" t="s">
-        <v>20</v>
+        <v>757</v>
       </c>
       <c r="K67" s="3" t="s">
-        <v>21</v>
+        <v>758</v>
       </c>
       <c r="L67" s="3" t="s">
-        <v>22</v>
+        <v>759</v>
       </c>
       <c r="M67" s="3" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="68" ht="16.5" spans="1:13">
+        <v>760</v>
+      </c>
+      <c r="N67" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O67" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P67" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q67" s="3" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="68" ht="16.5" spans="1:17">
       <c r="A68" s="3" t="s">
-        <v>529</v>
+        <v>761</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>530</v>
+        <v>762</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>531</v>
+        <v>763</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>531</v>
+        <v>763</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>532</v>
+        <v>764</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>533</v>
+        <v>765</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>534</v>
+        <v>766</v>
       </c>
       <c r="H68" s="3" t="s">
-        <v>535</v>
+        <v>767</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>536</v>
+        <v>768</v>
       </c>
       <c r="J68" s="3" t="s">
-        <v>20</v>
+        <v>769</v>
       </c>
       <c r="K68" s="3" t="s">
-        <v>21</v>
+        <v>770</v>
       </c>
       <c r="L68" s="3" t="s">
-        <v>22</v>
+        <v>771</v>
       </c>
       <c r="M68" s="3" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="69" ht="30" spans="1:13">
+        <v>772</v>
+      </c>
+      <c r="N68" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O68" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P68" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q68" s="3" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="69" ht="30" spans="1:17">
       <c r="A69" s="3" t="s">
-        <v>537</v>
+        <v>773</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>538</v>
+        <v>774</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>539</v>
+        <v>775</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>540</v>
+        <v>776</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>541</v>
+        <v>777</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>542</v>
+        <v>778</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>543</v>
+        <v>779</v>
       </c>
       <c r="H69" s="3" t="s">
-        <v>544</v>
+        <v>780</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>545</v>
+        <v>781</v>
       </c>
       <c r="J69" s="3" t="s">
-        <v>20</v>
+        <v>782</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>21</v>
+        <v>783</v>
       </c>
       <c r="L69" s="3" t="s">
-        <v>22</v>
+        <v>784</v>
       </c>
       <c r="M69" s="3" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="70" ht="30" spans="1:13">
+        <v>785</v>
+      </c>
+      <c r="N69" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O69" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P69" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q69" s="3" t="s">
+        <v>774</v>
+      </c>
+    </row>
+    <row r="70" ht="30" spans="1:17">
       <c r="A70" s="3" t="s">
-        <v>546</v>
+        <v>786</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>547</v>
+        <v>787</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>548</v>
+        <v>788</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>549</v>
+        <v>789</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>550</v>
+        <v>790</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>551</v>
+        <v>791</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>552</v>
+        <v>792</v>
       </c>
       <c r="H70" s="3" t="s">
-        <v>553</v>
+        <v>793</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>554</v>
+        <v>794</v>
       </c>
       <c r="J70" s="3" t="s">
-        <v>20</v>
+        <v>795</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>21</v>
+        <v>796</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>101</v>
+        <v>797</v>
       </c>
       <c r="M70" s="3" t="s">
-        <v>547</v>
+        <v>798</v>
+      </c>
+      <c r="N70" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="O70" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="P70" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q70" s="3" t="s">
+        <v>787</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:L70" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:P70" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <dataValidations count="1">
-    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="K70 K2:K69">
+    <dataValidation type="list" showErrorMessage="1" error="请选择正常、待复核、已复核或待清理。" sqref="O2:O70">
       <formula1>"正常,待复核,已复核,待清理"</formula1>
     </dataValidation>
   </dataValidations>
@@ -5812,374 +7384,374 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>555</v>
+        <v>799</v>
       </c>
       <c r="B1" t="s">
-        <v>101</v>
+        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>556</v>
+        <v>800</v>
       </c>
       <c r="B2" t="s">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>557</v>
+        <v>801</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>558</v>
+        <v>802</v>
       </c>
       <c r="B3" t="s">
-        <v>559</v>
+        <v>803</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>54</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>67</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>56</v>
+        <v>79</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10" t="s">
-        <v>64</v>
+        <v>91</v>
       </c>
     </row>
     <row r="11" spans="1:3">
       <c r="A11" t="s">
-        <v>72</v>
+        <v>103</v>
       </c>
     </row>
     <row r="12" spans="1:3">
       <c r="A12" t="s">
-        <v>81</v>
+        <v>116</v>
       </c>
     </row>
     <row r="13" spans="1:3">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>129</v>
       </c>
     </row>
     <row r="14" spans="1:3">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>130</v>
       </c>
     </row>
     <row r="15" spans="1:3">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
     </row>
     <row r="16" spans="1:3">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:1">
       <c r="A17" t="s">
-        <v>111</v>
+        <v>158</v>
       </c>
     </row>
     <row r="18" spans="1:1">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:1">
       <c r="A19" t="s">
-        <v>128</v>
+        <v>183</v>
       </c>
     </row>
     <row r="20" spans="1:1">
       <c r="A20" t="s">
-        <v>137</v>
+        <v>196</v>
       </c>
     </row>
     <row r="21" spans="1:1">
       <c r="A21" t="s">
-        <v>145</v>
+        <v>208</v>
       </c>
     </row>
     <row r="22" spans="1:1">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>219</v>
       </c>
     </row>
     <row r="23" spans="1:1">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>232</v>
       </c>
     </row>
     <row r="24" spans="1:1">
       <c r="A24" t="s">
-        <v>170</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" spans="1:1">
       <c r="A25" t="s">
-        <v>179</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" spans="1:1">
       <c r="A26" t="s">
-        <v>188</v>
+        <v>270</v>
       </c>
     </row>
     <row r="27" spans="1:1">
       <c r="A27" t="s">
-        <v>197</v>
+        <v>283</v>
       </c>
     </row>
     <row r="28" spans="1:1">
       <c r="A28" t="s">
-        <v>205</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:1">
       <c r="A29" t="s">
-        <v>214</v>
+        <v>308</v>
       </c>
     </row>
     <row r="30" spans="1:1">
       <c r="A30" t="s">
-        <v>223</v>
+        <v>321</v>
       </c>
     </row>
     <row r="31" spans="1:1">
       <c r="A31" t="s">
-        <v>232</v>
+        <v>334</v>
       </c>
     </row>
     <row r="32" spans="1:1">
       <c r="A32" t="s">
-        <v>241</v>
+        <v>346</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>249</v>
+        <v>358</v>
       </c>
     </row>
     <row r="34" spans="1:1">
       <c r="A34" t="s">
-        <v>258</v>
+        <v>371</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>267</v>
+        <v>384</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>276</v>
+        <v>397</v>
       </c>
     </row>
     <row r="37" spans="1:1">
       <c r="A37" t="s">
-        <v>285</v>
+        <v>410</v>
       </c>
     </row>
     <row r="38" spans="1:1">
       <c r="A38" t="s">
-        <v>294</v>
+        <v>423</v>
       </c>
     </row>
     <row r="39" spans="1:1">
       <c r="A39" t="s">
-        <v>303</v>
+        <v>436</v>
       </c>
     </row>
     <row r="40" spans="1:1">
       <c r="A40" t="s">
-        <v>312</v>
+        <v>449</v>
       </c>
     </row>
     <row r="41" spans="1:1">
       <c r="A41" t="s">
-        <v>321</v>
+        <v>462</v>
       </c>
     </row>
     <row r="42" spans="1:1">
       <c r="A42" t="s">
-        <v>330</v>
+        <v>475</v>
       </c>
     </row>
     <row r="43" spans="1:1">
       <c r="A43" t="s">
-        <v>338</v>
+        <v>487</v>
       </c>
     </row>
     <row r="44" spans="1:1">
       <c r="A44" t="s">
-        <v>345</v>
+        <v>494</v>
       </c>
     </row>
     <row r="45" spans="1:1">
       <c r="A45" t="s">
-        <v>352</v>
+        <v>504</v>
       </c>
     </row>
     <row r="46" spans="1:1">
       <c r="A46" t="s">
-        <v>361</v>
+        <v>517</v>
       </c>
     </row>
     <row r="47" spans="1:1">
       <c r="A47" t="s">
-        <v>369</v>
+        <v>529</v>
       </c>
     </row>
     <row r="48" spans="1:1">
       <c r="A48" t="s">
-        <v>377</v>
+        <v>541</v>
       </c>
     </row>
     <row r="49" spans="1:1">
       <c r="A49" t="s">
-        <v>384</v>
+        <v>552</v>
       </c>
     </row>
     <row r="50" spans="1:1">
       <c r="A50" t="s">
-        <v>385</v>
+        <v>553</v>
       </c>
     </row>
     <row r="51" spans="1:1">
       <c r="A51" t="s">
-        <v>393</v>
+        <v>565</v>
       </c>
     </row>
     <row r="52" spans="1:1">
       <c r="A52" t="s">
-        <v>402</v>
+        <v>578</v>
       </c>
     </row>
     <row r="53" spans="1:1">
       <c r="A53" t="s">
-        <v>403</v>
+        <v>579</v>
       </c>
     </row>
     <row r="54" spans="1:1">
       <c r="A54" t="s">
-        <v>411</v>
+        <v>591</v>
       </c>
     </row>
     <row r="55" spans="1:1">
       <c r="A55" t="s">
-        <v>420</v>
+        <v>602</v>
       </c>
     </row>
     <row r="56" spans="1:1">
       <c r="A56" t="s">
-        <v>429</v>
+        <v>615</v>
       </c>
     </row>
     <row r="57" spans="1:1">
       <c r="A57" t="s">
-        <v>430</v>
+        <v>616</v>
       </c>
     </row>
     <row r="58" spans="1:1">
       <c r="A58" t="s">
-        <v>438</v>
+        <v>628</v>
       </c>
     </row>
     <row r="59" spans="1:1">
       <c r="A59" t="s">
-        <v>444</v>
+        <v>637</v>
       </c>
     </row>
     <row r="60" spans="1:1">
       <c r="A60" t="s">
-        <v>453</v>
+        <v>650</v>
       </c>
     </row>
     <row r="61" spans="1:1">
       <c r="A61" t="s">
-        <v>460</v>
+        <v>661</v>
       </c>
     </row>
     <row r="62" spans="1:1">
       <c r="A62" t="s">
-        <v>469</v>
+        <v>674</v>
       </c>
     </row>
     <row r="63" spans="1:1">
       <c r="A63" t="s">
-        <v>477</v>
+        <v>685</v>
       </c>
     </row>
     <row r="64" spans="1:1">
       <c r="A64" t="s">
-        <v>484</v>
+        <v>696</v>
       </c>
     </row>
     <row r="65" spans="1:1">
       <c r="A65" t="s">
-        <v>493</v>
+        <v>709</v>
       </c>
     </row>
     <row r="66" spans="1:1">
       <c r="A66" t="s">
-        <v>494</v>
+        <v>710</v>
       </c>
     </row>
     <row r="67" spans="1:1">
       <c r="A67" t="s">
-        <v>503</v>
+        <v>723</v>
       </c>
     </row>
     <row r="68" spans="1:1">
       <c r="A68" t="s">
-        <v>512</v>
+        <v>736</v>
       </c>
     </row>
     <row r="69" spans="1:1">
       <c r="A69" t="s">
-        <v>521</v>
+        <v>749</v>
       </c>
     </row>
     <row r="70" spans="1:1">
       <c r="A70" t="s">
-        <v>529</v>
+        <v>761</v>
       </c>
     </row>
     <row r="71" spans="1:1">
       <c r="A71" t="s">
-        <v>537</v>
+        <v>773</v>
       </c>
     </row>
     <row r="72" spans="1:1">
       <c r="A72" t="s">
-        <v>546</v>
+        <v>786</v>
       </c>
     </row>
   </sheetData>
@@ -6200,42 +7772,42 @@
   <sheetData>
     <row r="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>560</v>
+        <v>804</v>
       </c>
     </row>
     <row r="2" spans="1:1">
       <c r="A2" s="1" t="s">
-        <v>561</v>
+        <v>805</v>
       </c>
     </row>
     <row r="3" spans="1:1">
       <c r="A3" s="1" t="s">
-        <v>562</v>
+        <v>806</v>
       </c>
     </row>
     <row r="4" spans="1:1">
       <c r="A4" s="1" t="s">
-        <v>563</v>
+        <v>807</v>
       </c>
     </row>
     <row r="5" spans="1:1">
       <c r="A5" s="1" t="s">
-        <v>564</v>
+        <v>808</v>
       </c>
     </row>
     <row r="6" spans="1:1">
       <c r="A6" s="1" t="s">
-        <v>565</v>
+        <v>809</v>
       </c>
     </row>
     <row r="7" spans="1:1">
       <c r="A7" s="1" t="s">
-        <v>566</v>
+        <v>810</v>
       </c>
     </row>
     <row r="8" spans="1:1">
       <c r="A8" s="1" t="s">
-        <v>567</v>
+        <v>811</v>
       </c>
     </row>
   </sheetData>
